--- a/IG/7日版/AI Native-提案演習_IG.xlsx
+++ b/IG/7日版/AI Native-提案演習_IG.xlsx
@@ -5,23 +5,23 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{967999EE-CBC3-4386-B263-3556BE4F6A21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4369A00-70B5-4A43-AD0C-6997A41DFC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="スケジュール（5日）" sheetId="33" r:id="rId1"/>
+    <sheet name="スケジュール（3日）" sheetId="33" r:id="rId1"/>
     <sheet name="特記イベント" sheetId="36" r:id="rId2"/>
     <sheet name="講義" sheetId="31" r:id="rId3"/>
     <sheet name="master" sheetId="21" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（5日）'!$A$1:$L$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$60</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$14</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（3日）'!$A$1:$H$44</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
 </workbook>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="301" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="150">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -550,44 +550,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>【参考】最終発表時の評価基準</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>ブロック内発表の実施</t>
-    <rPh sb="4" eb="5">
-      <t>ナイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ハッピョウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ジッシ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>全体発表</t>
-    <rPh sb="0" eb="2">
-      <t>ゼンタイ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ハッピョウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>個人演習</t>
-    <rPh sb="0" eb="2">
-      <t>コジン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>チーム演習</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>2 日目</t>
     <rPh sb="2" eb="3">
       <t>ニチ</t>
@@ -608,26 +570,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>4 日目</t>
-    <rPh sb="2" eb="3">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>メ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>5 日目</t>
-    <rPh sb="2" eb="3">
-      <t>ニチ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>メ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>予備</t>
     <rPh sb="0" eb="2">
       <t>ヨビ</t>
@@ -639,9 +581,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>【AI Native提案企画研修】チーム演習説明.pptx</t>
-  </si>
-  <si>
     <t xml:space="preserve">・AI-02
 </t>
     <phoneticPr fontId="3"/>
@@ -677,19 +616,6 @@
     </rPh>
     <rPh sb="4" eb="6">
       <t>テイシュツ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>ブロック内発表の説明</t>
-    <rPh sb="4" eb="5">
-      <t>ナイ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ハッピョウ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>セツメイ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -812,32 +738,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>サービスの決定（チーム）</t>
-    <rPh sb="5" eb="7">
-      <t>ケッテイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>サービスの提案</t>
-    <rPh sb="5" eb="7">
-      <t>テイアン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>チーム演習の概要について説明する。
-■手順
-1. サービスの提案
-2. サービスの決定
-3. 成果物の作成
-4. 成果物の提出</t>
-    <rPh sb="31" eb="33">
-      <t>テイアン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">個人演習の概要について説明する。
 ■手順
 1. サービスの検討
@@ -855,63 +755,8 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>決定したサービスについて、チームで企画提案書およびプロトタイプを作成することを説明する。
-個人演習で作成した成果物やチーム内での議論を踏まえ、サービス内容をブラッシュアップすること。
-また、課題の背景、ターゲットユーザー、提供価値、社会的意義、実現性、市場性などの観点からサービスを深掘りし、チームとしての提案内容を具体化すること。
-ブラッシュアップおよび深掘りした内容を企画提案書にまとめるとともに、サービスの利用イメージが伝わるプロトタイプを作成すること。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">・AI-01
 </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">発表の進め方について説明する。
-各チームで作成した企画提案書およびプロトタイプを用いて、サービスの提案を行う。
-提案では、解決したい課題、ターゲットユーザー、提供価値、社会的意義、実現性、市場性、およびサービスの利用イメージについて説明すること。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>※Teams会議の画面共有機能を利用し、企画提案書やプロトタイプを表示しながら発表することを推奨する。</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>ブロック代表（選抜チーム）の決定</t>
-    <rPh sb="4" eb="6">
-      <t>ダイヒョウ</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>センバツ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ケッテイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>Teamsのアンケート機能を利用して、ブロック代表を決定する。</t>
-    <rPh sb="11" eb="13">
-      <t>キノウ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>リヨウ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>ダイヒョウ</t>
-    </rPh>
-    <rPh sb="26" eb="28">
-      <t>ケッテイ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1310,103 +1155,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">成果物の概要について説明する。
-■成果物の種類
-　・企画提案書
-　　PowerPoint形式
-　・プロトタイプ
-　　作成したアプリケーションのソースコード一式
-　　※ルートディレクトリをそのままzip化する
-　・命名規約
-　　企画提案書　→　チーム名_企画提案書.pptx
-　　プロトタイプ　→　チーム名_プロトタイプ.zip
-■提出方法
-　・提出先：Teamの共有フォルダ
-　　※全体連絡・共通＞02_AIネイティブ提案企画研修＞03_提出先＞02_チーム演習
-</t>
-    <rPh sb="0" eb="3">
-      <t>セイカブツ</t>
-    </rPh>
-    <rPh sb="115" eb="116">
-      <t>サキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">評価基準は存在してること説明する。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>※本研修の提案書として正しい内容であればよい。</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <rPh sb="0" eb="2">
-      <t>ヒョウカ</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>キジュン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ソンザイ</t>
-    </rPh>
-    <rPh sb="12" eb="14">
-      <t>セツメイ</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ホン</t>
-    </rPh>
-    <rPh sb="20" eb="22">
-      <t>ケンシュウ</t>
-    </rPh>
-    <rPh sb="23" eb="26">
-      <t>テイアンショ</t>
-    </rPh>
-    <rPh sb="29" eb="30">
-      <t>タダ</t>
-    </rPh>
-    <rPh sb="32" eb="34">
-      <t>ナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">チームとして提案するサービスを決定することを説明する。
-サービスの決定方法は問わないが、以下のいずれかの方法で決定すること。
-・チームメンバーが提案したサービス案の中から、代表となるサービスを選定する。
-・複数のサービス案の良い点を組み合わせ、新たなサービスとして再構築する。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>※決定にあたっては、提供価値、社会的意義、実現性、市場性などの観点を考慮すること。</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>背景（サービスを取り巻く状況や市場動向を説明＝Why＝なぜ？）について説明する。</t>
     <rPh sb="35" eb="37">
       <t>セツメイ</t>
@@ -1483,124 +1231,6 @@
   <si>
     <t xml:space="preserve">・AI-04
 </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>発表に向けて、チーム内で提案内容のリハーサルを実施してもらうことを説明する。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案のリハーサル</t>
-    <rPh sb="0" eb="2">
-      <t>テイアン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>個人演習で作成した成果物をチーム内で提案してもらうことを説明する。
-■手順
-1. 提案内容の発表順を決定する。
-2. 企画提案書およびプロトタイプを用いてサービスを提案する。
-3. 提案内容に対する質疑応答を行う。
-※手順2～3を繰り返し実施する。</t>
-  </si>
-  <si>
-    <t>チーム演習で作成した成果物をブロック内で提案してもらうことを説明する。
-■手順
-1. 提案内容の発表順を決定する。（15分）
-2. 企画提案書およびプロトタイプを用いてサービスを提案する。（15分）
-3. 提案内容に対する質疑応答を行う。（5分）
-※手順2～3をチームごとに繰り返し実施する。</t>
-    <rPh sb="3" eb="5">
-      <t>エンシュウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">ブロック代表の成果物を全体に提案してもらうことを説明する。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">※提案内容の発表順については講師側で決定しておく。
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">
-■手順
-1. 企画提案書およびプロトタイプを用いてサービスを提案する。（15分）
-2. 提案内容に対する質疑応答を行う。（8分）
-※手順1～2をブロック代表ごとに繰り返し実施する。</t>
-    </r>
-    <rPh sb="4" eb="6">
-      <t>ダイヒョウ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ゼンタイ</t>
-    </rPh>
-    <rPh sb="44" eb="46">
-      <t>コウシ</t>
-    </rPh>
-    <rPh sb="46" eb="47">
-      <t>ガワ</t>
-    </rPh>
-    <rPh sb="48" eb="50">
-      <t>ケッテイ</t>
-    </rPh>
-    <rPh sb="95" eb="96">
-      <t>ブン</t>
-    </rPh>
-    <rPh sb="134" eb="136">
-      <t>ダイヒョウ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1692,28 +1322,131 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>提案会（ブロック代表の決定）</t>
+    <t>個人演習1</t>
     <rPh sb="0" eb="2">
+      <t>コジン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>個人演習2</t>
+    <rPh sb="0" eb="2">
+      <t>コジン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>アンケート</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>・アンケートの説明</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>個人提案の実施</t>
+    <rPh sb="0" eb="2">
+      <t>コジン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
       <t>テイアン</t>
     </rPh>
-    <rPh sb="2" eb="3">
-      <t>カイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>ダイヒョウ</t>
+    <rPh sb="5" eb="7">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>演習内容の説明</t>
+    <rPh sb="0" eb="2">
+      <t>エンシュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-04
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案内容のブラッシュアップ</t>
+    <rPh sb="0" eb="4">
+      <t>テイアンナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">個人演習の概要について説明する。
+■手順
+1. 発表順の決定
+2. 提案の実施
+3. 提案内容のブラッシュアップ
+</t>
+    <rPh sb="0" eb="2">
+      <t>コジン</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>ハッピョウ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ケッテイ</t>
+    </rPh>
+    <rPh sb="35" eb="37">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="44" eb="46">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="46" eb="48">
+      <t>ナイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>フィードバックのを基に提案内容をブラッシュアップすることを伝える。</t>
+    <rPh sb="9" eb="10">
+      <t>モト</t>
     </rPh>
     <rPh sb="11" eb="13">
-      <t>ケッテイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案会（最終）</t>
-    <rPh sb="0" eb="3">
-      <t>テイアンカイ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>キョウシツダイヒョウ</t>
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="29" eb="30">
+      <t>ツタ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>作成した成果物をチーム内のメンバーに提案し、フィードバックをもらうことを説明する。
+■手順
+1. 企画提案書およびプロトタイプを用いてサービスを提案する。（10分）
+2. 質疑応答（5分）
+3. 提案内容（提案書、プロトタイプ、提案の方法）に関するフィードバックを行う。（5分）</t>
+    <rPh sb="87" eb="91">
+      <t>シツギオウトウ</t>
+    </rPh>
+    <rPh sb="104" eb="107">
+      <t>テイアンショ</t>
+    </rPh>
+    <rPh sb="115" eb="117">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="118" eb="120">
+      <t>ホウホウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1889,7 +1622,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1941,12 +1674,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFC5D9F1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2138,7 +1865,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="128">
+  <cellXfs count="114">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2334,93 +2061,63 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2460,6 +2157,15 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2478,14 +2184,14 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2496,32 +2202,11 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2879,7 +2564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:H44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="7" style="1" bestFit="1" customWidth="1"/>
@@ -2889,37 +2574,27 @@
     <col min="5" max="5" width="45" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="7.33203125" style="15" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="45" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.33203125" style="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="45" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.33203125" style="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="45" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7.33203125" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="6"/>
+    <col min="8" max="8" width="7.33203125" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:7">
       <c r="D1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="J1" s="1"/>
-    </row>
-    <row r="2" spans="1:11" ht="27">
+    </row>
+    <row r="2" spans="1:7" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="93" t="str">
+      <c r="B2" s="83" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-提案演習_IG」</v>
       </c>
-      <c r="C2" s="93"/>
-      <c r="D2" s="93"/>
-      <c r="E2" s="93"/>
-      <c r="F2" s="93"/>
-      <c r="G2" s="93"/>
-      <c r="H2" s="93"/>
-      <c r="I2" s="93"/>
-      <c r="J2" s="65"/>
-      <c r="K2" s="65"/>
-    </row>
-    <row r="3" spans="1:11" ht="27.6" thickBot="1">
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
+      <c r="G2" s="83"/>
+    </row>
+    <row r="3" spans="1:7" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
       <c r="B3" s="14"/>
       <c r="C3" s="13"/>
@@ -2927,88 +2602,60 @@
       <c r="E3" s="13"/>
       <c r="F3" s="13"/>
       <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
-      <c r="J3" s="13"/>
-      <c r="K3" s="13"/>
-    </row>
-    <row r="4" spans="1:11" ht="27.6" thickBot="1">
+    </row>
+    <row r="4" spans="1:7" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="94" t="s">
+      <c r="B4" s="84" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="95"/>
+      <c r="C4" s="85"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-    </row>
-    <row r="5" spans="1:11" ht="27.6" thickBot="1">
+    </row>
+    <row r="5" spans="1:7" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="96"/>
-      <c r="C5" s="97"/>
+      <c r="B5" s="86"/>
+      <c r="C5" s="87"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="13"/>
-    </row>
-    <row r="6" spans="1:11">
+    </row>
+    <row r="6" spans="1:7">
       <c r="D6" s="1"/>
       <c r="F6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="J6" s="1"/>
-    </row>
-    <row r="7" spans="1:11" ht="16.2">
-      <c r="B7" s="98" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="16.2">
+      <c r="B7" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="98"/>
+      <c r="C7" s="88"/>
       <c r="D7" s="1"/>
       <c r="F7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="J7" s="1"/>
-    </row>
-    <row r="8" spans="1:11">
+    </row>
+    <row r="8" spans="1:7">
       <c r="D8" s="1"/>
       <c r="E8" s="15"/>
       <c r="F8" s="1"/>
       <c r="G8" s="15"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="15"/>
-    </row>
-    <row r="9" spans="1:11">
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9" s="21"/>
       <c r="C9" s="21" t="s">
         <v>0</v>
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="21" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F9" s="21"/>
       <c r="G9" s="21" t="s">
-        <v>83</v>
-      </c>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21" t="s">
-        <v>84</v>
-      </c>
-      <c r="J9" s="21"/>
-      <c r="K9" s="21" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="14.25" customHeight="1">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="14.25" customHeight="1">
       <c r="A10" s="34">
         <v>0.39583333333333331</v>
       </c>
@@ -3030,20 +2677,8 @@
       <c r="G10" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="H10" s="16">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="I10" s="59" t="s">
-        <v>3</v>
-      </c>
-      <c r="J10" s="16">
-        <v>0.39583333333333331</v>
-      </c>
-      <c r="K10" s="59" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+    </row>
+    <row r="11" spans="1:7">
       <c r="A11" s="36"/>
       <c r="B11" s="54">
         <v>0.40625</v>
@@ -3055,31 +2690,20 @@
       <c r="D11" s="54">
         <v>0.40625</v>
       </c>
-      <c r="E11" s="90"/>
+      <c r="E11" s="80"/>
       <c r="F11" s="54">
         <v>0.40625</v>
       </c>
-      <c r="G11" s="90" t="str">
+      <c r="G11" s="80" t="str">
         <f>master!B40</f>
-        <v>チーム演習</v>
-      </c>
-      <c r="H11" s="54">
-        <v>0.40625</v>
-      </c>
-      <c r="I11" s="91"/>
-      <c r="J11" s="54">
-        <v>0.40625</v>
-      </c>
-      <c r="K11" s="79" t="str">
-        <f>master!B49</f>
-        <v>提案会（ブロック代表の決定）</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>個人演習2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="A12" s="34">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B12" s="86">
+      <c r="B12" s="76">
         <v>0.41666666666666669</v>
       </c>
       <c r="C12" s="57" t="str">
@@ -3087,28 +2711,20 @@
         <v>企画提案のステップ</v>
       </c>
       <c r="D12" s="56"/>
-      <c r="E12" s="91"/>
+      <c r="E12" s="81"/>
       <c r="F12" s="56"/>
-      <c r="G12" s="91"/>
-      <c r="H12" s="56"/>
-      <c r="I12" s="91"/>
-      <c r="J12" s="56"/>
-      <c r="K12" s="80"/>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="G12" s="81"/>
+    </row>
+    <row r="13" spans="1:7">
       <c r="A13" s="35"/>
-      <c r="B13" s="87"/>
+      <c r="B13" s="77"/>
       <c r="C13" s="58"/>
       <c r="D13" s="56"/>
-      <c r="E13" s="91"/>
+      <c r="E13" s="81"/>
       <c r="F13" s="56"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="56"/>
-      <c r="I13" s="91"/>
-      <c r="J13" s="56"/>
-      <c r="K13" s="80"/>
-    </row>
-    <row r="14" spans="1:11">
+      <c r="G13" s="81"/>
+    </row>
+    <row r="14" spans="1:7">
       <c r="A14" s="35"/>
       <c r="B14" s="54">
         <v>0.4375</v>
@@ -3118,117 +2734,85 @@
         <v>提案書のサンプルについて</v>
       </c>
       <c r="D14" s="56"/>
-      <c r="E14" s="91"/>
+      <c r="E14" s="81"/>
       <c r="F14" s="56"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="56"/>
-      <c r="I14" s="91"/>
-      <c r="J14" s="56"/>
-      <c r="K14" s="80"/>
-    </row>
-    <row r="15" spans="1:11">
+      <c r="G14" s="81"/>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" s="36"/>
-      <c r="B15" s="88" t="s">
+      <c r="B15" s="78" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="58"/>
       <c r="D15" s="56"/>
-      <c r="E15" s="91"/>
+      <c r="E15" s="81"/>
       <c r="F15" s="56"/>
-      <c r="G15" s="91"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="91"/>
-      <c r="J15" s="56"/>
-      <c r="K15" s="80"/>
-    </row>
-    <row r="16" spans="1:11">
+      <c r="G15" s="81"/>
+    </row>
+    <row r="16" spans="1:7">
       <c r="A16" s="34">
         <v>0.45833333333333331</v>
       </c>
       <c r="B16" s="54">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C16" s="90" t="str">
+      <c r="C16" s="80" t="str">
         <f>master!B32</f>
-        <v>個人演習</v>
+        <v>個人演習1</v>
       </c>
       <c r="D16" s="56"/>
-      <c r="E16" s="91"/>
+      <c r="E16" s="81"/>
       <c r="F16" s="56"/>
-      <c r="G16" s="91"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="91"/>
-      <c r="J16" s="56"/>
-      <c r="K16" s="80"/>
-    </row>
-    <row r="17" spans="1:12">
+      <c r="G16" s="81"/>
+    </row>
+    <row r="17" spans="1:8">
       <c r="A17" s="35"/>
       <c r="B17" s="56"/>
-      <c r="C17" s="91"/>
+      <c r="C17" s="81"/>
       <c r="D17" s="56"/>
-      <c r="E17" s="91"/>
+      <c r="E17" s="81"/>
       <c r="F17" s="56"/>
-      <c r="G17" s="91"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="91"/>
-      <c r="J17" s="56"/>
-      <c r="K17" s="80"/>
-    </row>
-    <row r="18" spans="1:12">
+      <c r="G17" s="81"/>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="35"/>
       <c r="B18" s="56"/>
-      <c r="C18" s="91"/>
+      <c r="C18" s="81"/>
       <c r="D18" s="56"/>
-      <c r="E18" s="91"/>
+      <c r="E18" s="81"/>
       <c r="F18" s="56"/>
-      <c r="G18" s="91"/>
-      <c r="H18" s="56"/>
-      <c r="I18" s="91"/>
-      <c r="J18" s="56"/>
-      <c r="K18" s="80"/>
-    </row>
-    <row r="19" spans="1:12">
+      <c r="G18" s="81"/>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="36"/>
       <c r="B19" s="56"/>
-      <c r="C19" s="91"/>
+      <c r="C19" s="81"/>
       <c r="D19" s="56"/>
-      <c r="E19" s="91"/>
+      <c r="E19" s="81"/>
       <c r="F19" s="56"/>
-      <c r="G19" s="91"/>
-      <c r="H19" s="56"/>
-      <c r="I19" s="91"/>
-      <c r="J19" s="56"/>
-      <c r="K19" s="80"/>
-    </row>
-    <row r="20" spans="1:12">
+      <c r="G19" s="81"/>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="53">
         <v>0.5</v>
       </c>
       <c r="B20" s="56"/>
-      <c r="C20" s="91"/>
+      <c r="C20" s="81"/>
       <c r="D20" s="56"/>
-      <c r="E20" s="91"/>
+      <c r="E20" s="81"/>
       <c r="F20" s="56"/>
-      <c r="G20" s="91"/>
-      <c r="H20" s="56"/>
-      <c r="I20" s="91"/>
-      <c r="J20" s="56"/>
-      <c r="K20" s="80"/>
-    </row>
-    <row r="21" spans="1:12">
+      <c r="G20" s="81"/>
+    </row>
+    <row r="21" spans="1:8">
       <c r="A21" s="49"/>
       <c r="B21" s="51"/>
-      <c r="C21" s="89"/>
-      <c r="D21" s="85"/>
-      <c r="E21" s="89"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="89"/>
-      <c r="H21" s="85"/>
-      <c r="I21" s="91"/>
-      <c r="J21" s="51"/>
-      <c r="K21" s="81"/>
-    </row>
-    <row r="22" spans="1:12">
+      <c r="C21" s="79"/>
+      <c r="D21" s="75"/>
+      <c r="E21" s="79"/>
+      <c r="F21" s="75"/>
+      <c r="G21" s="79"/>
+    </row>
+    <row r="22" spans="1:8">
       <c r="A22" s="35"/>
       <c r="B22" s="35">
         <v>0.52083333333333337</v>
@@ -3248,20 +2832,8 @@
       <c r="G22" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="H22" s="35">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="I22" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="35">
-        <v>0.52083333333333337</v>
-      </c>
-      <c r="K22" s="60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12">
+    </row>
+    <row r="23" spans="1:8">
       <c r="A23" s="36"/>
       <c r="B23" s="35" t="s">
         <v>29</v>
@@ -3275,16 +2847,8 @@
         <v>29</v>
       </c>
       <c r="G23" s="61"/>
-      <c r="H23" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="I23" s="61"/>
-      <c r="J23" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="K23" s="61"/>
-    </row>
-    <row r="24" spans="1:12">
+    </row>
+    <row r="24" spans="1:8">
       <c r="A24" s="34">
         <v>0.54166666666666663</v>
       </c>
@@ -3300,16 +2864,8 @@
         <v>29</v>
       </c>
       <c r="G24" s="61"/>
-      <c r="H24" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="I24" s="61"/>
-      <c r="J24" s="35" t="s">
-        <v>29</v>
-      </c>
-      <c r="K24" s="61"/>
-    </row>
-    <row r="25" spans="1:12">
+    </row>
+    <row r="25" spans="1:8">
       <c r="A25" s="35"/>
       <c r="B25" s="36" t="s">
         <v>29</v>
@@ -3323,312 +2879,221 @@
         <v>29</v>
       </c>
       <c r="G25" s="62"/>
-      <c r="H25" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="I25" s="62"/>
-      <c r="J25" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="K25" s="62"/>
-    </row>
-    <row r="26" spans="1:12">
+    </row>
+    <row r="26" spans="1:8">
       <c r="A26" s="35"/>
       <c r="B26" s="37">
         <v>0.5625</v>
       </c>
-      <c r="C26" s="90"/>
+      <c r="C26" s="80"/>
       <c r="D26" s="37">
         <v>0.5625</v>
       </c>
-      <c r="E26" s="90"/>
+      <c r="E26" s="80"/>
       <c r="F26" s="37">
         <v>0.5625</v>
       </c>
-      <c r="G26" s="90"/>
-      <c r="H26" s="37">
-        <v>0.5625</v>
-      </c>
-      <c r="I26" s="90"/>
-      <c r="J26" s="37">
-        <v>0.5625</v>
-      </c>
-      <c r="K26" s="79" t="str">
-        <f>master!B52</f>
-        <v>提案会（最終）</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12">
+      <c r="G26" s="80"/>
+    </row>
+    <row r="27" spans="1:8">
       <c r="A27" s="36"/>
       <c r="B27" s="39"/>
-      <c r="C27" s="91"/>
+      <c r="C27" s="81"/>
       <c r="D27" s="39"/>
-      <c r="E27" s="91"/>
+      <c r="E27" s="81"/>
       <c r="F27" s="39"/>
-      <c r="G27" s="91"/>
-      <c r="H27" s="39"/>
-      <c r="I27" s="91"/>
-      <c r="J27" s="39"/>
-      <c r="K27" s="80"/>
-    </row>
-    <row r="28" spans="1:12">
+      <c r="G27" s="81"/>
+    </row>
+    <row r="28" spans="1:8">
       <c r="A28" s="34">
         <v>0.58333333333333337</v>
       </c>
       <c r="B28" s="39"/>
-      <c r="C28" s="91"/>
+      <c r="C28" s="81"/>
       <c r="D28" s="39"/>
-      <c r="E28" s="91"/>
+      <c r="E28" s="81"/>
       <c r="F28" s="39"/>
-      <c r="G28" s="91"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="91"/>
-      <c r="J28" s="39"/>
-      <c r="K28" s="80"/>
-    </row>
-    <row r="29" spans="1:12">
+      <c r="G28" s="81"/>
+    </row>
+    <row r="29" spans="1:8">
       <c r="A29" s="35"/>
       <c r="B29" s="39"/>
-      <c r="C29" s="91"/>
+      <c r="C29" s="81"/>
       <c r="D29" s="39"/>
-      <c r="E29" s="91"/>
+      <c r="E29" s="81"/>
       <c r="F29" s="39"/>
-      <c r="G29" s="91"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="91"/>
-      <c r="J29" s="39"/>
-      <c r="K29" s="80"/>
-      <c r="L29" s="48"/>
-    </row>
-    <row r="30" spans="1:12">
+      <c r="G29" s="81"/>
+      <c r="H29" s="48"/>
+    </row>
+    <row r="30" spans="1:8">
       <c r="A30" s="35"/>
       <c r="B30" s="39"/>
-      <c r="C30" s="91"/>
+      <c r="C30" s="81"/>
       <c r="D30" s="39"/>
-      <c r="E30" s="91"/>
+      <c r="E30" s="81"/>
       <c r="F30" s="39"/>
-      <c r="G30" s="91"/>
-      <c r="H30" s="39"/>
-      <c r="I30" s="91"/>
-      <c r="J30" s="39"/>
-      <c r="K30" s="80"/>
-      <c r="L30" s="48"/>
-    </row>
-    <row r="31" spans="1:12">
+      <c r="G30" s="81"/>
+      <c r="H30" s="48"/>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" s="36"/>
       <c r="B31" s="39"/>
-      <c r="C31" s="91"/>
+      <c r="C31" s="81"/>
       <c r="D31" s="39"/>
-      <c r="E31" s="91"/>
+      <c r="E31" s="81"/>
       <c r="F31" s="39"/>
-      <c r="G31" s="91"/>
-      <c r="H31" s="39"/>
-      <c r="I31" s="91"/>
-      <c r="J31" s="39"/>
-      <c r="K31" s="80"/>
-      <c r="L31" s="48"/>
-    </row>
-    <row r="32" spans="1:12">
+      <c r="G31" s="81"/>
+      <c r="H31" s="48"/>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" s="53">
         <v>0.625</v>
       </c>
       <c r="B32" s="39"/>
-      <c r="C32" s="91"/>
+      <c r="C32" s="81"/>
       <c r="D32" s="39"/>
-      <c r="E32" s="91"/>
+      <c r="E32" s="81"/>
       <c r="F32" s="39"/>
-      <c r="G32" s="91"/>
-      <c r="H32" s="39"/>
-      <c r="I32" s="91"/>
-      <c r="J32" s="39"/>
-      <c r="K32" s="80"/>
-      <c r="L32" s="48"/>
-    </row>
-    <row r="33" spans="1:12">
+      <c r="G32" s="81"/>
+      <c r="H32" s="48"/>
+    </row>
+    <row r="33" spans="1:8">
       <c r="A33" s="49"/>
       <c r="B33" s="39"/>
-      <c r="C33" s="91"/>
+      <c r="C33" s="81"/>
       <c r="D33" s="39"/>
-      <c r="E33" s="91"/>
+      <c r="E33" s="81"/>
       <c r="F33" s="39"/>
-      <c r="G33" s="91"/>
-      <c r="H33" s="39"/>
-      <c r="I33" s="91"/>
-      <c r="J33" s="39"/>
-      <c r="K33" s="80"/>
-      <c r="L33" s="48"/>
-    </row>
-    <row r="34" spans="1:12">
+      <c r="G33" s="81"/>
+      <c r="H33" s="48"/>
+    </row>
+    <row r="34" spans="1:8">
       <c r="A34" s="49"/>
       <c r="B34" s="39"/>
-      <c r="C34" s="91"/>
+      <c r="C34" s="81"/>
       <c r="D34" s="39"/>
-      <c r="E34" s="91"/>
+      <c r="E34" s="81"/>
       <c r="F34" s="39"/>
-      <c r="G34" s="91"/>
-      <c r="H34" s="39"/>
-      <c r="I34" s="91"/>
-      <c r="J34" s="39"/>
-      <c r="K34" s="80"/>
-      <c r="L34" s="48"/>
-    </row>
-    <row r="35" spans="1:12">
+      <c r="G34" s="81"/>
+      <c r="H34" s="48"/>
+    </row>
+    <row r="35" spans="1:8">
       <c r="A35" s="36"/>
       <c r="B35" s="39"/>
-      <c r="C35" s="91"/>
+      <c r="C35" s="81"/>
       <c r="D35" s="39"/>
-      <c r="E35" s="91"/>
+      <c r="E35" s="81"/>
       <c r="F35" s="39"/>
-      <c r="G35" s="91"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="91"/>
-      <c r="J35" s="39"/>
-      <c r="K35" s="80"/>
-      <c r="L35" s="48"/>
-    </row>
-    <row r="36" spans="1:12">
+      <c r="G35" s="81"/>
+      <c r="H35" s="48"/>
+    </row>
+    <row r="36" spans="1:8">
       <c r="A36" s="34">
         <v>0.66666666666666663</v>
       </c>
       <c r="B36" s="39"/>
-      <c r="C36" s="91"/>
+      <c r="C36" s="81"/>
       <c r="D36" s="39"/>
-      <c r="E36" s="91"/>
+      <c r="E36" s="81"/>
       <c r="F36" s="39"/>
-      <c r="G36" s="91"/>
-      <c r="H36" s="39"/>
-      <c r="I36" s="91"/>
-      <c r="J36" s="39"/>
-      <c r="K36" s="80"/>
-      <c r="L36" s="48"/>
-    </row>
-    <row r="37" spans="1:12">
+      <c r="G36" s="81"/>
+      <c r="H36" s="48"/>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37" s="35"/>
       <c r="B37" s="39"/>
-      <c r="C37" s="91"/>
+      <c r="C37" s="81"/>
       <c r="D37" s="39"/>
-      <c r="E37" s="91"/>
+      <c r="E37" s="81"/>
       <c r="F37" s="39"/>
-      <c r="G37" s="91"/>
-      <c r="H37" s="39"/>
-      <c r="I37" s="91"/>
-      <c r="J37" s="39"/>
-      <c r="K37" s="80"/>
-      <c r="L37" s="48"/>
-    </row>
-    <row r="38" spans="1:12">
+      <c r="G37" s="81"/>
+      <c r="H37" s="48"/>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="35"/>
       <c r="B38" s="39"/>
-      <c r="C38" s="91"/>
+      <c r="C38" s="81"/>
       <c r="D38" s="39"/>
-      <c r="E38" s="91"/>
+      <c r="E38" s="81"/>
       <c r="F38" s="39"/>
-      <c r="G38" s="91"/>
-      <c r="H38" s="39"/>
-      <c r="I38" s="91"/>
-      <c r="J38" s="39"/>
-      <c r="K38" s="80"/>
-      <c r="L38" s="48"/>
-    </row>
-    <row r="39" spans="1:12">
+      <c r="G38" s="81"/>
+      <c r="H38" s="48"/>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="35"/>
       <c r="B39" s="39"/>
-      <c r="C39" s="91"/>
+      <c r="C39" s="81"/>
       <c r="D39" s="39"/>
-      <c r="E39" s="91"/>
+      <c r="E39" s="81"/>
       <c r="F39" s="39"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="39"/>
-      <c r="I39" s="91"/>
-      <c r="J39" s="39"/>
-      <c r="K39" s="80"/>
-      <c r="L39" s="48"/>
-    </row>
-    <row r="40" spans="1:12">
+      <c r="G39" s="81"/>
+      <c r="H39" s="48"/>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="37">
         <v>0.70833333333333337</v>
       </c>
       <c r="B40" s="39"/>
-      <c r="C40" s="91"/>
+      <c r="C40" s="81"/>
       <c r="D40" s="39"/>
-      <c r="E40" s="91"/>
-      <c r="F40" s="39"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="91"/>
-      <c r="J40" s="39"/>
-      <c r="K40" s="80"/>
-      <c r="L40" s="48"/>
-    </row>
-    <row r="41" spans="1:12">
+      <c r="E40" s="81"/>
+      <c r="F40" s="38"/>
+      <c r="G40" s="79"/>
+      <c r="H40" s="48"/>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="35"/>
       <c r="B41" s="39"/>
-      <c r="C41" s="91"/>
+      <c r="C41" s="81"/>
       <c r="D41" s="39"/>
-      <c r="E41" s="91"/>
-      <c r="F41" s="39"/>
-      <c r="G41" s="91"/>
-      <c r="H41" s="39"/>
-      <c r="I41" s="91"/>
-      <c r="J41" s="39"/>
-      <c r="K41" s="80"/>
-      <c r="L41" s="50"/>
-    </row>
-    <row r="42" spans="1:12">
+      <c r="E41" s="81"/>
+      <c r="F41" s="39">
+        <v>0.71875</v>
+      </c>
+      <c r="G41" s="113" t="s">
+        <v>141</v>
+      </c>
+      <c r="H41" s="50"/>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="39"/>
       <c r="B42" s="39"/>
-      <c r="C42" s="89"/>
+      <c r="C42" s="79"/>
       <c r="D42" s="39"/>
-      <c r="E42" s="89"/>
+      <c r="E42" s="79"/>
       <c r="F42" s="39"/>
-      <c r="G42" s="89"/>
-      <c r="H42" s="39"/>
-      <c r="I42" s="89"/>
-      <c r="J42" s="39"/>
-      <c r="K42" s="81"/>
-      <c r="L42" s="48"/>
-    </row>
-    <row r="43" spans="1:12" ht="14.25" customHeight="1">
+      <c r="G42" s="112"/>
+      <c r="H42" s="48"/>
+    </row>
+    <row r="43" spans="1:8" ht="14.25" customHeight="1">
       <c r="A43" s="38"/>
-      <c r="B43" s="82">
+      <c r="B43" s="72">
         <v>0.73958333333333337</v>
       </c>
-      <c r="C43" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="D43" s="82">
+      <c r="C43" s="73" t="s">
+        <v>79</v>
+      </c>
+      <c r="D43" s="72">
         <v>0.73958333333333337</v>
       </c>
-      <c r="E43" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="F43" s="82">
+      <c r="E43" s="73" t="s">
+        <v>79</v>
+      </c>
+      <c r="F43" s="72">
         <v>0.73958333333333337</v>
       </c>
-      <c r="G43" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="H43" s="82">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="I43" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="J43" s="82">
-        <v>0.73958333333333337</v>
-      </c>
-      <c r="K43" s="83" t="s">
-        <v>86</v>
-      </c>
-      <c r="L43" s="49"/>
-    </row>
-    <row r="44" spans="1:12" ht="15.6" thickBot="1">
+      <c r="G43" s="73" t="s">
+        <v>79</v>
+      </c>
+      <c r="H43" s="49"/>
+    </row>
+    <row r="44" spans="1:8" ht="15.6" thickBot="1">
       <c r="A44" s="6"/>
-      <c r="L44" s="20"/>
+      <c r="H44" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B2:G2"/>
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B7:C7"/>
@@ -3641,7 +3106,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A2:L13"/>
+  <dimension ref="A2:L14"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -3684,10 +3149,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="102"/>
+      <c r="C4" s="92"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -3698,16 +3163,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="103"/>
-      <c r="C5" s="103"/>
-      <c r="D5" s="103"/>
-      <c r="E5" s="103"/>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="103"/>
-      <c r="K5" s="103"/>
+      <c r="B5" s="93"/>
+      <c r="C5" s="93"/>
+      <c r="D5" s="93"/>
+      <c r="E5" s="93"/>
+      <c r="F5" s="93"/>
+      <c r="G5" s="93"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="93"/>
+      <c r="J5" s="93"/>
+      <c r="K5" s="93"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -3722,10 +3187,10 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="104" t="s">
+      <c r="D7" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="104"/>
+      <c r="E7" s="94"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
@@ -3757,60 +3222,60 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="10"/>
-      <c r="B10" s="101"/>
-      <c r="C10" s="101" t="s">
+      <c r="B10" s="91"/>
+      <c r="C10" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="101" t="s">
+      <c r="D10" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="101" t="s">
+      <c r="E10" s="91"/>
+      <c r="F10" s="91"/>
+      <c r="G10" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="105" t="s">
+      <c r="H10" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="100" t="s">
+      <c r="I10" s="90" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="100"/>
-      <c r="K10" s="100" t="s">
+      <c r="J10" s="90"/>
+      <c r="K10" s="90" t="s">
         <v>30</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="101"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="101"/>
-      <c r="H11" s="106"/>
+      <c r="B11" s="91"/>
+      <c r="C11" s="91"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="91"/>
+      <c r="F11" s="91"/>
+      <c r="G11" s="91"/>
+      <c r="H11" s="96"/>
       <c r="I11" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J11" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="101"/>
+      <c r="K11" s="91"/>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="63">
       <c r="A12" s="10"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="D12" s="99" t="s">
+        <v>136</v>
+      </c>
+      <c r="D12" s="89" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="99"/>
-      <c r="F12" s="99"/>
-      <c r="G12" s="92" t="s">
+      <c r="E12" s="89"/>
+      <c r="F12" s="89"/>
+      <c r="G12" s="82" t="s">
         <v>41</v>
       </c>
       <c r="H12" s="19"/>
@@ -3827,15 +3292,15 @@
       <c r="A13" s="10"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="D13" s="99" t="s">
-        <v>168</v>
-      </c>
-      <c r="E13" s="99"/>
-      <c r="F13" s="99"/>
-      <c r="G13" s="92" t="s">
-        <v>169</v>
+        <v>135</v>
+      </c>
+      <c r="D13" s="89" t="s">
+        <v>137</v>
+      </c>
+      <c r="E13" s="89"/>
+      <c r="F13" s="89"/>
+      <c r="G13" s="82" t="s">
+        <v>138</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13" s="46" t="s">
@@ -3847,9 +3312,33 @@
       <c r="K13" s="19"/>
       <c r="L13" s="10"/>
     </row>
+    <row r="14" spans="1:12" ht="25.2">
+      <c r="A14" s="10"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19" t="s">
+        <v>141</v>
+      </c>
+      <c r="D14" s="89" t="s">
+        <v>142</v>
+      </c>
+      <c r="E14" s="89"/>
+      <c r="F14" s="89"/>
+      <c r="G14" s="82" t="s">
+        <v>138</v>
+      </c>
+      <c r="H14" s="19"/>
+      <c r="I14" s="46" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="52">
+        <v>1.0416666666666666E-2</v>
+      </c>
+      <c r="K14" s="19"/>
+      <c r="L14" s="10"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="D13:F13"/>
+  <mergeCells count="13">
+    <mergeCell ref="D14:F14"/>
     <mergeCell ref="K10:K11"/>
     <mergeCell ref="D12:F12"/>
     <mergeCell ref="B4:C4"/>
@@ -3861,6 +3350,7 @@
     <mergeCell ref="G10:G11"/>
     <mergeCell ref="H10:H11"/>
     <mergeCell ref="I10:J10"/>
+    <mergeCell ref="D13:F13"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3873,7 +3363,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H12:H13</xm:sqref>
+          <xm:sqref>H12:H14</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3883,7 +3373,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N59"/>
+  <dimension ref="A2:N50"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -3933,12 +3423,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="92" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
+      <c r="C4" s="92"/>
+      <c r="D4" s="92"/>
+      <c r="E4" s="92"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -3949,16 +3439,16 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="118"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="118"/>
-      <c r="H5" s="118"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="118"/>
-      <c r="K5" s="118"/>
+      <c r="B5" s="111"/>
+      <c r="C5" s="111"/>
+      <c r="D5" s="111"/>
+      <c r="E5" s="111"/>
+      <c r="F5" s="111"/>
+      <c r="G5" s="111"/>
+      <c r="H5" s="111"/>
+      <c r="I5" s="111"/>
+      <c r="J5" s="111"/>
+      <c r="K5" s="111"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
@@ -3978,10 +3468,10 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="104" t="s">
+      <c r="D7" s="94" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="104"/>
+      <c r="E7" s="94"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
@@ -4063,10 +3553,10 @@
     </row>
     <row r="11" spans="1:14">
       <c r="B11" s="31" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="C11" s="33" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="D11" s="42" t="s">
         <v>19</v>
@@ -4085,28 +3575,28 @@
     </row>
     <row r="13" spans="1:14" ht="24" customHeight="1">
       <c r="A13" s="10"/>
-      <c r="B13" s="101" t="s">
+      <c r="B13" s="91" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="101" t="s">
+      <c r="C13" s="91" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="101" t="s">
+      <c r="D13" s="91" t="s">
         <v>8</v>
       </c>
-      <c r="E13" s="101"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="101" t="s">
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91" t="s">
         <v>9</v>
       </c>
-      <c r="H13" s="100" t="s">
+      <c r="H13" s="90" t="s">
         <v>23</v>
       </c>
-      <c r="I13" s="116" t="s">
+      <c r="I13" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="J13" s="117"/>
-      <c r="K13" s="100" t="s">
+      <c r="J13" s="110"/>
+      <c r="K13" s="90" t="s">
         <v>32</v>
       </c>
       <c r="L13" s="6"/>
@@ -4115,27 +3605,27 @@
     </row>
     <row r="14" spans="1:14">
       <c r="A14" s="10"/>
-      <c r="B14" s="101"/>
-      <c r="C14" s="101"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="101"/>
-      <c r="G14" s="101"/>
-      <c r="H14" s="100"/>
+      <c r="B14" s="91"/>
+      <c r="C14" s="91"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="91"/>
+      <c r="F14" s="91"/>
+      <c r="G14" s="91"/>
+      <c r="H14" s="90"/>
       <c r="I14" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J14" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K14" s="101"/>
+      <c r="K14" s="91"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
     </row>
     <row r="15" spans="1:14" ht="63">
       <c r="A15" s="10"/>
-      <c r="B15" s="84" t="str">
+      <c r="B15" s="74" t="str">
         <f>master!B4</f>
         <v>導入</v>
       </c>
@@ -4143,13 +3633,13 @@
         <f>master!C4</f>
         <v>はじめに　｜　“Be a social designer”とは</v>
       </c>
-      <c r="D15" s="107" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15" s="108"/>
-      <c r="F15" s="109"/>
+      <c r="D15" s="100" t="s">
+        <v>101</v>
+      </c>
+      <c r="E15" s="101"/>
+      <c r="F15" s="102"/>
       <c r="G15" s="47" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="45" t="s">
@@ -4165,7 +3655,7 @@
     </row>
     <row r="16" spans="1:14" ht="63">
       <c r="A16" s="10"/>
-      <c r="B16" s="119" t="str">
+      <c r="B16" s="97" t="str">
         <f>master!B5</f>
         <v>企画提案のステップ</v>
       </c>
@@ -4173,13 +3663,13 @@
         <f>master!C5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="D16" s="107" t="s">
-        <v>118</v>
-      </c>
-      <c r="E16" s="108"/>
-      <c r="F16" s="109"/>
+      <c r="D16" s="100" t="s">
+        <v>102</v>
+      </c>
+      <c r="E16" s="101"/>
+      <c r="F16" s="102"/>
       <c r="G16" s="47" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="45" t="s">
@@ -4195,18 +3685,18 @@
     </row>
     <row r="17" spans="1:14" ht="163.80000000000001">
       <c r="A17" s="11"/>
-      <c r="B17" s="120"/>
+      <c r="B17" s="98"/>
       <c r="C17" s="47" t="str">
         <f>master!C6</f>
         <v>STEP①-1　日常の不便を考える</v>
       </c>
-      <c r="D17" s="107" t="s">
-        <v>165</v>
-      </c>
-      <c r="E17" s="108"/>
-      <c r="F17" s="109"/>
+      <c r="D17" s="100" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="101"/>
+      <c r="F17" s="102"/>
       <c r="G17" s="47" t="s">
-        <v>164</v>
+        <v>133</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="45" t="s">
@@ -4222,16 +3712,16 @@
     </row>
     <row r="18" spans="1:14" ht="37.799999999999997">
       <c r="A18" s="11"/>
-      <c r="B18" s="120"/>
+      <c r="B18" s="98"/>
       <c r="C18" s="47" t="str">
         <f>master!C7</f>
         <v>STEP①-2　課題の深掘り</v>
       </c>
-      <c r="D18" s="107" t="s">
-        <v>119</v>
-      </c>
-      <c r="E18" s="108"/>
-      <c r="F18" s="109"/>
+      <c r="D18" s="100" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="101"/>
+      <c r="F18" s="102"/>
       <c r="G18" s="47" t="s">
         <v>36</v>
       </c>
@@ -4249,16 +3739,16 @@
     </row>
     <row r="19" spans="1:14" ht="151.19999999999999">
       <c r="A19" s="11"/>
-      <c r="B19" s="120"/>
+      <c r="B19" s="98"/>
       <c r="C19" s="47" t="str">
         <f>master!C8</f>
         <v>STEP①-3　ITアイデアへ落とし込む</v>
       </c>
-      <c r="D19" s="107" t="s">
-        <v>120</v>
-      </c>
-      <c r="E19" s="108"/>
-      <c r="F19" s="109"/>
+      <c r="D19" s="100" t="s">
+        <v>104</v>
+      </c>
+      <c r="E19" s="101"/>
+      <c r="F19" s="102"/>
       <c r="G19" s="47" t="s">
         <v>43</v>
       </c>
@@ -4276,16 +3766,16 @@
     </row>
     <row r="20" spans="1:14" ht="252">
       <c r="A20" s="11"/>
-      <c r="B20" s="120"/>
+      <c r="B20" s="98"/>
       <c r="C20" s="47" t="str">
         <f>master!C9</f>
         <v>STEP②-1 創出したアイデアに関する調査・確認</v>
       </c>
-      <c r="D20" s="107" t="s">
-        <v>121</v>
-      </c>
-      <c r="E20" s="108"/>
-      <c r="F20" s="109"/>
+      <c r="D20" s="100" t="s">
+        <v>105</v>
+      </c>
+      <c r="E20" s="101"/>
+      <c r="F20" s="102"/>
       <c r="G20" s="47" t="s">
         <v>45</v>
       </c>
@@ -4303,16 +3793,16 @@
     </row>
     <row r="21" spans="1:14" ht="126">
       <c r="A21" s="11"/>
-      <c r="B21" s="120"/>
+      <c r="B21" s="98"/>
       <c r="C21" s="47" t="str">
         <f>master!C10</f>
         <v>STEP②-2 環境分析</v>
       </c>
-      <c r="D21" s="107" t="s">
-        <v>122</v>
-      </c>
-      <c r="E21" s="108"/>
-      <c r="F21" s="109"/>
+      <c r="D21" s="100" t="s">
+        <v>106</v>
+      </c>
+      <c r="E21" s="101"/>
+      <c r="F21" s="102"/>
       <c r="G21" s="47" t="s">
         <v>44</v>
       </c>
@@ -4330,18 +3820,18 @@
     </row>
     <row r="22" spans="1:14" ht="63">
       <c r="A22" s="11"/>
-      <c r="B22" s="120"/>
+      <c r="B22" s="98"/>
       <c r="C22" s="47" t="str">
         <f>master!C11</f>
         <v>（参考）PEST分析</v>
       </c>
-      <c r="D22" s="107" t="s">
-        <v>123</v>
-      </c>
-      <c r="E22" s="108"/>
-      <c r="F22" s="109"/>
+      <c r="D22" s="100" t="s">
+        <v>107</v>
+      </c>
+      <c r="E22" s="101"/>
+      <c r="F22" s="102"/>
       <c r="G22" s="47" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="45" t="s">
@@ -4357,16 +3847,16 @@
     </row>
     <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="120"/>
+      <c r="B23" s="98"/>
       <c r="C23" s="47" t="str">
         <f>master!C12</f>
         <v>（参考） 3C分析</v>
       </c>
-      <c r="D23" s="107" t="s">
-        <v>124</v>
-      </c>
-      <c r="E23" s="108"/>
-      <c r="F23" s="109"/>
+      <c r="D23" s="100" t="s">
+        <v>108</v>
+      </c>
+      <c r="E23" s="101"/>
+      <c r="F23" s="102"/>
       <c r="G23" s="47" t="s">
         <v>37</v>
       </c>
@@ -4384,16 +3874,16 @@
     </row>
     <row r="24" spans="1:14" ht="75.599999999999994">
       <c r="A24" s="11"/>
-      <c r="B24" s="120"/>
+      <c r="B24" s="98"/>
       <c r="C24" s="47" t="str">
         <f>master!C13</f>
         <v>（参考） SWOT分析</v>
       </c>
-      <c r="D24" s="107" t="s">
-        <v>125</v>
-      </c>
-      <c r="E24" s="108"/>
-      <c r="F24" s="109"/>
+      <c r="D24" s="100" t="s">
+        <v>109</v>
+      </c>
+      <c r="E24" s="101"/>
+      <c r="F24" s="102"/>
       <c r="G24" s="47" t="s">
         <v>37</v>
       </c>
@@ -4411,16 +3901,16 @@
     </row>
     <row r="25" spans="1:14" ht="113.4">
       <c r="A25" s="11"/>
-      <c r="B25" s="120"/>
+      <c r="B25" s="98"/>
       <c r="C25" s="47" t="str">
         <f>master!C14</f>
         <v>STEP③-1 提案書作成</v>
       </c>
-      <c r="D25" s="107" t="s">
-        <v>126</v>
-      </c>
-      <c r="E25" s="108"/>
-      <c r="F25" s="109"/>
+      <c r="D25" s="100" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="101"/>
+      <c r="F25" s="102"/>
       <c r="G25" s="47" t="s">
         <v>38</v>
       </c>
@@ -4438,16 +3928,16 @@
     </row>
     <row r="26" spans="1:14" ht="88.2">
       <c r="A26" s="11"/>
-      <c r="B26" s="120"/>
+      <c r="B26" s="98"/>
       <c r="C26" s="47" t="str">
         <f>master!C15</f>
         <v>STEP③-2 プロトタイプ作成</v>
       </c>
-      <c r="D26" s="107" t="s">
-        <v>127</v>
-      </c>
-      <c r="E26" s="108"/>
-      <c r="F26" s="109"/>
+      <c r="D26" s="100" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" s="101"/>
+      <c r="F26" s="102"/>
       <c r="G26" s="47" t="s">
         <v>39</v>
       </c>
@@ -4465,16 +3955,16 @@
     </row>
     <row r="27" spans="1:14" ht="113.4">
       <c r="A27" s="11"/>
-      <c r="B27" s="121"/>
+      <c r="B27" s="99"/>
       <c r="C27" s="47" t="str">
         <f>master!C16</f>
         <v>まとめ</v>
       </c>
-      <c r="D27" s="107" t="s">
-        <v>128</v>
-      </c>
-      <c r="E27" s="108"/>
-      <c r="F27" s="109"/>
+      <c r="D27" s="100" t="s">
+        <v>112</v>
+      </c>
+      <c r="E27" s="101"/>
+      <c r="F27" s="102"/>
       <c r="G27" s="47" t="s">
         <v>38</v>
       </c>
@@ -4492,7 +3982,7 @@
     </row>
     <row r="28" spans="1:14" ht="37.799999999999997">
       <c r="A28" s="11"/>
-      <c r="B28" s="119" t="str">
+      <c r="B28" s="97" t="str">
         <f>master!B18</f>
         <v>提案書のサンプルについて</v>
       </c>
@@ -4500,13 +3990,13 @@
         <f>master!C18</f>
         <v>はじめに</v>
       </c>
-      <c r="D28" s="107" t="s">
-        <v>150</v>
-      </c>
-      <c r="E28" s="108"/>
-      <c r="F28" s="109"/>
+      <c r="D28" s="100" t="s">
+        <v>131</v>
+      </c>
+      <c r="E28" s="101"/>
+      <c r="F28" s="102"/>
       <c r="G28" s="47" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="45" t="s">
@@ -4522,18 +4012,18 @@
     </row>
     <row r="29" spans="1:14" ht="25.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="120"/>
+      <c r="B29" s="98"/>
       <c r="C29" s="47" t="str">
         <f>master!C19</f>
         <v>１．サマリ</v>
       </c>
-      <c r="D29" s="107" t="s">
-        <v>129</v>
-      </c>
-      <c r="E29" s="108"/>
-      <c r="F29" s="109"/>
+      <c r="D29" s="100" t="s">
+        <v>113</v>
+      </c>
+      <c r="E29" s="101"/>
+      <c r="F29" s="102"/>
       <c r="G29" s="47" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="45" t="s">
@@ -4549,18 +4039,18 @@
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="120"/>
+      <c r="B30" s="98"/>
       <c r="C30" s="47" t="str">
         <f>master!C20</f>
         <v>２．背景</v>
       </c>
-      <c r="D30" s="107" t="s">
-        <v>147</v>
-      </c>
-      <c r="E30" s="108"/>
-      <c r="F30" s="109"/>
+      <c r="D30" s="100" t="s">
+        <v>128</v>
+      </c>
+      <c r="E30" s="101"/>
+      <c r="F30" s="102"/>
       <c r="G30" s="47" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="45" t="s">
@@ -4576,18 +4066,18 @@
     </row>
     <row r="31" spans="1:14" ht="25.2">
       <c r="A31" s="11"/>
-      <c r="B31" s="120"/>
+      <c r="B31" s="98"/>
       <c r="C31" s="47" t="str">
         <f>master!C21</f>
         <v>３．現状課題</v>
       </c>
-      <c r="D31" s="107" t="s">
-        <v>148</v>
-      </c>
-      <c r="E31" s="108"/>
-      <c r="F31" s="109"/>
+      <c r="D31" s="100" t="s">
+        <v>129</v>
+      </c>
+      <c r="E31" s="101"/>
+      <c r="F31" s="102"/>
       <c r="G31" s="47" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="45" t="s">
@@ -4603,18 +4093,18 @@
     </row>
     <row r="32" spans="1:14" ht="63">
       <c r="A32" s="11"/>
-      <c r="B32" s="120"/>
+      <c r="B32" s="98"/>
       <c r="C32" s="47" t="str">
         <f>master!C22</f>
         <v>４．業界動向・市場分析</v>
       </c>
-      <c r="D32" s="107" t="s">
-        <v>134</v>
-      </c>
-      <c r="E32" s="108"/>
-      <c r="F32" s="109"/>
+      <c r="D32" s="100" t="s">
+        <v>118</v>
+      </c>
+      <c r="E32" s="101"/>
+      <c r="F32" s="102"/>
       <c r="G32" s="47" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="45" t="s">
@@ -4630,18 +4120,18 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="120"/>
+      <c r="B33" s="98"/>
       <c r="C33" s="47" t="str">
         <f>master!C23</f>
         <v>５．市場機会</v>
       </c>
-      <c r="D33" s="107" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33" s="108"/>
-      <c r="F33" s="109"/>
+      <c r="D33" s="100" t="s">
+        <v>121</v>
+      </c>
+      <c r="E33" s="101"/>
+      <c r="F33" s="102"/>
       <c r="G33" s="47" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="45" t="s">
@@ -4657,18 +4147,18 @@
     </row>
     <row r="34" spans="1:14" ht="37.799999999999997">
       <c r="A34" s="11"/>
-      <c r="B34" s="120"/>
+      <c r="B34" s="98"/>
       <c r="C34" s="47" t="str">
         <f>master!C24</f>
         <v>６．サービス概要</v>
       </c>
-      <c r="D34" s="107" t="s">
-        <v>138</v>
-      </c>
-      <c r="E34" s="108"/>
-      <c r="F34" s="109"/>
+      <c r="D34" s="100" t="s">
+        <v>122</v>
+      </c>
+      <c r="E34" s="101"/>
+      <c r="F34" s="102"/>
       <c r="G34" s="47" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="45" t="s">
@@ -4684,18 +4174,18 @@
     </row>
     <row r="35" spans="1:14" ht="63">
       <c r="A35" s="11"/>
-      <c r="B35" s="120"/>
+      <c r="B35" s="98"/>
       <c r="C35" s="47" t="str">
         <f>master!C25</f>
         <v>７．利用者体験イメージ</v>
       </c>
-      <c r="D35" s="107" t="s">
-        <v>139</v>
-      </c>
-      <c r="E35" s="108"/>
-      <c r="F35" s="109"/>
+      <c r="D35" s="100" t="s">
+        <v>123</v>
+      </c>
+      <c r="E35" s="101"/>
+      <c r="F35" s="102"/>
       <c r="G35" s="47" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="45" t="s">
@@ -4711,18 +4201,18 @@
     </row>
     <row r="36" spans="1:14" ht="25.2">
       <c r="A36" s="11"/>
-      <c r="B36" s="120"/>
+      <c r="B36" s="98"/>
       <c r="C36" s="47" t="str">
         <f>master!C26</f>
         <v>８．事業構成</v>
       </c>
-      <c r="D36" s="107" t="s">
-        <v>130</v>
-      </c>
-      <c r="E36" s="108"/>
-      <c r="F36" s="109"/>
+      <c r="D36" s="100" t="s">
+        <v>114</v>
+      </c>
+      <c r="E36" s="101"/>
+      <c r="F36" s="102"/>
       <c r="G36" s="47" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="45" t="s">
@@ -4738,18 +4228,18 @@
     </row>
     <row r="37" spans="1:14" ht="37.799999999999997">
       <c r="A37" s="11"/>
-      <c r="B37" s="120"/>
+      <c r="B37" s="98"/>
       <c r="C37" s="47" t="str">
         <f>master!C27</f>
         <v>９．提供価値</v>
       </c>
-      <c r="D37" s="107" t="s">
-        <v>140</v>
-      </c>
-      <c r="E37" s="108"/>
-      <c r="F37" s="109"/>
+      <c r="D37" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="E37" s="101"/>
+      <c r="F37" s="102"/>
       <c r="G37" s="47" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="45" t="s">
@@ -4765,18 +4255,18 @@
     </row>
     <row r="38" spans="1:14" ht="63">
       <c r="A38" s="11"/>
-      <c r="B38" s="120"/>
+      <c r="B38" s="98"/>
       <c r="C38" s="47" t="str">
         <f>master!C28</f>
         <v>１０．収益モデル</v>
       </c>
-      <c r="D38" s="107" t="s">
-        <v>133</v>
-      </c>
-      <c r="E38" s="108"/>
-      <c r="F38" s="109"/>
+      <c r="D38" s="100" t="s">
+        <v>117</v>
+      </c>
+      <c r="E38" s="101"/>
+      <c r="F38" s="102"/>
       <c r="G38" s="47" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="45" t="s">
@@ -4792,18 +4282,18 @@
     </row>
     <row r="39" spans="1:14" ht="63">
       <c r="A39" s="11"/>
-      <c r="B39" s="120"/>
+      <c r="B39" s="98"/>
       <c r="C39" s="47" t="str">
         <f>master!C29</f>
         <v>１１．リスク・課題</v>
       </c>
-      <c r="D39" s="107" t="s">
-        <v>141</v>
-      </c>
-      <c r="E39" s="108"/>
-      <c r="F39" s="109"/>
+      <c r="D39" s="100" t="s">
+        <v>125</v>
+      </c>
+      <c r="E39" s="101"/>
+      <c r="F39" s="102"/>
       <c r="G39" s="47" t="s">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="45" t="s">
@@ -4819,18 +4309,18 @@
     </row>
     <row r="40" spans="1:14" ht="37.799999999999997">
       <c r="A40" s="11"/>
-      <c r="B40" s="121"/>
+      <c r="B40" s="99"/>
       <c r="C40" s="47" t="str">
         <f>master!C30</f>
         <v>１２．今後の展望</v>
       </c>
-      <c r="D40" s="107" t="s">
-        <v>142</v>
-      </c>
-      <c r="E40" s="108"/>
-      <c r="F40" s="109"/>
+      <c r="D40" s="100" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" s="101"/>
+      <c r="F40" s="102"/>
       <c r="G40" s="47" t="s">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="H40" s="12"/>
       <c r="I40" s="45" t="s">
@@ -4846,578 +4336,288 @@
     </row>
     <row r="41" spans="1:14" ht="113.4">
       <c r="A41" s="11"/>
-      <c r="B41" s="125" t="str">
+      <c r="B41" s="106" t="str">
         <f>master!B32</f>
-        <v>個人演習</v>
-      </c>
-      <c r="C41" s="66" t="str">
+        <v>個人演習1</v>
+      </c>
+      <c r="C41" s="65" t="str">
         <f>master!C32</f>
         <v>演習内容の説明</v>
       </c>
-      <c r="D41" s="110" t="s">
-        <v>111</v>
-      </c>
-      <c r="E41" s="111"/>
-      <c r="F41" s="112"/>
-      <c r="G41" s="66" t="s">
-        <v>95</v>
-      </c>
-      <c r="H41" s="67"/>
-      <c r="I41" s="68" t="s">
+      <c r="D41" s="103" t="s">
+        <v>99</v>
+      </c>
+      <c r="E41" s="104"/>
+      <c r="F41" s="105"/>
+      <c r="G41" s="65" t="s">
+        <v>86</v>
+      </c>
+      <c r="H41" s="66"/>
+      <c r="I41" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="J41" s="69">
+      <c r="J41" s="68">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K41" s="70"/>
+      <c r="K41" s="69"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
     <row r="42" spans="1:14" ht="201.6">
       <c r="A42" s="11"/>
-      <c r="B42" s="126"/>
-      <c r="C42" s="66" t="str">
+      <c r="B42" s="107"/>
+      <c r="C42" s="65" t="str">
         <f>master!C33</f>
         <v>演習成果物の説明</v>
       </c>
-      <c r="D42" s="110" t="s">
-        <v>143</v>
-      </c>
-      <c r="E42" s="111"/>
-      <c r="F42" s="112"/>
-      <c r="G42" s="66" t="s">
-        <v>97</v>
-      </c>
-      <c r="H42" s="67"/>
-      <c r="I42" s="68" t="s">
+      <c r="D42" s="103" t="s">
+        <v>127</v>
+      </c>
+      <c r="E42" s="104"/>
+      <c r="F42" s="105"/>
+      <c r="G42" s="65" t="s">
+        <v>88</v>
+      </c>
+      <c r="H42" s="66"/>
+      <c r="I42" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="J42" s="69">
+      <c r="J42" s="68">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K42" s="70"/>
+      <c r="K42" s="69"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
     </row>
     <row r="43" spans="1:14" ht="176.4">
       <c r="A43" s="11"/>
-      <c r="B43" s="126"/>
-      <c r="C43" s="66" t="str">
+      <c r="B43" s="107"/>
+      <c r="C43" s="65" t="str">
         <f>master!C34</f>
         <v>サービスの検討</v>
       </c>
-      <c r="D43" s="110" t="s">
-        <v>106</v>
-      </c>
-      <c r="E43" s="111"/>
-      <c r="F43" s="112"/>
-      <c r="G43" s="66" t="s">
-        <v>99</v>
-      </c>
-      <c r="H43" s="67"/>
-      <c r="I43" s="68" t="s">
+      <c r="D43" s="103" t="s">
+        <v>97</v>
+      </c>
+      <c r="E43" s="104"/>
+      <c r="F43" s="105"/>
+      <c r="G43" s="65" t="s">
+        <v>90</v>
+      </c>
+      <c r="H43" s="66"/>
+      <c r="I43" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="J43" s="69">
+      <c r="J43" s="68">
         <v>1.3888888888888888E-2</v>
       </c>
-      <c r="K43" s="70"/>
+      <c r="K43" s="69"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
     <row r="44" spans="1:14" ht="138.6">
       <c r="A44" s="11"/>
-      <c r="B44" s="126"/>
-      <c r="C44" s="66" t="str">
+      <c r="B44" s="107"/>
+      <c r="C44" s="65" t="str">
         <f>master!C35</f>
         <v>サービスのブラッシュアップ</v>
       </c>
-      <c r="D44" s="110" t="s">
-        <v>105</v>
-      </c>
-      <c r="E44" s="111"/>
-      <c r="F44" s="112"/>
-      <c r="G44" s="66" t="s">
-        <v>101</v>
-      </c>
-      <c r="H44" s="67"/>
-      <c r="I44" s="68" t="s">
+      <c r="D44" s="103" t="s">
+        <v>96</v>
+      </c>
+      <c r="E44" s="104"/>
+      <c r="F44" s="105"/>
+      <c r="G44" s="65" t="s">
+        <v>92</v>
+      </c>
+      <c r="H44" s="66"/>
+      <c r="I44" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="J44" s="69">
+      <c r="J44" s="68">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K44" s="70"/>
+      <c r="K44" s="69"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
     <row r="45" spans="1:14" ht="63">
       <c r="A45" s="11"/>
-      <c r="B45" s="126"/>
-      <c r="C45" s="66" t="str">
+      <c r="B45" s="107"/>
+      <c r="C45" s="65" t="str">
         <f>master!C36</f>
         <v>サービスの決定</v>
       </c>
-      <c r="D45" s="110" t="s">
-        <v>104</v>
-      </c>
-      <c r="E45" s="111"/>
-      <c r="F45" s="112"/>
-      <c r="G45" s="66" t="s">
-        <v>98</v>
-      </c>
-      <c r="H45" s="67"/>
-      <c r="I45" s="68" t="s">
+      <c r="D45" s="103" t="s">
+        <v>95</v>
+      </c>
+      <c r="E45" s="104"/>
+      <c r="F45" s="105"/>
+      <c r="G45" s="65" t="s">
+        <v>89</v>
+      </c>
+      <c r="H45" s="66"/>
+      <c r="I45" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="J45" s="69">
+      <c r="J45" s="68">
         <v>2.0833333333333332E-2</v>
       </c>
-      <c r="K45" s="70"/>
+      <c r="K45" s="69"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
     <row r="46" spans="1:14" ht="138.6">
       <c r="A46" s="11"/>
-      <c r="B46" s="126"/>
-      <c r="C46" s="66" t="str">
+      <c r="B46" s="107"/>
+      <c r="C46" s="65" t="str">
         <f>master!C37</f>
         <v>成果物の作成</v>
       </c>
-      <c r="D46" s="110" t="s">
-        <v>103</v>
-      </c>
-      <c r="E46" s="111"/>
-      <c r="F46" s="112"/>
-      <c r="G46" s="66" t="s">
-        <v>101</v>
-      </c>
-      <c r="H46" s="67"/>
-      <c r="I46" s="68" t="s">
+      <c r="D46" s="103" t="s">
+        <v>94</v>
+      </c>
+      <c r="E46" s="104"/>
+      <c r="F46" s="105"/>
+      <c r="G46" s="65" t="s">
+        <v>92</v>
+      </c>
+      <c r="H46" s="66"/>
+      <c r="I46" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="J46" s="69" t="s">
-        <v>135</v>
-      </c>
-      <c r="K46" s="70"/>
+      <c r="J46" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="K46" s="69"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
     <row r="47" spans="1:14" ht="25.2">
       <c r="A47" s="11"/>
-      <c r="B47" s="127"/>
-      <c r="C47" s="66" t="str">
+      <c r="B47" s="108"/>
+      <c r="C47" s="65" t="str">
         <f>master!C38</f>
         <v>成果物の提出</v>
       </c>
-      <c r="D47" s="110" t="s">
-        <v>102</v>
-      </c>
-      <c r="E47" s="111"/>
-      <c r="F47" s="112"/>
-      <c r="G47" s="66" t="s">
-        <v>107</v>
-      </c>
-      <c r="H47" s="67"/>
-      <c r="I47" s="68" t="s">
+      <c r="D47" s="103" t="s">
+        <v>93</v>
+      </c>
+      <c r="E47" s="104"/>
+      <c r="F47" s="105"/>
+      <c r="G47" s="65" t="s">
+        <v>98</v>
+      </c>
+      <c r="H47" s="66"/>
+      <c r="I47" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="69" t="s">
-        <v>135</v>
-      </c>
-      <c r="K47" s="70"/>
+      <c r="J47" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="K47" s="69"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="1:14" ht="100.8">
+    <row r="48" spans="1:14" ht="88.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="125" t="str">
+      <c r="B48" s="106" t="str">
         <f>master!B40</f>
-        <v>チーム演習</v>
-      </c>
-      <c r="C48" s="66" t="str">
+        <v>個人演習2</v>
+      </c>
+      <c r="C48" s="65" t="str">
         <f>master!C40</f>
         <v>演習内容の説明</v>
       </c>
-      <c r="D48" s="110" t="s">
-        <v>110</v>
-      </c>
-      <c r="E48" s="111"/>
-      <c r="F48" s="112"/>
-      <c r="G48" s="66" t="s">
-        <v>151</v>
-      </c>
-      <c r="H48" s="67"/>
-      <c r="I48" s="68" t="s">
+      <c r="D48" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="E48" s="104"/>
+      <c r="F48" s="105"/>
+      <c r="G48" s="65" t="s">
+        <v>145</v>
+      </c>
+      <c r="H48" s="66"/>
+      <c r="I48" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="J48" s="69">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K48" s="70"/>
+      <c r="J48" s="68">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K48" s="69"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
-    <row r="49" spans="1:14" ht="201.6">
+    <row r="49" spans="1:14" ht="88.2">
       <c r="A49" s="11"/>
-      <c r="B49" s="126"/>
-      <c r="C49" s="66" t="str">
+      <c r="B49" s="107"/>
+      <c r="C49" s="65" t="str">
         <f>master!C41</f>
-        <v>演習成果物の説明</v>
-      </c>
-      <c r="D49" s="110" t="s">
-        <v>144</v>
-      </c>
-      <c r="E49" s="111"/>
-      <c r="F49" s="112"/>
-      <c r="G49" s="66" t="s">
-        <v>152</v>
-      </c>
-      <c r="H49" s="67"/>
-      <c r="I49" s="68" t="s">
+        <v>個人提案の実施</v>
+      </c>
+      <c r="D49" s="103" t="s">
+        <v>149</v>
+      </c>
+      <c r="E49" s="104"/>
+      <c r="F49" s="105"/>
+      <c r="G49" s="65" t="s">
+        <v>145</v>
+      </c>
+      <c r="H49" s="66"/>
+      <c r="I49" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="J49" s="69">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K49" s="70"/>
+      <c r="J49" s="68">
+        <v>6.25E-2</v>
+      </c>
+      <c r="K49" s="69"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
-    <row r="50" spans="1:14" ht="37.799999999999997">
+    <row r="50" spans="1:14" ht="25.2">
       <c r="A50" s="11"/>
-      <c r="B50" s="126"/>
-      <c r="C50" s="66" t="str">
+      <c r="B50" s="108"/>
+      <c r="C50" s="65" t="str">
         <f>master!C42</f>
-        <v>【参考】最終発表時の評価基準</v>
-      </c>
-      <c r="D50" s="110" t="s">
-        <v>145</v>
-      </c>
-      <c r="E50" s="111"/>
-      <c r="F50" s="112"/>
-      <c r="G50" s="66" t="s">
-        <v>153</v>
-      </c>
-      <c r="H50" s="67"/>
-      <c r="I50" s="68" t="s">
+        <v>提案内容のブラッシュアップ</v>
+      </c>
+      <c r="D50" s="103" t="s">
+        <v>148</v>
+      </c>
+      <c r="E50" s="104"/>
+      <c r="F50" s="105"/>
+      <c r="G50" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="H50" s="66"/>
+      <c r="I50" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="J50" s="69">
-        <v>1.3888888888888889E-3</v>
-      </c>
-      <c r="K50" s="70"/>
+      <c r="J50" s="68" t="s">
+        <v>119</v>
+      </c>
+      <c r="K50" s="69"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
-    <row r="51" spans="1:14" ht="113.4">
-      <c r="A51" s="11"/>
-      <c r="B51" s="126"/>
-      <c r="C51" s="66" t="str">
-        <f>master!C43</f>
-        <v>サービスの提案</v>
-      </c>
-      <c r="D51" s="110" t="s">
-        <v>161</v>
-      </c>
-      <c r="E51" s="111"/>
-      <c r="F51" s="112"/>
-      <c r="G51" s="66" t="s">
-        <v>154</v>
-      </c>
-      <c r="H51" s="67"/>
-      <c r="I51" s="68" t="s">
-        <v>24</v>
-      </c>
-      <c r="J51" s="69">
-        <v>4.1666666666666664E-2</v>
-      </c>
-      <c r="K51" s="70"/>
-      <c r="L51" s="6"/>
-      <c r="M51" s="6"/>
-      <c r="N51" s="6"/>
-    </row>
-    <row r="52" spans="1:14" ht="100.8">
-      <c r="A52" s="11"/>
-      <c r="B52" s="126"/>
-      <c r="C52" s="66" t="str">
-        <f>master!C44</f>
-        <v>サービスの決定（チーム）</v>
-      </c>
-      <c r="D52" s="110" t="s">
-        <v>146</v>
-      </c>
-      <c r="E52" s="111"/>
-      <c r="F52" s="112"/>
-      <c r="G52" s="66" t="s">
-        <v>151</v>
-      </c>
-      <c r="H52" s="67"/>
-      <c r="I52" s="68" t="s">
-        <v>24</v>
-      </c>
-      <c r="J52" s="69" t="s">
-        <v>135</v>
-      </c>
-      <c r="K52" s="70"/>
-      <c r="L52" s="6"/>
-      <c r="M52" s="6"/>
-      <c r="N52" s="6"/>
-    </row>
-    <row r="53" spans="1:14" ht="113.4">
-      <c r="A53" s="11"/>
-      <c r="B53" s="126"/>
-      <c r="C53" s="66" t="str">
-        <f>master!C45</f>
-        <v>成果物の作成</v>
-      </c>
-      <c r="D53" s="110" t="s">
-        <v>112</v>
-      </c>
-      <c r="E53" s="111"/>
-      <c r="F53" s="112"/>
-      <c r="G53" s="66" t="s">
-        <v>154</v>
-      </c>
-      <c r="H53" s="67"/>
-      <c r="I53" s="68" t="s">
-        <v>24</v>
-      </c>
-      <c r="J53" s="69" t="s">
-        <v>135</v>
-      </c>
-      <c r="K53" s="70"/>
-      <c r="L53" s="6"/>
-      <c r="M53" s="6"/>
-      <c r="N53" s="6"/>
-    </row>
-    <row r="54" spans="1:14" ht="25.2">
-      <c r="A54" s="11"/>
-      <c r="B54" s="126"/>
-      <c r="C54" s="66" t="str">
-        <f>master!C46</f>
-        <v>成果物の提出</v>
-      </c>
-      <c r="D54" s="110" t="s">
-        <v>102</v>
-      </c>
-      <c r="E54" s="111"/>
-      <c r="F54" s="112"/>
-      <c r="G54" s="66" t="s">
-        <v>155</v>
-      </c>
-      <c r="H54" s="67"/>
-      <c r="I54" s="68" t="s">
-        <v>24</v>
-      </c>
-      <c r="J54" s="69" t="s">
-        <v>135</v>
-      </c>
-      <c r="K54" s="70"/>
-      <c r="L54" s="6"/>
-      <c r="M54" s="6"/>
-      <c r="N54" s="6"/>
-    </row>
-    <row r="55" spans="1:14" ht="25.2">
-      <c r="A55" s="11"/>
-      <c r="B55" s="127"/>
-      <c r="C55" s="66" t="str">
-        <f>master!C47</f>
-        <v>提案のリハーサル</v>
-      </c>
-      <c r="D55" s="110" t="s">
-        <v>159</v>
-      </c>
-      <c r="E55" s="111"/>
-      <c r="F55" s="112"/>
-      <c r="G55" s="66" t="s">
-        <v>155</v>
-      </c>
-      <c r="H55" s="67"/>
-      <c r="I55" s="68" t="s">
-        <v>24</v>
-      </c>
-      <c r="J55" s="69" t="s">
-        <v>135</v>
-      </c>
-      <c r="K55" s="70"/>
-      <c r="L55" s="6"/>
-      <c r="M55" s="6"/>
-      <c r="N55" s="6"/>
-    </row>
-    <row r="56" spans="1:14" ht="100.8">
-      <c r="A56" s="11"/>
-      <c r="B56" s="122" t="str">
-        <f>master!B49</f>
-        <v>提案会（ブロック代表の決定）</v>
-      </c>
-      <c r="C56" s="73" t="str">
-        <f>master!C49</f>
-        <v>ブロック内発表の説明</v>
-      </c>
-      <c r="D56" s="113" t="s">
-        <v>114</v>
-      </c>
-      <c r="E56" s="114"/>
-      <c r="F56" s="115"/>
-      <c r="G56" s="73" t="s">
-        <v>156</v>
-      </c>
-      <c r="H56" s="74"/>
-      <c r="I56" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="J56" s="76">
-        <v>6.9444444444444441E-3</v>
-      </c>
-      <c r="K56" s="77"/>
-      <c r="L56" s="6"/>
-      <c r="M56" s="6"/>
-      <c r="N56" s="6"/>
-    </row>
-    <row r="57" spans="1:14" ht="113.4">
-      <c r="A57" s="11"/>
-      <c r="B57" s="123"/>
-      <c r="C57" s="73" t="str">
-        <f>master!C50</f>
-        <v>ブロック内発表の実施</v>
-      </c>
-      <c r="D57" s="113" t="s">
-        <v>162</v>
-      </c>
-      <c r="E57" s="114"/>
-      <c r="F57" s="115"/>
-      <c r="G57" s="73" t="s">
-        <v>157</v>
-      </c>
-      <c r="H57" s="74"/>
-      <c r="I57" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="J57" s="76" t="s">
-        <v>135</v>
-      </c>
-      <c r="K57" s="77"/>
-      <c r="L57" s="6"/>
-      <c r="M57" s="6"/>
-      <c r="N57" s="6"/>
-    </row>
-    <row r="58" spans="1:14" ht="25.2">
-      <c r="A58" s="11"/>
-      <c r="B58" s="124"/>
-      <c r="C58" s="73" t="str">
-        <f>master!C51</f>
-        <v>ブロック代表（選抜チーム）の決定</v>
-      </c>
-      <c r="D58" s="113" t="s">
-        <v>116</v>
-      </c>
-      <c r="E58" s="114"/>
-      <c r="F58" s="115"/>
-      <c r="G58" s="73" t="s">
-        <v>158</v>
-      </c>
-      <c r="H58" s="74"/>
-      <c r="I58" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="J58" s="76">
-        <v>1.3888888888888888E-2</v>
-      </c>
-      <c r="K58" s="77"/>
-      <c r="L58" s="6"/>
-      <c r="M58" s="6"/>
-      <c r="N58" s="6"/>
-    </row>
-    <row r="59" spans="1:14" ht="113.4">
-      <c r="A59" s="11"/>
-      <c r="B59" s="78" t="str">
-        <f>master!B52</f>
-        <v>提案会（最終）</v>
-      </c>
-      <c r="C59" s="73" t="str">
-        <f>master!C52</f>
-        <v>全体発表</v>
-      </c>
-      <c r="D59" s="113" t="s">
-        <v>163</v>
-      </c>
-      <c r="E59" s="114"/>
-      <c r="F59" s="115"/>
-      <c r="G59" s="73" t="s">
-        <v>157</v>
-      </c>
-      <c r="H59" s="74"/>
-      <c r="I59" s="75" t="s">
-        <v>24</v>
-      </c>
-      <c r="J59" s="76" t="s">
-        <v>135</v>
-      </c>
-      <c r="K59" s="77"/>
-      <c r="L59" s="6"/>
-      <c r="M59" s="6"/>
-      <c r="N59" s="6"/>
-    </row>
   </sheetData>
-  <mergeCells count="60">
-    <mergeCell ref="B16:B27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="B28:B40"/>
-    <mergeCell ref="B56:B58"/>
-    <mergeCell ref="D44:F44"/>
+  <mergeCells count="50">
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="B48:B50"/>
     <mergeCell ref="B41:B47"/>
-    <mergeCell ref="B48:B55"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D51:F51"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D53:F53"/>
     <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D59:F59"/>
     <mergeCell ref="D30:F30"/>
     <mergeCell ref="D31:F31"/>
     <mergeCell ref="D32:F32"/>
@@ -5429,8 +4629,39 @@
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="D39:F39"/>
     <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D13:F14"/>
+    <mergeCell ref="G13:G14"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="K13:K14"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B16:B27"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="B28:B40"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D43:F43"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5443,7 +4674,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H15:H59</xm:sqref>
+          <xm:sqref>H15:H50</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5453,7 +4684,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:C52"/>
+  <dimension ref="B1:C43"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
@@ -5558,69 +4789,69 @@
     </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
-        <v>136</v>
-      </c>
-      <c r="C18" s="71" t="s">
-        <v>149</v>
+        <v>120</v>
+      </c>
+      <c r="C18" s="70" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="C19" s="71" t="s">
+      <c r="C19" s="70" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="C20" s="71" t="s">
+      <c r="C20" s="70" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="C21" s="71" t="s">
+      <c r="C21" s="70" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="C22" s="71" t="s">
+      <c r="C22" s="70" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="C23" s="71" t="s">
+      <c r="C23" s="70" t="s">
         <v>68</v>
       </c>
     </row>
     <row r="24" spans="2:3">
-      <c r="C24" s="71" t="s">
+      <c r="C24" s="70" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="25" spans="2:3">
-      <c r="C25" s="72" t="s">
+      <c r="C25" s="71" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="26" spans="2:3">
-      <c r="C26" s="71" t="s">
+      <c r="C26" s="70" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="27" spans="2:3">
-      <c r="C27" s="71" t="s">
+      <c r="C27" s="70" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="28" spans="2:3">
-      <c r="C28" s="71" t="s">
+      <c r="C28" s="70" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="29" spans="2:3">
-      <c r="C29" s="71" t="s">
+      <c r="C29" s="70" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="30" spans="2:3">
-      <c r="C30" s="71" t="s">
+      <c r="C30" s="70" t="s">
         <v>75</v>
       </c>
     </row>
@@ -5630,40 +4861,40 @@
     </row>
     <row r="32" spans="2:3">
       <c r="B32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="71" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="70" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="33" spans="2:3">
-      <c r="C33" s="71" t="s">
-        <v>96</v>
+      <c r="C33" s="70" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="2:3">
-      <c r="C34" s="71" t="s">
-        <v>90</v>
+      <c r="C34" s="70" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="35" spans="2:3">
-      <c r="C35" s="71" t="s">
-        <v>100</v>
+      <c r="C35" s="70" t="s">
+        <v>91</v>
       </c>
     </row>
     <row r="36" spans="2:3">
       <c r="C36" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="C37" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="C38" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="2:3">
@@ -5672,76 +4903,24 @@
     </row>
     <row r="40" spans="2:3">
       <c r="B40" t="s">
-        <v>81</v>
-      </c>
-      <c r="C40" s="71" t="s">
-        <v>76</v>
+        <v>140</v>
+      </c>
+      <c r="C40" s="70" t="s">
+        <v>144</v>
       </c>
     </row>
     <row r="41" spans="2:3">
-      <c r="C41" s="71" t="s">
-        <v>96</v>
+      <c r="C41" s="70" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="42" spans="2:3">
-      <c r="C42" s="71" t="s">
-        <v>77</v>
+      <c r="C42" s="70" t="s">
+        <v>146</v>
       </c>
     </row>
     <row r="43" spans="2:3">
-      <c r="C43" s="71" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3">
-      <c r="C44" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3">
-      <c r="C45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="46" spans="2:3">
-      <c r="C46" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="47" spans="2:3">
-      <c r="C47" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="48" spans="2:3">
-      <c r="B48" s="64"/>
-      <c r="C48" s="64"/>
-    </row>
-    <row r="49" spans="2:3">
-      <c r="B49" t="s">
-        <v>170</v>
-      </c>
-      <c r="C49" s="71" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="50" spans="2:3">
-      <c r="C50" s="71" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="51" spans="2:3">
-      <c r="C51" s="71" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="52" spans="2:3">
-      <c r="B52" t="s">
-        <v>171</v>
-      </c>
-      <c r="C52" s="71" t="s">
-        <v>79</v>
-      </c>
+      <c r="C43" s="70"/>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>

--- a/IG/7日版/AI Native-提案演習_IG.xlsx
+++ b/IG/7日版/AI Native-提案演習_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4369A00-70B5-4A43-AD0C-6997A41DFC34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C12445E-6676-4B14-BA5E-FABBA54CAF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'スケジュール（3日）'!$A$1:$H$44</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$51</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">講義!$A$1:$L$61</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -88,7 +88,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="249" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="166">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -435,10 +435,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>【AI Native提案企画研修】個人演習説明.pptx</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>はじめに　｜　“Be a social designer”とは</t>
     <phoneticPr fontId="3"/>
   </si>
@@ -546,10 +542,6 @@
     <phoneticPr fontId="22"/>
   </si>
   <si>
-    <t>演習内容の説明</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>2 日目</t>
     <rPh sb="2" eb="3">
       <t>ニチ</t>
@@ -577,61 +569,16 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>AI-04</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">・AI-02
 </t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>サービスの検討</t>
-    <rPh sb="5" eb="7">
-      <t>ケントウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>サービスの決定</t>
-    <rPh sb="5" eb="7">
-      <t>ケッテイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>成果物の作成</t>
-    <rPh sb="0" eb="3">
-      <t>セイカブツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>サクセイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>成果物の提出</t>
-    <rPh sb="0" eb="3">
-      <t>セイカブツ</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>テイシュツ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">・AI-03
 </t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>演習成果物の説明</t>
-    <rPh sb="2" eb="5">
-      <t>セイカブツ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">・AI-03
 </t>
     <phoneticPr fontId="3"/>
@@ -644,114 +591,6 @@
   <si>
     <t xml:space="preserve">・AI-03
 </t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>サービスのブラッシュアップ</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>作成した成果物を指定の場所に納品することを説明する。</t>
-    <rPh sb="0" eb="2">
-      <t>サクセイ</t>
-    </rPh>
-    <rPh sb="4" eb="7">
-      <t>セイカブツ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="14" eb="16">
-      <t>ノウヒン</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>決定したサービスについて、企画提案書およびプロトタイプを作成することを説明する。
-■企画提案書
-　解決したい課題、ターゲットユーザー、提供価値、社会的意義、実現性、市場性などを整理し、サービスの概要をまとめること。
-■プロトタイプ
-　サービスの利用イメージや主要な画面を作成し、ユーザー体験を具体的に表現すること。
-　なお、本演習では実装の完成度ではなく、体験設計を重視する。分かりやすさ、使いやすさ、課題への理解、アイデアの納得感が伝わるように作成すること。</t>
-    <rPh sb="35" eb="37">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>チームメンバーからのフィードバックを踏まえ、サービス案をブラッシュアップすることを説明する。
-フィードバック内容を整理し、必要に応じて課題設定、ターゲットユーザー、提供価値、機能案などを見直すこと。
-ブラッシュアップ後、最終的に提案するサービスを決定する。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>サービス案をチーム内で発表し、メンバーからフィードバックを受けることを説明する。
-フィードバックでは、以下の観点を中心に意見交換を行うこと。
-・提供する価値が明確か
-・解決したい課題やターゲットユーザーが適切か
-・社会への影響や意義があるか
-・実現性や事業性に課題はないか
-・市場や競合との差別化ができているか
-フィードバックを踏まえ、サービス案をブラッシュアップする。</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">解決したい課題やターゲットユーザーを明確にし、サービス案を検討することを説明する。
-なお、サービス案の検討にあたっては、以下の観点を考慮すること。
-・提供する価値（顧客や社会にどのような価値を提供できるか）
-・社会への影響（NTT DATAとして取り組む意義があるか）
-・実現性・コスト・収益性（事業として成立するか）
-・市場・競合分析（市場機会があり、競争優位性を確保できるか）
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="Meiryo UI"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">
-【生成AI利用ルール】
-・サービスの初期アイデア創出は、生成AIを利用せず自身で考えること。
-・サービス案が作成できた後は、アイデアの検証、調査、市場分析、競合分析、ブラッシュアップを目的として生成AIを利用してよい。
-・生成AIから得た情報は鵜呑みにせず、必要に応じて根拠や情報源を確認すること。</t>
-    </r>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-03
-</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">個人演習の概要について説明する。
-■手順
-1. サービスの検討
-2. サービスをチーム内でブラッシュアップ
-3. サービスの決定
-4. 成果物の作成
-5. 成果物の提出
-</t>
-    <rPh sb="0" eb="2">
-      <t>コジン</t>
-    </rPh>
-    <rPh sb="69" eb="72">
-      <t>セイカブツ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1116,41 +955,6 @@
     </rPh>
     <rPh sb="55" eb="57">
       <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">成果物の概要について説明する。
-■成果物の種類
-　・企画提案書
-　　PowerPoint形式
-　・プロトタイプ
-　　作成したアプリケーションのソースコード一式
-　　※ルートディレクトリをそのままzip化する
-　・命名規約
-　　企画提案書　→　受講者ID_氏名_企画提案書.pptx
-　　プロトタイプ　→　受講者ID_氏名_プロトタイプ.zip
-■提出方法
-　・提出先：Teamの共有フォルダに格納してください。
-　　※全体連絡・共通＞02_AIネイティブ提案企画研修＞03_提出先＞01_個人演習
-</t>
-    <rPh sb="0" eb="3">
-      <t>セイカブツ</t>
-    </rPh>
-    <rPh sb="18" eb="21">
-      <t>セイカブツ</t>
-    </rPh>
-    <rPh sb="22" eb="24">
-      <t>シュルイ</t>
-    </rPh>
-    <rPh sb="175" eb="177">
-      <t>テイシュツ</t>
-    </rPh>
-    <rPh sb="177" eb="179">
-      <t>ホウホウ</t>
-    </rPh>
-    <rPh sb="184" eb="185">
-      <t>サキ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1226,11 +1030,6 @@
     <rPh sb="58" eb="59">
       <t>ヨ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">・AI-04
-</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1322,38 +1121,11 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>個人演習1</t>
-    <rPh sb="0" eb="2">
-      <t>コジン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>個人演習2</t>
-    <rPh sb="0" eb="2">
-      <t>コジン</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t>アンケート</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>・アンケートの説明</t>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>個人提案の実施</t>
-    <rPh sb="0" eb="2">
-      <t>コジン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ジッシ</t>
-    </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1370,83 +1142,613 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t xml:space="preserve">・AI-04
+    <t>提案の実施</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案の実施の説明</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案の実施</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案テーマの検討</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ケントウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案テーマの意見交換</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="6" eb="10">
+      <t>イケンコウカン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案内容の具体化</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>グタイカ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案テーマの調査</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウサ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
 </t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>提案内容のブラッシュアップ</t>
-    <rPh sb="0" eb="4">
-      <t>テイアンナイヨウ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t xml:space="preserve">個人演習の概要について説明する。
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案内容の具体化の流れを説明する。
+1. 解決する課題を整理する。
+2. 提案するサービスや機能を検討する。
+3. 利用者や利用シーンを整理する。
+4. 提案の効果やアピールポイントを整理する。</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>グタイカ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案テーマの調査の流れを説明する。
+1. 情報を収集する。
+2. 収集した情報を整理する。
+3. 提案テーマの実現性や有効性を確認する。</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>チョウサ</t>
+    </rPh>
+    <rPh sb="9" eb="10">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案テーマについて、企画提案書およびプロトタイプを作成することを説明する。
+■企画提案書
+　解決したい課題、ターゲットユーザー、提供価値、社会的意義、実現性、市場性などを整理し、サービスの概要をまとめること。
+■プロトタイプ
+　利用イメージや主要な画面を作成し、ユーザー体験を具体的に表現すること。
+　なお、本演習では実装の完成度ではなく、体験設計を重視する。分かりやすさ、使いやすさ、課題への理解、アイデアの納得感が伝わるように作成すること。</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提案の実施の流れについて説明する。
 ■手順
 1. 発表順の決定
 2. 提案の実施
-3. 提案内容のブラッシュアップ
+3. 提案のフィードバック
 </t>
     <rPh sb="0" eb="2">
-      <t>コジン</t>
-    </rPh>
-    <rPh sb="25" eb="27">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
       <t>ハッピョウ</t>
     </rPh>
-    <rPh sb="27" eb="28">
+    <rPh sb="28" eb="29">
       <t>ジュン</t>
     </rPh>
-    <rPh sb="29" eb="31">
+    <rPh sb="30" eb="32">
       <t>ケッテイ</t>
     </rPh>
-    <rPh sb="35" eb="37">
+    <rPh sb="36" eb="38">
       <t>テイアン</t>
     </rPh>
-    <rPh sb="38" eb="40">
+    <rPh sb="39" eb="41">
       <t>ジッシ</t>
     </rPh>
-    <rPh sb="44" eb="46">
+    <rPh sb="45" eb="47">
       <t>テイアン</t>
     </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案資料の作成</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案の改善</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提案演習の全体像について説明する。
+■手順
+1. 提案資料の作成
+2. 提案の実施
+3. 提案の改善
+</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>エンシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ゼンタイゾウ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="28" eb="30">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>サクセイ</t>
+    </rPh>
+    <rPh sb="37" eb="39">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="40" eb="42">
+      <t>ジッシ</t>
+    </rPh>
     <rPh sb="46" eb="48">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="49" eb="51">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>発表順の決定</t>
+    <rPh sb="0" eb="2">
+      <t>ハッピョウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ジュン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ケッテイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案のフィードバック</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>フィードバック内容の整理</t>
+    <rPh sb="7" eb="9">
       <t>ナイヨウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>フィードバックのを基に提案内容をブラッシュアップすることを伝える。</t>
-    <rPh sb="9" eb="10">
-      <t>モト</t>
+    <rPh sb="10" eb="12">
+      <t>セイリ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>最終発表の準備</t>
+    <rPh sb="0" eb="2">
+      <t>サイシュウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ハッピョウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ジュンビ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案演習の全体像</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>エンシュウ</t>
+    </rPh>
+    <rPh sb="5" eb="8">
+      <t>ゼンタイゾウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案演習の全体像について</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">解決したい課題やターゲットユーザーを明確にし、提案テーマを検討することを説明する。
+なお、提案テーマの検討にあたっては、以下の観点を考慮すること。
+・提供する価値（顧客や社会にどのような価値を提供できるか）
+・社会への影響（NTT DATAとして取り組む意義があるか）
+・実現性・コスト・収益性（事業として成立するか）
+・市場・競合分析（市場機会があり、競争優位性を確保できるか）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">
+【生成AI利用ルール】
+・提案テーマの創出は、生成AIを利用せず自身で考えること。
+・提案テーマが作成できた後は、検証、調査、市場分析、競合分析、改善を目的として生成AIを利用してよい。
+・生成AIから得た情報は鵜呑みにせず、必要に応じて根拠や情報源を確認すること。</t>
+    </r>
+    <rPh sb="206" eb="208">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="266" eb="268">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案テーマをチーム内で発表し、メンバーからフィードバックを受けることを説明する。
+フィードバックでは、以下の観点を中心に意見交換を行うこと。
+・提供する価値が明確か
+・解決したい課題やターゲットユーザーが適切か
+・社会への影響や意義があるか
+・実現性や事業性に課題はないか
+・市場や競合との差別化ができているか
+フィードバックを踏まえ、提案テーマを改善する。</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="176" eb="178">
+      <t>カイゼン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>チームで任意で決定して良いと伝える。</t>
+    <rPh sb="4" eb="6">
+      <t>ニンイ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ケッテイ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>ヨ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ツタ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>演習の実施</t>
+    <rPh sb="0" eb="2">
+      <t>エンシュウ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジッシ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案資料の作成</t>
+    <rPh sb="5" eb="7">
+      <t>サクセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案資料の提出</t>
+    <rPh sb="5" eb="7">
+      <t>テイシュツ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案資料の修正</t>
+    <rPh sb="5" eb="7">
+      <t>シュウセイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案資料の確認</t>
+    <rPh sb="5" eb="7">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案資料</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シリョウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案資料について</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案資料の概要について説明する。
+■提案資料の種類
+　・企画提案書
+　　PowerPoint形式
+　・プロトタイプ
+　　作成したアプリケーションのソースコード一式
+　　※ルートディレクトリをそのままzip化する
+　・命名規約
+　　企画提案書　→　受講者ID_氏名_企画提案書.pptx
+　　プロトタイプ　→　受講者ID_氏名_プロトタイプ.zip
+■提出方法
+　・提出先：XXX</t>
+    <rPh sb="24" eb="26">
+      <t>シュルイ</t>
+    </rPh>
+    <rPh sb="177" eb="179">
+      <t>テイシュツ</t>
+    </rPh>
+    <rPh sb="179" eb="181">
+      <t>ホウホウ</t>
+    </rPh>
+    <rPh sb="186" eb="187">
+      <t>サキ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案資料を指定の場所に納品することを説明する。</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バショ</t>
     </rPh>
     <rPh sb="11" eb="13">
+      <t>ノウヒン</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">提案の実施の流れについて説明する。
+■手順
+1. フィードバック内容の整理
+2. 提案資料の修正
+3. 提案資料の確認
+4. 提案資料の提出
+5. 最終発表の準備
+</t>
+    <rPh sb="0" eb="2">
       <t>テイアン</t>
     </rPh>
-    <rPh sb="13" eb="15">
+    <rPh sb="3" eb="5">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="6" eb="7">
+      <t>ナガ</t>
+    </rPh>
+    <rPh sb="33" eb="35">
       <t>ナイヨウ</t>
     </rPh>
-    <rPh sb="29" eb="30">
+    <rPh sb="36" eb="38">
+      <t>セイリ</t>
+    </rPh>
+    <rPh sb="42" eb="46">
+      <t>テイアンシリョウ</t>
+    </rPh>
+    <rPh sb="47" eb="49">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="53" eb="55">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="55" eb="57">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>カクニン</t>
+    </rPh>
+    <rPh sb="69" eb="71">
+      <t>テイシュツ</t>
+    </rPh>
+    <rPh sb="75" eb="79">
+      <t>サイシュウハッピョウ</t>
+    </rPh>
+    <rPh sb="80" eb="82">
+      <t>ジュンビ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>企画提案書とプロトタイプを用いた提案を実施することを説明する。</t>
+    <rPh sb="0" eb="5">
+      <t>キカクテイアンショ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>モチ</t>
+    </rPh>
+    <rPh sb="16" eb="18">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="19" eb="21">
+      <t>ジッシ</t>
+    </rPh>
+    <rPh sb="26" eb="28">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>改善点を中心にフィードバックすることを説明する。</t>
+    <rPh sb="0" eb="3">
+      <t>カイゼンテン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>チュウシン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>フィードバック内容を整理し、優先度を考慮して、どの内容を反映するかを決定することを説明する。</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>優先度を意識し、修正することを説明する。</t>
+    <rPh sb="0" eb="3">
+      <t>ユウセンド</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>イシキ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="58" eb="60">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="65" eb="66">
       <t>ツタ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>作成した成果物をチーム内のメンバーに提案し、フィードバックをもらうことを説明する。
-■手順
-1. 企画提案書およびプロトタイプを用いてサービスを提案する。（10分）
-2. 質疑応答（5分）
-3. 提案内容（提案書、プロトタイプ、提案の方法）に関するフィードバックを行う。（5分）</t>
-    <rPh sb="87" eb="91">
-      <t>シツギオウトウ</t>
-    </rPh>
-    <rPh sb="104" eb="107">
-      <t>テイアンショ</t>
-    </rPh>
-    <rPh sb="115" eb="117">
+    <t>修正内容がフィードバック内容を適切に反映しているかを、生成AIを活用して確認することを説明する。</t>
+    <rPh sb="0" eb="2">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="12" eb="14">
+      <t>ナイヨウ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>テキセツ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>ハンエイ</t>
+    </rPh>
+    <rPh sb="27" eb="29">
+      <t>セイセイ</t>
+    </rPh>
+    <rPh sb="32" eb="34">
+      <t>カツヨウ</t>
+    </rPh>
+    <rPh sb="36" eb="38">
+      <t>カクニン</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>【AI Native提案企画研修】提案演習の概要.pptx</t>
+    <rPh sb="17" eb="19">
       <t>テイアン</t>
     </rPh>
-    <rPh sb="118" eb="120">
-      <t>ホウホウ</t>
+    <rPh sb="19" eb="21">
+      <t>エンシュウ</t>
+    </rPh>
+    <rPh sb="22" eb="24">
+      <t>ガイヨウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1678,7 +1980,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="15">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -1850,6 +2152,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1865,7 +2198,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="114">
+  <cellXfs count="122">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2019,9 +2352,6 @@
     <xf numFmtId="20" fontId="15" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="20" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="20" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
@@ -2100,9 +2430,6 @@
     <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -2115,6 +2442,12 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2157,6 +2490,42 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
@@ -2166,47 +2535,35 @@
     <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+      <alignment vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2648,11 +3005,11 @@
       </c>
       <c r="D9" s="21"/>
       <c r="E9" s="21" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F9" s="21"/>
       <c r="G9" s="21" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" spans="1:7" ht="14.25" customHeight="1">
@@ -2662,174 +3019,180 @@
       <c r="B10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="58" t="s">
         <v>3</v>
       </c>
       <c r="D10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="E10" s="59" t="s">
+      <c r="E10" s="58" t="s">
         <v>3</v>
       </c>
       <c r="F10" s="16">
         <v>0.39583333333333331</v>
       </c>
-      <c r="G10" s="59" t="s">
+      <c r="G10" s="58" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="36"/>
-      <c r="B11" s="54">
+      <c r="B11" s="53">
         <v>0.40625</v>
       </c>
-      <c r="C11" s="57" t="str">
+      <c r="C11" s="56" t="str">
         <f>master!B4</f>
         <v>導入</v>
       </c>
-      <c r="D11" s="54">
+      <c r="D11" s="53">
         <v>0.40625</v>
       </c>
-      <c r="E11" s="80"/>
-      <c r="F11" s="54">
+      <c r="E11" s="78"/>
+      <c r="F11" s="53">
         <v>0.40625</v>
       </c>
-      <c r="G11" s="80" t="str">
-        <f>master!B40</f>
-        <v>個人演習2</v>
+      <c r="G11" s="78" t="str">
+        <f>master!B41</f>
+        <v>提案の実施</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" s="34">
         <v>0.41666666666666669</v>
       </c>
-      <c r="B12" s="76">
+      <c r="B12" s="75">
         <v>0.41666666666666669</v>
       </c>
-      <c r="C12" s="57" t="str">
+      <c r="C12" s="56" t="str">
         <f>master!B5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="D12" s="56"/>
-      <c r="E12" s="81"/>
-      <c r="F12" s="56"/>
-      <c r="G12" s="81"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="79"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="79"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="35"/>
-      <c r="B13" s="77"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="56"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="56"/>
-      <c r="G13" s="81"/>
+      <c r="B13" s="76"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="55"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="79"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="35"/>
-      <c r="B14" s="54">
+      <c r="B14" s="53">
         <v>0.4375</v>
       </c>
-      <c r="C14" s="57" t="str">
+      <c r="C14" s="56" t="str">
         <f>master!B18</f>
         <v>提案書のサンプルについて</v>
       </c>
-      <c r="D14" s="56"/>
-      <c r="E14" s="81"/>
-      <c r="F14" s="56"/>
-      <c r="G14" s="81"/>
+      <c r="D14" s="55"/>
+      <c r="E14" s="79"/>
+      <c r="F14" s="55"/>
+      <c r="G14" s="79"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="36"/>
-      <c r="B15" s="78" t="s">
+      <c r="B15" s="119" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="58"/>
-      <c r="D15" s="56"/>
-      <c r="E15" s="81"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="81"/>
+      <c r="C15" s="115"/>
+      <c r="D15" s="55"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="55"/>
+      <c r="G15" s="79"/>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="34">
+      <c r="A16" s="52">
         <v>0.45833333333333331</v>
       </c>
-      <c r="B16" s="54">
+      <c r="B16" s="53">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C16" s="80" t="str">
+      <c r="C16" s="121" t="str">
         <f>master!B32</f>
-        <v>個人演習1</v>
-      </c>
-      <c r="D16" s="56"/>
-      <c r="E16" s="81"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="81"/>
+        <v>提案演習の全体像</v>
+      </c>
+      <c r="D16" s="114"/>
+      <c r="E16" s="79"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="79"/>
     </row>
     <row r="17" spans="1:8">
-      <c r="A17" s="35"/>
-      <c r="B17" s="56"/>
-      <c r="C17" s="81"/>
-      <c r="D17" s="56"/>
-      <c r="E17" s="81"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="81"/>
+      <c r="A17" s="49"/>
+      <c r="B17" s="55"/>
+      <c r="C17" s="117" t="str">
+        <f>master!B33</f>
+        <v>提案資料</v>
+      </c>
+      <c r="D17" s="114"/>
+      <c r="E17" s="79"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="79"/>
     </row>
     <row r="18" spans="1:8">
-      <c r="A18" s="35"/>
-      <c r="B18" s="56"/>
-      <c r="C18" s="81"/>
-      <c r="D18" s="56"/>
-      <c r="E18" s="81"/>
-      <c r="F18" s="56"/>
-      <c r="G18" s="81"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="55"/>
+      <c r="C18" s="117" t="str">
+        <f>master!B34</f>
+        <v>提案資料の作成</v>
+      </c>
+      <c r="D18" s="114"/>
+      <c r="E18" s="79"/>
+      <c r="F18" s="55"/>
+      <c r="G18" s="79"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="36"/>
-      <c r="B19" s="56"/>
-      <c r="C19" s="81"/>
-      <c r="D19" s="56"/>
-      <c r="E19" s="81"/>
-      <c r="F19" s="56"/>
-      <c r="G19" s="81"/>
+      <c r="A19" s="116"/>
+      <c r="B19" s="55"/>
+      <c r="C19" s="117"/>
+      <c r="D19" s="114"/>
+      <c r="E19" s="79"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="79"/>
     </row>
     <row r="20" spans="1:8">
-      <c r="A20" s="53">
+      <c r="A20" s="52">
         <v>0.5</v>
       </c>
-      <c r="B20" s="56"/>
-      <c r="C20" s="81"/>
-      <c r="D20" s="56"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="56"/>
-      <c r="G20" s="81"/>
+      <c r="B20" s="55"/>
+      <c r="C20" s="117"/>
+      <c r="D20" s="114"/>
+      <c r="E20" s="79"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="79"/>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="49"/>
-      <c r="B21" s="51"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="75"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="79"/>
+      <c r="B21" s="38"/>
+      <c r="C21" s="118"/>
+      <c r="D21" s="120"/>
+      <c r="E21" s="77"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="77"/>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="35"/>
       <c r="B22" s="35">
         <v>0.52083333333333337</v>
       </c>
-      <c r="C22" s="60" t="s">
+      <c r="C22" s="59" t="s">
         <v>1</v>
       </c>
       <c r="D22" s="35">
         <v>0.52083333333333337</v>
       </c>
-      <c r="E22" s="60" t="s">
+      <c r="E22" s="59" t="s">
         <v>1</v>
       </c>
       <c r="F22" s="35">
         <v>0.52083333333333337</v>
       </c>
-      <c r="G22" s="60" t="s">
+      <c r="G22" s="59" t="s">
         <v>1</v>
       </c>
     </row>
@@ -2838,15 +3201,15 @@
       <c r="B23" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C23" s="61"/>
+      <c r="C23" s="60"/>
       <c r="D23" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="E23" s="61"/>
+      <c r="E23" s="60"/>
       <c r="F23" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="G23" s="61"/>
+      <c r="G23" s="60"/>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="34">
@@ -2855,136 +3218,139 @@
       <c r="B24" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="61"/>
+      <c r="C24" s="60"/>
       <c r="D24" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="E24" s="61"/>
+      <c r="E24" s="60"/>
       <c r="F24" s="35" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="61"/>
+      <c r="G24" s="60"/>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="35"/>
       <c r="B25" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="C25" s="62"/>
+      <c r="C25" s="61"/>
       <c r="D25" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="E25" s="62"/>
+      <c r="E25" s="61"/>
       <c r="F25" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="G25" s="62"/>
+      <c r="G25" s="61"/>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="35"/>
       <c r="B26" s="37">
         <v>0.5625</v>
       </c>
-      <c r="C26" s="80"/>
+      <c r="C26" s="78"/>
       <c r="D26" s="37">
         <v>0.5625</v>
       </c>
-      <c r="E26" s="80"/>
+      <c r="E26" s="78"/>
       <c r="F26" s="37">
         <v>0.5625</v>
       </c>
-      <c r="G26" s="80"/>
+      <c r="G26" s="78" t="str">
+        <f>master!B46</f>
+        <v>提案の改善</v>
+      </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="36"/>
       <c r="B27" s="39"/>
-      <c r="C27" s="81"/>
+      <c r="C27" s="79"/>
       <c r="D27" s="39"/>
-      <c r="E27" s="81"/>
+      <c r="E27" s="79"/>
       <c r="F27" s="39"/>
-      <c r="G27" s="81"/>
+      <c r="G27" s="79"/>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="34">
         <v>0.58333333333333337</v>
       </c>
       <c r="B28" s="39"/>
-      <c r="C28" s="81"/>
+      <c r="C28" s="79"/>
       <c r="D28" s="39"/>
-      <c r="E28" s="81"/>
+      <c r="E28" s="79"/>
       <c r="F28" s="39"/>
-      <c r="G28" s="81"/>
+      <c r="G28" s="79"/>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="35"/>
       <c r="B29" s="39"/>
-      <c r="C29" s="81"/>
+      <c r="C29" s="79"/>
       <c r="D29" s="39"/>
-      <c r="E29" s="81"/>
+      <c r="E29" s="79"/>
       <c r="F29" s="39"/>
-      <c r="G29" s="81"/>
+      <c r="G29" s="79"/>
       <c r="H29" s="48"/>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="35"/>
       <c r="B30" s="39"/>
-      <c r="C30" s="81"/>
+      <c r="C30" s="79"/>
       <c r="D30" s="39"/>
-      <c r="E30" s="81"/>
+      <c r="E30" s="79"/>
       <c r="F30" s="39"/>
-      <c r="G30" s="81"/>
+      <c r="G30" s="79"/>
       <c r="H30" s="48"/>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="36"/>
       <c r="B31" s="39"/>
-      <c r="C31" s="81"/>
+      <c r="C31" s="79"/>
       <c r="D31" s="39"/>
-      <c r="E31" s="81"/>
+      <c r="E31" s="79"/>
       <c r="F31" s="39"/>
-      <c r="G31" s="81"/>
+      <c r="G31" s="79"/>
       <c r="H31" s="48"/>
     </row>
     <row r="32" spans="1:8">
-      <c r="A32" s="53">
+      <c r="A32" s="52">
         <v>0.625</v>
       </c>
       <c r="B32" s="39"/>
-      <c r="C32" s="81"/>
+      <c r="C32" s="79"/>
       <c r="D32" s="39"/>
-      <c r="E32" s="81"/>
+      <c r="E32" s="79"/>
       <c r="F32" s="39"/>
-      <c r="G32" s="81"/>
+      <c r="G32" s="79"/>
       <c r="H32" s="48"/>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="49"/>
       <c r="B33" s="39"/>
-      <c r="C33" s="81"/>
+      <c r="C33" s="79"/>
       <c r="D33" s="39"/>
-      <c r="E33" s="81"/>
+      <c r="E33" s="79"/>
       <c r="F33" s="39"/>
-      <c r="G33" s="81"/>
+      <c r="G33" s="79"/>
       <c r="H33" s="48"/>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="49"/>
       <c r="B34" s="39"/>
-      <c r="C34" s="81"/>
+      <c r="C34" s="79"/>
       <c r="D34" s="39"/>
-      <c r="E34" s="81"/>
+      <c r="E34" s="79"/>
       <c r="F34" s="39"/>
-      <c r="G34" s="81"/>
+      <c r="G34" s="79"/>
       <c r="H34" s="48"/>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="36"/>
       <c r="B35" s="39"/>
-      <c r="C35" s="81"/>
+      <c r="C35" s="79"/>
       <c r="D35" s="39"/>
-      <c r="E35" s="81"/>
+      <c r="E35" s="79"/>
       <c r="F35" s="39"/>
-      <c r="G35" s="81"/>
+      <c r="G35" s="79"/>
       <c r="H35" s="48"/>
     </row>
     <row r="36" spans="1:8">
@@ -2992,41 +3358,41 @@
         <v>0.66666666666666663</v>
       </c>
       <c r="B36" s="39"/>
-      <c r="C36" s="81"/>
+      <c r="C36" s="79"/>
       <c r="D36" s="39"/>
-      <c r="E36" s="81"/>
+      <c r="E36" s="79"/>
       <c r="F36" s="39"/>
-      <c r="G36" s="81"/>
+      <c r="G36" s="79"/>
       <c r="H36" s="48"/>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="35"/>
       <c r="B37" s="39"/>
-      <c r="C37" s="81"/>
+      <c r="C37" s="79"/>
       <c r="D37" s="39"/>
-      <c r="E37" s="81"/>
+      <c r="E37" s="79"/>
       <c r="F37" s="39"/>
-      <c r="G37" s="81"/>
+      <c r="G37" s="79"/>
       <c r="H37" s="48"/>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="35"/>
       <c r="B38" s="39"/>
-      <c r="C38" s="81"/>
+      <c r="C38" s="79"/>
       <c r="D38" s="39"/>
-      <c r="E38" s="81"/>
+      <c r="E38" s="79"/>
       <c r="F38" s="39"/>
-      <c r="G38" s="81"/>
+      <c r="G38" s="79"/>
       <c r="H38" s="48"/>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="35"/>
       <c r="B39" s="39"/>
-      <c r="C39" s="81"/>
+      <c r="C39" s="79"/>
       <c r="D39" s="39"/>
-      <c r="E39" s="81"/>
+      <c r="E39" s="79"/>
       <c r="F39" s="39"/>
-      <c r="G39" s="81"/>
+      <c r="G39" s="79"/>
       <c r="H39" s="48"/>
     </row>
     <row r="40" spans="1:8">
@@ -3034,56 +3400,56 @@
         <v>0.70833333333333337</v>
       </c>
       <c r="B40" s="39"/>
-      <c r="C40" s="81"/>
+      <c r="C40" s="79"/>
       <c r="D40" s="39"/>
-      <c r="E40" s="81"/>
+      <c r="E40" s="79"/>
       <c r="F40" s="38"/>
-      <c r="G40" s="79"/>
+      <c r="G40" s="77"/>
       <c r="H40" s="48"/>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="35"/>
       <c r="B41" s="39"/>
-      <c r="C41" s="81"/>
+      <c r="C41" s="79"/>
       <c r="D41" s="39"/>
-      <c r="E41" s="81"/>
+      <c r="E41" s="79"/>
       <c r="F41" s="39">
         <v>0.71875</v>
       </c>
-      <c r="G41" s="113" t="s">
-        <v>141</v>
+      <c r="G41" s="82" t="s">
+        <v>120</v>
       </c>
       <c r="H41" s="50"/>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="39"/>
       <c r="B42" s="39"/>
-      <c r="C42" s="79"/>
+      <c r="C42" s="77"/>
       <c r="D42" s="39"/>
-      <c r="E42" s="79"/>
+      <c r="E42" s="77"/>
       <c r="F42" s="39"/>
-      <c r="G42" s="112"/>
+      <c r="G42" s="81"/>
       <c r="H42" s="48"/>
     </row>
     <row r="43" spans="1:8" ht="14.25" customHeight="1">
       <c r="A43" s="38"/>
-      <c r="B43" s="72">
+      <c r="B43" s="71">
         <v>0.73958333333333337</v>
       </c>
-      <c r="C43" s="73" t="s">
-        <v>79</v>
-      </c>
-      <c r="D43" s="72">
+      <c r="C43" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="D43" s="71">
         <v>0.73958333333333337</v>
       </c>
-      <c r="E43" s="73" t="s">
-        <v>79</v>
-      </c>
-      <c r="F43" s="72">
+      <c r="E43" s="72" t="s">
+        <v>77</v>
+      </c>
+      <c r="F43" s="71">
         <v>0.73958333333333337</v>
       </c>
-      <c r="G43" s="73" t="s">
-        <v>79</v>
+      <c r="G43" s="72" t="s">
+        <v>77</v>
       </c>
       <c r="H43" s="49"/>
     </row>
@@ -3268,21 +3634,21 @@
       <c r="A12" s="10"/>
       <c r="B12" s="19"/>
       <c r="C12" s="19" t="s">
-        <v>136</v>
+        <v>117</v>
       </c>
       <c r="D12" s="89" t="s">
         <v>40</v>
       </c>
       <c r="E12" s="89"/>
       <c r="F12" s="89"/>
-      <c r="G12" s="82" t="s">
+      <c r="G12" s="80" t="s">
         <v>41</v>
       </c>
       <c r="H12" s="19"/>
       <c r="I12" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="52">
+      <c r="J12" s="51">
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="K12" s="19"/>
@@ -3292,21 +3658,21 @@
       <c r="A13" s="10"/>
       <c r="B13" s="19"/>
       <c r="C13" s="19" t="s">
-        <v>135</v>
+        <v>116</v>
       </c>
       <c r="D13" s="89" t="s">
-        <v>137</v>
+        <v>118</v>
       </c>
       <c r="E13" s="89"/>
       <c r="F13" s="89"/>
-      <c r="G13" s="82" t="s">
-        <v>138</v>
+      <c r="G13" s="80" t="s">
+        <v>119</v>
       </c>
       <c r="H13" s="19"/>
       <c r="I13" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="J13" s="52">
+      <c r="J13" s="51">
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="K13" s="19"/>
@@ -3316,21 +3682,21 @@
       <c r="A14" s="10"/>
       <c r="B14" s="19"/>
       <c r="C14" s="19" t="s">
-        <v>141</v>
+        <v>120</v>
       </c>
       <c r="D14" s="89" t="s">
-        <v>142</v>
+        <v>121</v>
       </c>
       <c r="E14" s="89"/>
       <c r="F14" s="89"/>
-      <c r="G14" s="82" t="s">
-        <v>138</v>
+      <c r="G14" s="80" t="s">
+        <v>119</v>
       </c>
       <c r="H14" s="19"/>
       <c r="I14" s="46" t="s">
         <v>24</v>
       </c>
-      <c r="J14" s="52">
+      <c r="J14" s="51">
         <v>1.0416666666666666E-2</v>
       </c>
       <c r="K14" s="19"/>
@@ -3373,7 +3739,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A2:N50"/>
+  <dimension ref="A2:N60"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="4.33203125" style="1" customWidth="1"/>
@@ -3439,16 +3805,16 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="111"/>
-      <c r="C5" s="111"/>
-      <c r="D5" s="111"/>
-      <c r="E5" s="111"/>
-      <c r="F5" s="111"/>
-      <c r="G5" s="111"/>
-      <c r="H5" s="111"/>
-      <c r="I5" s="111"/>
-      <c r="J5" s="111"/>
-      <c r="K5" s="111"/>
+      <c r="B5" s="108"/>
+      <c r="C5" s="108"/>
+      <c r="D5" s="108"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="108"/>
+      <c r="K5" s="108"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
@@ -3489,7 +3855,7 @@
       <c r="B8" s="31" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="55" t="s">
+      <c r="C8" s="54" t="s">
         <v>47</v>
       </c>
       <c r="D8" s="42" t="s">
@@ -3511,7 +3877,7 @@
       <c r="B9" s="31" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="55" t="s">
+      <c r="C9" s="54" t="s">
         <v>48</v>
       </c>
       <c r="D9" s="42" t="s">
@@ -3534,7 +3900,7 @@
         <v>42</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>49</v>
+        <v>165</v>
       </c>
       <c r="D10" s="42" t="s">
         <v>19</v>
@@ -3551,95 +3917,103 @@
       <c r="M10" s="6"/>
       <c r="N10" s="6"/>
     </row>
-    <row r="11" spans="1:14">
-      <c r="B11" s="31" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" s="33" t="s">
-        <v>49</v>
-      </c>
-      <c r="D11" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="41"/>
-      <c r="F11" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="G11" s="33" t="s">
-        <v>18</v>
-      </c>
-      <c r="K11" s="6"/>
-      <c r="L11" s="6"/>
-      <c r="M11" s="6"/>
-      <c r="N11" s="6"/>
-    </row>
-    <row r="13" spans="1:14" ht="24" customHeight="1">
+    <row r="12" spans="1:14" ht="24" customHeight="1">
+      <c r="A12" s="10"/>
+      <c r="B12" s="91" t="s">
+        <v>5</v>
+      </c>
+      <c r="C12" s="91" t="s">
+        <v>7</v>
+      </c>
+      <c r="D12" s="91" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="91"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="91" t="s">
+        <v>9</v>
+      </c>
+      <c r="H12" s="90" t="s">
+        <v>23</v>
+      </c>
+      <c r="I12" s="106" t="s">
+        <v>31</v>
+      </c>
+      <c r="J12" s="107"/>
+      <c r="K12" s="90" t="s">
+        <v>32</v>
+      </c>
+      <c r="L12" s="6"/>
+      <c r="M12" s="6"/>
+      <c r="N12" s="6"/>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" s="10"/>
-      <c r="B13" s="91" t="s">
-        <v>5</v>
-      </c>
-      <c r="C13" s="91" t="s">
-        <v>7</v>
-      </c>
-      <c r="D13" s="91" t="s">
-        <v>8</v>
-      </c>
+      <c r="B13" s="91"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
       <c r="E13" s="91"/>
       <c r="F13" s="91"/>
-      <c r="G13" s="91" t="s">
-        <v>9</v>
-      </c>
-      <c r="H13" s="90" t="s">
-        <v>23</v>
-      </c>
-      <c r="I13" s="109" t="s">
-        <v>31</v>
-      </c>
-      <c r="J13" s="110"/>
-      <c r="K13" s="90" t="s">
-        <v>32</v>
-      </c>
+      <c r="G13" s="91"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="J13" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="K13" s="91"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" ht="63">
       <c r="A14" s="10"/>
-      <c r="B14" s="91"/>
-      <c r="C14" s="91"/>
-      <c r="D14" s="91"/>
-      <c r="E14" s="91"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="91"/>
-      <c r="H14" s="90"/>
-      <c r="I14" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="K14" s="91"/>
+      <c r="B14" s="73" t="str">
+        <f>master!B4</f>
+        <v>導入</v>
+      </c>
+      <c r="C14" s="47" t="str">
+        <f>master!C4</f>
+        <v>はじめに　｜　“Be a social designer”とは</v>
+      </c>
+      <c r="D14" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="104"/>
+      <c r="F14" s="105"/>
+      <c r="G14" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="H14" s="12"/>
+      <c r="I14" s="45" t="s">
+        <v>24</v>
+      </c>
+      <c r="J14" s="43">
+        <v>2.0833333333333333E-3</v>
+      </c>
+      <c r="K14" s="40"/>
       <c r="L14" s="6"/>
       <c r="M14" s="6"/>
       <c r="N14" s="6"/>
     </row>
     <row r="15" spans="1:14" ht="63">
       <c r="A15" s="10"/>
-      <c r="B15" s="74" t="str">
-        <f>master!B4</f>
-        <v>導入</v>
+      <c r="B15" s="109" t="str">
+        <f>master!B5</f>
+        <v>企画提案のステップ</v>
       </c>
       <c r="C15" s="47" t="str">
-        <f>master!C4</f>
-        <v>はじめに　｜　“Be a social designer”とは</v>
-      </c>
-      <c r="D15" s="100" t="s">
-        <v>101</v>
-      </c>
-      <c r="E15" s="101"/>
-      <c r="F15" s="102"/>
+        <f>master!C5</f>
+        <v>企画提案のステップ</v>
+      </c>
+      <c r="D15" s="103" t="s">
+        <v>85</v>
+      </c>
+      <c r="E15" s="104"/>
+      <c r="F15" s="105"/>
       <c r="G15" s="47" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="45" t="s">
@@ -3653,185 +4027,182 @@
       <c r="M15" s="6"/>
       <c r="N15" s="6"/>
     </row>
-    <row r="16" spans="1:14" ht="63">
-      <c r="A16" s="10"/>
-      <c r="B16" s="97" t="str">
-        <f>master!B5</f>
-        <v>企画提案のステップ</v>
-      </c>
+    <row r="16" spans="1:14" ht="163.80000000000001">
+      <c r="A16" s="11"/>
+      <c r="B16" s="110"/>
       <c r="C16" s="47" t="str">
-        <f>master!C5</f>
-        <v>企画提案のステップ</v>
-      </c>
-      <c r="D16" s="100" t="s">
-        <v>102</v>
-      </c>
-      <c r="E16" s="101"/>
-      <c r="F16" s="102"/>
+        <f>master!C6</f>
+        <v>STEP①-1　日常の不便を考える</v>
+      </c>
+      <c r="D16" s="103" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="104"/>
+      <c r="F16" s="105"/>
       <c r="G16" s="47" t="s">
-        <v>100</v>
+        <v>114</v>
       </c>
       <c r="H16" s="12"/>
       <c r="I16" s="45" t="s">
         <v>24</v>
       </c>
       <c r="J16" s="43">
-        <v>2.0833333333333333E-3</v>
+        <v>3.472222222222222E-3</v>
       </c>
       <c r="K16" s="40"/>
       <c r="L16" s="6"/>
       <c r="M16" s="6"/>
       <c r="N16" s="6"/>
     </row>
-    <row r="17" spans="1:14" ht="163.80000000000001">
+    <row r="17" spans="1:14" ht="37.799999999999997">
       <c r="A17" s="11"/>
-      <c r="B17" s="98"/>
+      <c r="B17" s="110"/>
       <c r="C17" s="47" t="str">
-        <f>master!C6</f>
-        <v>STEP①-1　日常の不便を考える</v>
-      </c>
-      <c r="D17" s="100" t="s">
-        <v>134</v>
-      </c>
-      <c r="E17" s="101"/>
-      <c r="F17" s="102"/>
+        <f>master!C7</f>
+        <v>STEP①-2　課題の深掘り</v>
+      </c>
+      <c r="D17" s="103" t="s">
+        <v>86</v>
+      </c>
+      <c r="E17" s="104"/>
+      <c r="F17" s="105"/>
       <c r="G17" s="47" t="s">
-        <v>133</v>
+        <v>36</v>
       </c>
       <c r="H17" s="12"/>
       <c r="I17" s="45" t="s">
         <v>24</v>
       </c>
       <c r="J17" s="43">
-        <v>3.472222222222222E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K17" s="40"/>
       <c r="L17" s="6"/>
       <c r="M17" s="6"/>
       <c r="N17" s="6"/>
     </row>
-    <row r="18" spans="1:14" ht="37.799999999999997">
+    <row r="18" spans="1:14" ht="151.19999999999999">
       <c r="A18" s="11"/>
-      <c r="B18" s="98"/>
+      <c r="B18" s="110"/>
       <c r="C18" s="47" t="str">
-        <f>master!C7</f>
-        <v>STEP①-2　課題の深掘り</v>
-      </c>
-      <c r="D18" s="100" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="101"/>
-      <c r="F18" s="102"/>
+        <f>master!C8</f>
+        <v>STEP①-3　ITアイデアへ落とし込む</v>
+      </c>
+      <c r="D18" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="104"/>
+      <c r="F18" s="105"/>
       <c r="G18" s="47" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="H18" s="12"/>
       <c r="I18" s="45" t="s">
         <v>24</v>
       </c>
       <c r="J18" s="43">
-        <v>1.3888888888888889E-3</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K18" s="40"/>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
       <c r="N18" s="6"/>
     </row>
-    <row r="19" spans="1:14" ht="151.19999999999999">
+    <row r="19" spans="1:14" ht="252">
       <c r="A19" s="11"/>
-      <c r="B19" s="98"/>
+      <c r="B19" s="110"/>
       <c r="C19" s="47" t="str">
-        <f>master!C8</f>
-        <v>STEP①-3　ITアイデアへ落とし込む</v>
-      </c>
-      <c r="D19" s="100" t="s">
-        <v>104</v>
-      </c>
-      <c r="E19" s="101"/>
-      <c r="F19" s="102"/>
+        <f>master!C9</f>
+        <v>STEP②-1 創出したアイデアに関する調査・確認</v>
+      </c>
+      <c r="D19" s="103" t="s">
+        <v>88</v>
+      </c>
+      <c r="E19" s="104"/>
+      <c r="F19" s="105"/>
       <c r="G19" s="47" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="H19" s="12"/>
       <c r="I19" s="45" t="s">
         <v>24</v>
       </c>
       <c r="J19" s="43">
-        <v>2.0833333333333333E-3</v>
+        <v>0</v>
       </c>
       <c r="K19" s="40"/>
       <c r="L19" s="6"/>
       <c r="M19" s="6"/>
       <c r="N19" s="6"/>
     </row>
-    <row r="20" spans="1:14" ht="252">
+    <row r="20" spans="1:14" ht="126">
       <c r="A20" s="11"/>
-      <c r="B20" s="98"/>
+      <c r="B20" s="110"/>
       <c r="C20" s="47" t="str">
-        <f>master!C9</f>
-        <v>STEP②-1 創出したアイデアに関する調査・確認</v>
-      </c>
-      <c r="D20" s="100" t="s">
-        <v>105</v>
-      </c>
-      <c r="E20" s="101"/>
-      <c r="F20" s="102"/>
+        <f>master!C10</f>
+        <v>STEP②-2 環境分析</v>
+      </c>
+      <c r="D20" s="103" t="s">
+        <v>89</v>
+      </c>
+      <c r="E20" s="104"/>
+      <c r="F20" s="105"/>
       <c r="G20" s="47" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H20" s="12"/>
       <c r="I20" s="45" t="s">
         <v>24</v>
       </c>
       <c r="J20" s="43">
-        <v>0</v>
+        <v>2.0833333333333333E-3</v>
       </c>
       <c r="K20" s="40"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
       <c r="N20" s="6"/>
     </row>
-    <row r="21" spans="1:14" ht="126">
+    <row r="21" spans="1:14" ht="63">
       <c r="A21" s="11"/>
-      <c r="B21" s="98"/>
+      <c r="B21" s="110"/>
       <c r="C21" s="47" t="str">
-        <f>master!C10</f>
-        <v>STEP②-2 環境分析</v>
-      </c>
-      <c r="D21" s="100" t="s">
-        <v>106</v>
-      </c>
-      <c r="E21" s="101"/>
-      <c r="F21" s="102"/>
+        <f>master!C11</f>
+        <v>（参考）PEST分析</v>
+      </c>
+      <c r="D21" s="103" t="s">
+        <v>90</v>
+      </c>
+      <c r="E21" s="104"/>
+      <c r="F21" s="105"/>
       <c r="G21" s="47" t="s">
-        <v>44</v>
+        <v>83</v>
       </c>
       <c r="H21" s="12"/>
       <c r="I21" s="45" t="s">
         <v>24</v>
       </c>
       <c r="J21" s="43">
-        <v>2.0833333333333333E-3</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K21" s="40"/>
       <c r="L21" s="6"/>
       <c r="M21" s="6"/>
       <c r="N21" s="6"/>
     </row>
-    <row r="22" spans="1:14" ht="63">
+    <row r="22" spans="1:14" ht="75.599999999999994">
       <c r="A22" s="11"/>
-      <c r="B22" s="98"/>
+      <c r="B22" s="110"/>
       <c r="C22" s="47" t="str">
-        <f>master!C11</f>
-        <v>（参考）PEST分析</v>
-      </c>
-      <c r="D22" s="100" t="s">
-        <v>107</v>
-      </c>
-      <c r="E22" s="101"/>
-      <c r="F22" s="102"/>
+        <f>master!C12</f>
+        <v>（参考） 3C分析</v>
+      </c>
+      <c r="D22" s="103" t="s">
+        <v>91</v>
+      </c>
+      <c r="E22" s="104"/>
+      <c r="F22" s="105"/>
       <c r="G22" s="47" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
       <c r="H22" s="12"/>
       <c r="I22" s="45" t="s">
@@ -3847,16 +4218,16 @@
     </row>
     <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="98"/>
+      <c r="B23" s="110"/>
       <c r="C23" s="47" t="str">
-        <f>master!C12</f>
-        <v>（参考） 3C分析</v>
-      </c>
-      <c r="D23" s="100" t="s">
-        <v>108</v>
-      </c>
-      <c r="E23" s="101"/>
-      <c r="F23" s="102"/>
+        <f>master!C13</f>
+        <v>（参考） SWOT分析</v>
+      </c>
+      <c r="D23" s="103" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="104"/>
+      <c r="F23" s="105"/>
       <c r="G23" s="47" t="s">
         <v>37</v>
       </c>
@@ -3872,20 +4243,20 @@
       <c r="M23" s="6"/>
       <c r="N23" s="6"/>
     </row>
-    <row r="24" spans="1:14" ht="75.599999999999994">
+    <row r="24" spans="1:14" ht="113.4">
       <c r="A24" s="11"/>
-      <c r="B24" s="98"/>
+      <c r="B24" s="110"/>
       <c r="C24" s="47" t="str">
-        <f>master!C13</f>
-        <v>（参考） SWOT分析</v>
-      </c>
-      <c r="D24" s="100" t="s">
-        <v>109</v>
-      </c>
-      <c r="E24" s="101"/>
-      <c r="F24" s="102"/>
+        <f>master!C14</f>
+        <v>STEP③-1 提案書作成</v>
+      </c>
+      <c r="D24" s="103" t="s">
+        <v>93</v>
+      </c>
+      <c r="E24" s="104"/>
+      <c r="F24" s="105"/>
       <c r="G24" s="47" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H24" s="12"/>
       <c r="I24" s="45" t="s">
@@ -3899,20 +4270,20 @@
       <c r="M24" s="6"/>
       <c r="N24" s="6"/>
     </row>
-    <row r="25" spans="1:14" ht="113.4">
+    <row r="25" spans="1:14" ht="88.2">
       <c r="A25" s="11"/>
-      <c r="B25" s="98"/>
+      <c r="B25" s="110"/>
       <c r="C25" s="47" t="str">
-        <f>master!C14</f>
-        <v>STEP③-1 提案書作成</v>
-      </c>
-      <c r="D25" s="100" t="s">
-        <v>110</v>
-      </c>
-      <c r="E25" s="101"/>
-      <c r="F25" s="102"/>
+        <f>master!C15</f>
+        <v>STEP③-2 プロトタイプ作成</v>
+      </c>
+      <c r="D25" s="103" t="s">
+        <v>94</v>
+      </c>
+      <c r="E25" s="104"/>
+      <c r="F25" s="105"/>
       <c r="G25" s="47" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H25" s="12"/>
       <c r="I25" s="45" t="s">
@@ -3926,20 +4297,20 @@
       <c r="M25" s="6"/>
       <c r="N25" s="6"/>
     </row>
-    <row r="26" spans="1:14" ht="88.2">
+    <row r="26" spans="1:14" ht="113.4">
       <c r="A26" s="11"/>
-      <c r="B26" s="98"/>
+      <c r="B26" s="111"/>
       <c r="C26" s="47" t="str">
-        <f>master!C15</f>
-        <v>STEP③-2 プロトタイプ作成</v>
-      </c>
-      <c r="D26" s="100" t="s">
-        <v>111</v>
-      </c>
-      <c r="E26" s="101"/>
-      <c r="F26" s="102"/>
+        <f>master!C16</f>
+        <v>まとめ</v>
+      </c>
+      <c r="D26" s="103" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="104"/>
+      <c r="F26" s="105"/>
       <c r="G26" s="47" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="H26" s="12"/>
       <c r="I26" s="45" t="s">
@@ -3953,50 +4324,50 @@
       <c r="M26" s="6"/>
       <c r="N26" s="6"/>
     </row>
-    <row r="27" spans="1:14" ht="113.4">
+    <row r="27" spans="1:14" ht="37.799999999999997">
       <c r="A27" s="11"/>
-      <c r="B27" s="99"/>
+      <c r="B27" s="109" t="str">
+        <f>master!B18</f>
+        <v>提案書のサンプルについて</v>
+      </c>
       <c r="C27" s="47" t="str">
-        <f>master!C16</f>
-        <v>まとめ</v>
-      </c>
-      <c r="D27" s="100" t="s">
-        <v>112</v>
-      </c>
-      <c r="E27" s="101"/>
-      <c r="F27" s="102"/>
+        <f>master!C18</f>
+        <v>はじめに</v>
+      </c>
+      <c r="D27" s="103" t="s">
+        <v>113</v>
+      </c>
+      <c r="E27" s="104"/>
+      <c r="F27" s="105"/>
       <c r="G27" s="47" t="s">
-        <v>38</v>
+        <v>98</v>
       </c>
       <c r="H27" s="12"/>
       <c r="I27" s="45" t="s">
         <v>24</v>
       </c>
       <c r="J27" s="43">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K27" s="40"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
       <c r="N27" s="6"/>
     </row>
-    <row r="28" spans="1:14" ht="37.799999999999997">
+    <row r="28" spans="1:14" ht="25.2">
       <c r="A28" s="11"/>
-      <c r="B28" s="97" t="str">
-        <f>master!B18</f>
-        <v>提案書のサンプルについて</v>
-      </c>
+      <c r="B28" s="110"/>
       <c r="C28" s="47" t="str">
-        <f>master!C18</f>
-        <v>はじめに</v>
-      </c>
-      <c r="D28" s="100" t="s">
-        <v>131</v>
-      </c>
-      <c r="E28" s="101"/>
-      <c r="F28" s="102"/>
+        <f>master!C19</f>
+        <v>１．サマリ</v>
+      </c>
+      <c r="D28" s="103" t="s">
+        <v>96</v>
+      </c>
+      <c r="E28" s="104"/>
+      <c r="F28" s="105"/>
       <c r="G28" s="47" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="H28" s="12"/>
       <c r="I28" s="45" t="s">
@@ -4012,25 +4383,25 @@
     </row>
     <row r="29" spans="1:14" ht="25.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="98"/>
+      <c r="B29" s="110"/>
       <c r="C29" s="47" t="str">
-        <f>master!C19</f>
-        <v>１．サマリ</v>
-      </c>
-      <c r="D29" s="100" t="s">
-        <v>113</v>
-      </c>
-      <c r="E29" s="101"/>
-      <c r="F29" s="102"/>
+        <f>master!C20</f>
+        <v>２．背景</v>
+      </c>
+      <c r="D29" s="103" t="s">
+        <v>110</v>
+      </c>
+      <c r="E29" s="104"/>
+      <c r="F29" s="105"/>
       <c r="G29" s="47" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H29" s="12"/>
       <c r="I29" s="45" t="s">
         <v>24</v>
       </c>
       <c r="J29" s="43">
-        <v>6.9444444444444447E-4</v>
+        <v>1.3888888888888889E-3</v>
       </c>
       <c r="K29" s="40"/>
       <c r="L29" s="6"/>
@@ -4039,18 +4410,18 @@
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="98"/>
+      <c r="B30" s="110"/>
       <c r="C30" s="47" t="str">
-        <f>master!C20</f>
-        <v>２．背景</v>
-      </c>
-      <c r="D30" s="100" t="s">
-        <v>128</v>
-      </c>
-      <c r="E30" s="101"/>
-      <c r="F30" s="102"/>
+        <f>master!C21</f>
+        <v>３．現状課題</v>
+      </c>
+      <c r="D30" s="103" t="s">
+        <v>111</v>
+      </c>
+      <c r="E30" s="104"/>
+      <c r="F30" s="105"/>
       <c r="G30" s="47" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="H30" s="12"/>
       <c r="I30" s="45" t="s">
@@ -4064,20 +4435,20 @@
       <c r="M30" s="6"/>
       <c r="N30" s="6"/>
     </row>
-    <row r="31" spans="1:14" ht="25.2">
+    <row r="31" spans="1:14" ht="63">
       <c r="A31" s="11"/>
-      <c r="B31" s="98"/>
+      <c r="B31" s="110"/>
       <c r="C31" s="47" t="str">
-        <f>master!C21</f>
-        <v>３．現状課題</v>
-      </c>
-      <c r="D31" s="100" t="s">
-        <v>129</v>
-      </c>
-      <c r="E31" s="101"/>
-      <c r="F31" s="102"/>
+        <f>master!C22</f>
+        <v>４．業界動向・市場分析</v>
+      </c>
+      <c r="D31" s="103" t="s">
+        <v>101</v>
+      </c>
+      <c r="E31" s="104"/>
+      <c r="F31" s="105"/>
       <c r="G31" s="47" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="H31" s="12"/>
       <c r="I31" s="45" t="s">
@@ -4091,20 +4462,20 @@
       <c r="M31" s="6"/>
       <c r="N31" s="6"/>
     </row>
-    <row r="32" spans="1:14" ht="63">
+    <row r="32" spans="1:14" ht="37.799999999999997">
       <c r="A32" s="11"/>
-      <c r="B32" s="98"/>
+      <c r="B32" s="110"/>
       <c r="C32" s="47" t="str">
-        <f>master!C22</f>
-        <v>４．業界動向・市場分析</v>
-      </c>
-      <c r="D32" s="100" t="s">
-        <v>118</v>
-      </c>
-      <c r="E32" s="101"/>
-      <c r="F32" s="102"/>
+        <f>master!C23</f>
+        <v>５．市場機会</v>
+      </c>
+      <c r="D32" s="103" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" s="104"/>
+      <c r="F32" s="105"/>
       <c r="G32" s="47" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="H32" s="12"/>
       <c r="I32" s="45" t="s">
@@ -4120,18 +4491,18 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="98"/>
+      <c r="B33" s="110"/>
       <c r="C33" s="47" t="str">
-        <f>master!C23</f>
-        <v>５．市場機会</v>
-      </c>
-      <c r="D33" s="100" t="s">
-        <v>121</v>
-      </c>
-      <c r="E33" s="101"/>
-      <c r="F33" s="102"/>
+        <f>master!C24</f>
+        <v>６．サービス概要</v>
+      </c>
+      <c r="D33" s="103" t="s">
+        <v>105</v>
+      </c>
+      <c r="E33" s="104"/>
+      <c r="F33" s="105"/>
       <c r="G33" s="47" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="H33" s="12"/>
       <c r="I33" s="45" t="s">
@@ -4145,20 +4516,20 @@
       <c r="M33" s="6"/>
       <c r="N33" s="6"/>
     </row>
-    <row r="34" spans="1:14" ht="37.799999999999997">
+    <row r="34" spans="1:14" ht="63">
       <c r="A34" s="11"/>
-      <c r="B34" s="98"/>
+      <c r="B34" s="110"/>
       <c r="C34" s="47" t="str">
-        <f>master!C24</f>
-        <v>６．サービス概要</v>
-      </c>
-      <c r="D34" s="100" t="s">
-        <v>122</v>
-      </c>
-      <c r="E34" s="101"/>
-      <c r="F34" s="102"/>
+        <f>master!C25</f>
+        <v>７．利用者体験イメージ</v>
+      </c>
+      <c r="D34" s="103" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" s="104"/>
+      <c r="F34" s="105"/>
       <c r="G34" s="47" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="H34" s="12"/>
       <c r="I34" s="45" t="s">
@@ -4172,20 +4543,20 @@
       <c r="M34" s="6"/>
       <c r="N34" s="6"/>
     </row>
-    <row r="35" spans="1:14" ht="63">
+    <row r="35" spans="1:14" ht="25.2">
       <c r="A35" s="11"/>
-      <c r="B35" s="98"/>
+      <c r="B35" s="110"/>
       <c r="C35" s="47" t="str">
-        <f>master!C25</f>
-        <v>７．利用者体験イメージ</v>
-      </c>
-      <c r="D35" s="100" t="s">
-        <v>123</v>
-      </c>
-      <c r="E35" s="101"/>
-      <c r="F35" s="102"/>
+        <f>master!C26</f>
+        <v>８．事業構成</v>
+      </c>
+      <c r="D35" s="103" t="s">
+        <v>97</v>
+      </c>
+      <c r="E35" s="104"/>
+      <c r="F35" s="105"/>
       <c r="G35" s="47" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="H35" s="12"/>
       <c r="I35" s="45" t="s">
@@ -4199,20 +4570,20 @@
       <c r="M35" s="6"/>
       <c r="N35" s="6"/>
     </row>
-    <row r="36" spans="1:14" ht="25.2">
+    <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="98"/>
+      <c r="B36" s="110"/>
       <c r="C36" s="47" t="str">
-        <f>master!C26</f>
-        <v>８．事業構成</v>
-      </c>
-      <c r="D36" s="100" t="s">
-        <v>114</v>
-      </c>
-      <c r="E36" s="101"/>
-      <c r="F36" s="102"/>
+        <f>master!C27</f>
+        <v>９．提供価値</v>
+      </c>
+      <c r="D36" s="103" t="s">
+        <v>107</v>
+      </c>
+      <c r="E36" s="104"/>
+      <c r="F36" s="105"/>
       <c r="G36" s="47" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="H36" s="12"/>
       <c r="I36" s="45" t="s">
@@ -4226,20 +4597,20 @@
       <c r="M36" s="6"/>
       <c r="N36" s="6"/>
     </row>
-    <row r="37" spans="1:14" ht="37.799999999999997">
+    <row r="37" spans="1:14" ht="63">
       <c r="A37" s="11"/>
-      <c r="B37" s="98"/>
+      <c r="B37" s="110"/>
       <c r="C37" s="47" t="str">
-        <f>master!C27</f>
-        <v>９．提供価値</v>
-      </c>
-      <c r="D37" s="100" t="s">
-        <v>124</v>
-      </c>
-      <c r="E37" s="101"/>
-      <c r="F37" s="102"/>
+        <f>master!C28</f>
+        <v>１０．収益モデル</v>
+      </c>
+      <c r="D37" s="103" t="s">
+        <v>100</v>
+      </c>
+      <c r="E37" s="104"/>
+      <c r="F37" s="105"/>
       <c r="G37" s="47" t="s">
-        <v>115</v>
+        <v>99</v>
       </c>
       <c r="H37" s="12"/>
       <c r="I37" s="45" t="s">
@@ -4255,18 +4626,18 @@
     </row>
     <row r="38" spans="1:14" ht="63">
       <c r="A38" s="11"/>
-      <c r="B38" s="98"/>
+      <c r="B38" s="110"/>
       <c r="C38" s="47" t="str">
-        <f>master!C28</f>
-        <v>１０．収益モデル</v>
-      </c>
-      <c r="D38" s="100" t="s">
-        <v>117</v>
-      </c>
-      <c r="E38" s="101"/>
-      <c r="F38" s="102"/>
+        <f>master!C29</f>
+        <v>１１．リスク・課題</v>
+      </c>
+      <c r="D38" s="103" t="s">
+        <v>108</v>
+      </c>
+      <c r="E38" s="104"/>
+      <c r="F38" s="105"/>
       <c r="G38" s="47" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="H38" s="12"/>
       <c r="I38" s="45" t="s">
@@ -4280,388 +4651,671 @@
       <c r="M38" s="6"/>
       <c r="N38" s="6"/>
     </row>
-    <row r="39" spans="1:14" ht="63">
+    <row r="39" spans="1:14" ht="37.799999999999997">
       <c r="A39" s="11"/>
-      <c r="B39" s="98"/>
+      <c r="B39" s="111"/>
       <c r="C39" s="47" t="str">
-        <f>master!C29</f>
-        <v>１１．リスク・課題</v>
-      </c>
-      <c r="D39" s="100" t="s">
-        <v>125</v>
-      </c>
-      <c r="E39" s="101"/>
-      <c r="F39" s="102"/>
+        <f>master!C30</f>
+        <v>１２．今後の展望</v>
+      </c>
+      <c r="D39" s="103" t="s">
+        <v>109</v>
+      </c>
+      <c r="E39" s="104"/>
+      <c r="F39" s="105"/>
       <c r="G39" s="47" t="s">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="H39" s="12"/>
       <c r="I39" s="45" t="s">
         <v>24</v>
       </c>
       <c r="J39" s="43">
-        <v>1.3888888888888889E-3</v>
+        <v>6.9444444444444447E-4</v>
       </c>
       <c r="K39" s="40"/>
       <c r="L39" s="6"/>
       <c r="M39" s="6"/>
       <c r="N39" s="6"/>
     </row>
-    <row r="40" spans="1:14" ht="37.799999999999997">
+    <row r="40" spans="1:14" ht="88.2">
       <c r="A40" s="11"/>
-      <c r="B40" s="99"/>
-      <c r="C40" s="47" t="str">
-        <f>master!C30</f>
-        <v>１２．今後の展望</v>
-      </c>
-      <c r="D40" s="100" t="s">
-        <v>126</v>
-      </c>
-      <c r="E40" s="101"/>
-      <c r="F40" s="102"/>
-      <c r="G40" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="H40" s="12"/>
-      <c r="I40" s="45" t="s">
+      <c r="B40" s="112" t="str">
+        <f>master!B32</f>
+        <v>提案演習の全体像</v>
+      </c>
+      <c r="C40" s="64" t="str">
+        <f>master!C32</f>
+        <v>提案演習の全体像について</v>
+      </c>
+      <c r="D40" s="97" t="s">
+        <v>139</v>
+      </c>
+      <c r="E40" s="98"/>
+      <c r="F40" s="99"/>
+      <c r="G40" s="64" t="s">
+        <v>131</v>
+      </c>
+      <c r="H40" s="65"/>
+      <c r="I40" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J40" s="43">
+      <c r="J40" s="67">
         <v>6.9444444444444447E-4</v>
       </c>
-      <c r="K40" s="40"/>
+      <c r="K40" s="68"/>
       <c r="L40" s="6"/>
       <c r="M40" s="6"/>
       <c r="N40" s="6"/>
     </row>
-    <row r="41" spans="1:14" ht="113.4">
+    <row r="41" spans="1:14" ht="201.6">
       <c r="A41" s="11"/>
-      <c r="B41" s="106" t="str">
-        <f>master!B32</f>
-        <v>個人演習1</v>
-      </c>
-      <c r="C41" s="65" t="str">
-        <f>master!C32</f>
-        <v>演習内容の説明</v>
-      </c>
-      <c r="D41" s="103" t="s">
-        <v>99</v>
-      </c>
-      <c r="E41" s="104"/>
-      <c r="F41" s="105"/>
-      <c r="G41" s="65" t="s">
-        <v>86</v>
-      </c>
-      <c r="H41" s="66"/>
-      <c r="I41" s="67" t="s">
+      <c r="B41" s="113" t="str">
+        <f>master!B33</f>
+        <v>提案資料</v>
+      </c>
+      <c r="C41" s="64" t="str">
+        <f>master!C33</f>
+        <v>提案資料について</v>
+      </c>
+      <c r="D41" s="97" t="s">
+        <v>157</v>
+      </c>
+      <c r="E41" s="98"/>
+      <c r="F41" s="99"/>
+      <c r="G41" s="64" t="s">
+        <v>80</v>
+      </c>
+      <c r="H41" s="65"/>
+      <c r="I41" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J41" s="68">
+      <c r="J41" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K41" s="69"/>
+      <c r="K41" s="68"/>
       <c r="L41" s="6"/>
       <c r="M41" s="6"/>
       <c r="N41" s="6"/>
     </row>
-    <row r="42" spans="1:14" ht="201.6">
+    <row r="42" spans="1:14" ht="163.80000000000001">
       <c r="A42" s="11"/>
-      <c r="B42" s="107"/>
-      <c r="C42" s="65" t="str">
-        <f>master!C33</f>
-        <v>演習成果物の説明</v>
-      </c>
-      <c r="D42" s="103" t="s">
-        <v>127</v>
-      </c>
-      <c r="E42" s="104"/>
-      <c r="F42" s="105"/>
-      <c r="G42" s="65" t="s">
-        <v>88</v>
-      </c>
-      <c r="H42" s="66"/>
-      <c r="I42" s="67" t="s">
+      <c r="B42" s="100" t="str">
+        <f>master!B34</f>
+        <v>提案資料の作成</v>
+      </c>
+      <c r="C42" s="64" t="str">
+        <f>master!C34</f>
+        <v>提案テーマの検討</v>
+      </c>
+      <c r="D42" s="97" t="s">
+        <v>146</v>
+      </c>
+      <c r="E42" s="98"/>
+      <c r="F42" s="99"/>
+      <c r="G42" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="H42" s="65"/>
+      <c r="I42" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J42" s="68">
+      <c r="J42" s="67">
         <v>1.3888888888888889E-3</v>
       </c>
-      <c r="K42" s="69"/>
+      <c r="K42" s="68"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
       <c r="N42" s="6"/>
     </row>
-    <row r="43" spans="1:14" ht="176.4">
+    <row r="43" spans="1:14" ht="138.6">
       <c r="A43" s="11"/>
-      <c r="B43" s="107"/>
-      <c r="C43" s="65" t="str">
-        <f>master!C34</f>
-        <v>サービスの検討</v>
-      </c>
-      <c r="D43" s="103" t="s">
-        <v>97</v>
-      </c>
-      <c r="E43" s="104"/>
-      <c r="F43" s="105"/>
-      <c r="G43" s="65" t="s">
-        <v>90</v>
-      </c>
-      <c r="H43" s="66"/>
-      <c r="I43" s="67" t="s">
+      <c r="B43" s="101"/>
+      <c r="C43" s="64" t="str">
+        <f>master!C35</f>
+        <v>提案テーマの意見交換</v>
+      </c>
+      <c r="D43" s="97" t="s">
+        <v>147</v>
+      </c>
+      <c r="E43" s="98"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="64" t="s">
+        <v>81</v>
+      </c>
+      <c r="H43" s="65"/>
+      <c r="I43" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J43" s="68">
-        <v>1.3888888888888888E-2</v>
-      </c>
-      <c r="K43" s="69"/>
+      <c r="J43" s="67">
+        <v>1.3888888888888889E-3</v>
+      </c>
+      <c r="K43" s="68"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
       <c r="N43" s="6"/>
     </row>
-    <row r="44" spans="1:14" ht="138.6">
+    <row r="44" spans="1:14" ht="75.599999999999994">
       <c r="A44" s="11"/>
-      <c r="B44" s="107"/>
-      <c r="C44" s="65" t="str">
-        <f>master!C35</f>
-        <v>サービスのブラッシュアップ</v>
-      </c>
-      <c r="D44" s="103" t="s">
-        <v>96</v>
-      </c>
-      <c r="E44" s="104"/>
-      <c r="F44" s="105"/>
-      <c r="G44" s="65" t="s">
-        <v>92</v>
-      </c>
-      <c r="H44" s="66"/>
-      <c r="I44" s="67" t="s">
+      <c r="B44" s="101"/>
+      <c r="C44" s="64" t="str">
+        <f>master!C36</f>
+        <v>提案テーマの調査</v>
+      </c>
+      <c r="D44" s="97" t="s">
+        <v>134</v>
+      </c>
+      <c r="E44" s="98"/>
+      <c r="F44" s="99"/>
+      <c r="G44" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="H44" s="65"/>
+      <c r="I44" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J44" s="68">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K44" s="69"/>
+      <c r="J44" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K44" s="68"/>
       <c r="L44" s="6"/>
       <c r="M44" s="6"/>
       <c r="N44" s="6"/>
     </row>
-    <row r="45" spans="1:14" ht="63">
+    <row r="45" spans="1:14" ht="88.2">
       <c r="A45" s="11"/>
-      <c r="B45" s="107"/>
-      <c r="C45" s="65" t="str">
-        <f>master!C36</f>
-        <v>サービスの決定</v>
-      </c>
-      <c r="D45" s="103" t="s">
-        <v>95</v>
-      </c>
-      <c r="E45" s="104"/>
-      <c r="F45" s="105"/>
-      <c r="G45" s="65" t="s">
-        <v>89</v>
-      </c>
-      <c r="H45" s="66"/>
-      <c r="I45" s="67" t="s">
+      <c r="B45" s="101"/>
+      <c r="C45" s="64" t="str">
+        <f>master!C37</f>
+        <v>提案内容の具体化</v>
+      </c>
+      <c r="D45" s="97" t="s">
+        <v>133</v>
+      </c>
+      <c r="E45" s="98"/>
+      <c r="F45" s="99"/>
+      <c r="G45" s="64" t="s">
+        <v>131</v>
+      </c>
+      <c r="H45" s="65"/>
+      <c r="I45" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J45" s="68">
-        <v>2.0833333333333332E-2</v>
-      </c>
-      <c r="K45" s="69"/>
+      <c r="J45" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K45" s="68"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
       <c r="N45" s="6"/>
     </row>
-    <row r="46" spans="1:14" ht="138.6">
+    <row r="46" spans="1:14" ht="151.19999999999999">
       <c r="A46" s="11"/>
-      <c r="B46" s="107"/>
-      <c r="C46" s="65" t="str">
-        <f>master!C37</f>
-        <v>成果物の作成</v>
-      </c>
-      <c r="D46" s="103" t="s">
-        <v>94</v>
-      </c>
-      <c r="E46" s="104"/>
-      <c r="F46" s="105"/>
-      <c r="G46" s="65" t="s">
-        <v>92</v>
-      </c>
-      <c r="H46" s="66"/>
-      <c r="I46" s="67" t="s">
+      <c r="B46" s="101"/>
+      <c r="C46" s="64" t="str">
+        <f>master!C38</f>
+        <v>提案資料の作成</v>
+      </c>
+      <c r="D46" s="97" t="s">
+        <v>135</v>
+      </c>
+      <c r="E46" s="98"/>
+      <c r="F46" s="99"/>
+      <c r="G46" s="64" t="s">
+        <v>148</v>
+      </c>
+      <c r="H46" s="65"/>
+      <c r="I46" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J46" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="K46" s="69"/>
+      <c r="J46" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K46" s="68"/>
       <c r="L46" s="6"/>
       <c r="M46" s="6"/>
       <c r="N46" s="6"/>
     </row>
     <row r="47" spans="1:14" ht="25.2">
       <c r="A47" s="11"/>
-      <c r="B47" s="108"/>
-      <c r="C47" s="65" t="str">
-        <f>master!C38</f>
-        <v>成果物の提出</v>
-      </c>
-      <c r="D47" s="103" t="s">
-        <v>93</v>
-      </c>
-      <c r="E47" s="104"/>
-      <c r="F47" s="105"/>
-      <c r="G47" s="65" t="s">
-        <v>98</v>
-      </c>
-      <c r="H47" s="66"/>
-      <c r="I47" s="67" t="s">
+      <c r="B47" s="101"/>
+      <c r="C47" s="64" t="str">
+        <f>master!C39</f>
+        <v>提案資料の提出</v>
+      </c>
+      <c r="D47" s="97" t="s">
+        <v>158</v>
+      </c>
+      <c r="E47" s="98"/>
+      <c r="F47" s="99"/>
+      <c r="G47" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="H47" s="65"/>
+      <c r="I47" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J47" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="K47" s="69"/>
+      <c r="J47" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K47" s="68"/>
       <c r="L47" s="6"/>
       <c r="M47" s="6"/>
       <c r="N47" s="6"/>
     </row>
-    <row r="48" spans="1:14" ht="88.2">
+    <row r="48" spans="1:14" ht="25.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="106" t="str">
-        <f>master!B40</f>
-        <v>個人演習2</v>
-      </c>
-      <c r="C48" s="65" t="str">
+      <c r="B48" s="101"/>
+      <c r="C48" s="64" t="str">
         <f>master!C40</f>
-        <v>演習内容の説明</v>
-      </c>
-      <c r="D48" s="103" t="s">
-        <v>147</v>
-      </c>
-      <c r="E48" s="104"/>
-      <c r="F48" s="105"/>
-      <c r="G48" s="65" t="s">
-        <v>145</v>
-      </c>
-      <c r="H48" s="66"/>
-      <c r="I48" s="67" t="s">
+        <v>演習の実施</v>
+      </c>
+      <c r="D48" s="97"/>
+      <c r="E48" s="98"/>
+      <c r="F48" s="99"/>
+      <c r="G48" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="H48" s="65"/>
+      <c r="I48" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J48" s="68">
-        <v>2.0833333333333333E-3</v>
-      </c>
-      <c r="K48" s="69"/>
+      <c r="J48" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="K48" s="68"/>
       <c r="L48" s="6"/>
       <c r="M48" s="6"/>
       <c r="N48" s="6"/>
     </row>
     <row r="49" spans="1:14" ht="88.2">
       <c r="A49" s="11"/>
-      <c r="B49" s="107"/>
-      <c r="C49" s="65" t="str">
+      <c r="B49" s="100" t="str">
+        <f>master!B41</f>
+        <v>提案の実施</v>
+      </c>
+      <c r="C49" s="64" t="str">
         <f>master!C41</f>
-        <v>個人提案の実施</v>
-      </c>
-      <c r="D49" s="103" t="s">
-        <v>149</v>
-      </c>
-      <c r="E49" s="104"/>
-      <c r="F49" s="105"/>
-      <c r="G49" s="65" t="s">
-        <v>145</v>
-      </c>
-      <c r="H49" s="66"/>
-      <c r="I49" s="67" t="s">
+        <v>提案の実施の説明</v>
+      </c>
+      <c r="D49" s="97" t="s">
+        <v>136</v>
+      </c>
+      <c r="E49" s="98"/>
+      <c r="F49" s="99"/>
+      <c r="G49" s="64" t="s">
+        <v>131</v>
+      </c>
+      <c r="H49" s="65"/>
+      <c r="I49" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J49" s="68">
-        <v>6.25E-2</v>
-      </c>
-      <c r="K49" s="69"/>
+      <c r="J49" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K49" s="68"/>
       <c r="L49" s="6"/>
       <c r="M49" s="6"/>
       <c r="N49" s="6"/>
     </row>
     <row r="50" spans="1:14" ht="25.2">
       <c r="A50" s="11"/>
-      <c r="B50" s="108"/>
-      <c r="C50" s="65" t="str">
+      <c r="B50" s="101"/>
+      <c r="C50" s="64" t="str">
         <f>master!C42</f>
-        <v>提案内容のブラッシュアップ</v>
-      </c>
-      <c r="D50" s="103" t="s">
-        <v>148</v>
-      </c>
-      <c r="E50" s="104"/>
-      <c r="F50" s="105"/>
-      <c r="G50" s="65" t="s">
-        <v>132</v>
-      </c>
-      <c r="H50" s="66"/>
-      <c r="I50" s="67" t="s">
+        <v>発表順の決定</v>
+      </c>
+      <c r="D50" s="97" t="s">
+        <v>149</v>
+      </c>
+      <c r="E50" s="98"/>
+      <c r="F50" s="99"/>
+      <c r="G50" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="H50" s="65"/>
+      <c r="I50" s="66" t="s">
         <v>24</v>
       </c>
-      <c r="J50" s="68" t="s">
-        <v>119</v>
-      </c>
-      <c r="K50" s="69"/>
+      <c r="J50" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K50" s="68"/>
       <c r="L50" s="6"/>
       <c r="M50" s="6"/>
       <c r="N50" s="6"/>
     </row>
+    <row r="51" spans="1:14" ht="25.2">
+      <c r="A51" s="11"/>
+      <c r="B51" s="101"/>
+      <c r="C51" s="64" t="str">
+        <f>master!C43</f>
+        <v>提案の実施</v>
+      </c>
+      <c r="D51" s="97" t="s">
+        <v>160</v>
+      </c>
+      <c r="E51" s="98"/>
+      <c r="F51" s="99"/>
+      <c r="G51" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="H51" s="65"/>
+      <c r="I51" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J51" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K51" s="68"/>
+      <c r="L51" s="6"/>
+      <c r="M51" s="6"/>
+      <c r="N51" s="6"/>
+    </row>
+    <row r="52" spans="1:14" ht="25.2">
+      <c r="A52" s="11"/>
+      <c r="B52" s="101"/>
+      <c r="C52" s="64" t="str">
+        <f>master!C44</f>
+        <v>提案のフィードバック</v>
+      </c>
+      <c r="D52" s="97" t="s">
+        <v>161</v>
+      </c>
+      <c r="E52" s="98"/>
+      <c r="F52" s="99"/>
+      <c r="G52" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="H52" s="65"/>
+      <c r="I52" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J52" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K52" s="68"/>
+      <c r="L52" s="6"/>
+      <c r="M52" s="6"/>
+      <c r="N52" s="6"/>
+    </row>
+    <row r="53" spans="1:14" ht="25.2">
+      <c r="A53" s="11"/>
+      <c r="B53" s="102"/>
+      <c r="C53" s="64" t="str">
+        <f>master!C45</f>
+        <v>演習の実施</v>
+      </c>
+      <c r="D53" s="97"/>
+      <c r="E53" s="98"/>
+      <c r="F53" s="99"/>
+      <c r="G53" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="H53" s="65"/>
+      <c r="I53" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J53" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="K53" s="68"/>
+      <c r="L53" s="6"/>
+      <c r="M53" s="6"/>
+      <c r="N53" s="6"/>
+    </row>
+    <row r="54" spans="1:14" ht="113.4">
+      <c r="A54" s="11"/>
+      <c r="B54" s="100" t="str">
+        <f>master!B46</f>
+        <v>提案の改善</v>
+      </c>
+      <c r="C54" s="64" t="str">
+        <f>master!C46</f>
+        <v>演習内容の説明</v>
+      </c>
+      <c r="D54" s="97" t="s">
+        <v>159</v>
+      </c>
+      <c r="E54" s="98"/>
+      <c r="F54" s="99"/>
+      <c r="G54" s="64" t="s">
+        <v>79</v>
+      </c>
+      <c r="H54" s="65"/>
+      <c r="I54" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J54" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K54" s="68"/>
+      <c r="L54" s="6"/>
+      <c r="M54" s="6"/>
+      <c r="N54" s="6"/>
+    </row>
+    <row r="55" spans="1:14" ht="25.2">
+      <c r="A55" s="11"/>
+      <c r="B55" s="101"/>
+      <c r="C55" s="64" t="str">
+        <f>master!C47</f>
+        <v>フィードバック内容の整理</v>
+      </c>
+      <c r="D55" s="97" t="s">
+        <v>162</v>
+      </c>
+      <c r="E55" s="98"/>
+      <c r="F55" s="99"/>
+      <c r="G55" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="H55" s="65"/>
+      <c r="I55" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J55" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K55" s="68"/>
+      <c r="L55" s="6"/>
+      <c r="M55" s="6"/>
+      <c r="N55" s="6"/>
+    </row>
+    <row r="56" spans="1:14" ht="25.2">
+      <c r="A56" s="11"/>
+      <c r="B56" s="101"/>
+      <c r="C56" s="64" t="str">
+        <f>master!C48</f>
+        <v>提案資料の修正</v>
+      </c>
+      <c r="D56" s="97" t="s">
+        <v>163</v>
+      </c>
+      <c r="E56" s="98"/>
+      <c r="F56" s="99"/>
+      <c r="G56" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="H56" s="65"/>
+      <c r="I56" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J56" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K56" s="68"/>
+      <c r="L56" s="6"/>
+      <c r="M56" s="6"/>
+      <c r="N56" s="6"/>
+    </row>
+    <row r="57" spans="1:14" ht="25.2">
+      <c r="A57" s="11"/>
+      <c r="B57" s="101"/>
+      <c r="C57" s="64" t="str">
+        <f>master!C49</f>
+        <v>提案資料の確認</v>
+      </c>
+      <c r="D57" s="97" t="s">
+        <v>164</v>
+      </c>
+      <c r="E57" s="98"/>
+      <c r="F57" s="99"/>
+      <c r="G57" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="H57" s="65"/>
+      <c r="I57" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J57" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K57" s="68"/>
+      <c r="L57" s="6"/>
+      <c r="M57" s="6"/>
+      <c r="N57" s="6"/>
+    </row>
+    <row r="58" spans="1:14" ht="25.2">
+      <c r="A58" s="11"/>
+      <c r="B58" s="101"/>
+      <c r="C58" s="64" t="str">
+        <f>master!C50</f>
+        <v>提案資料の提出</v>
+      </c>
+      <c r="D58" s="97" t="s">
+        <v>158</v>
+      </c>
+      <c r="E58" s="98"/>
+      <c r="F58" s="99"/>
+      <c r="G58" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="H58" s="65"/>
+      <c r="I58" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J58" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K58" s="68"/>
+      <c r="L58" s="6"/>
+      <c r="M58" s="6"/>
+      <c r="N58" s="6"/>
+    </row>
+    <row r="59" spans="1:14" ht="25.2">
+      <c r="A59" s="11"/>
+      <c r="B59" s="101"/>
+      <c r="C59" s="64" t="str">
+        <f>master!C51</f>
+        <v>最終発表の準備</v>
+      </c>
+      <c r="D59" s="97"/>
+      <c r="E59" s="98"/>
+      <c r="F59" s="99"/>
+      <c r="G59" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="H59" s="65"/>
+      <c r="I59" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J59" s="67">
+        <v>6.9444444444444447E-4</v>
+      </c>
+      <c r="K59" s="68"/>
+      <c r="L59" s="6"/>
+      <c r="M59" s="6"/>
+      <c r="N59" s="6"/>
+    </row>
+    <row r="60" spans="1:14" ht="25.2">
+      <c r="A60" s="11"/>
+      <c r="B60" s="102"/>
+      <c r="C60" s="64" t="str">
+        <f>master!C52</f>
+        <v>演習の実施</v>
+      </c>
+      <c r="D60" s="97"/>
+      <c r="E60" s="98"/>
+      <c r="F60" s="99"/>
+      <c r="G60" s="64" t="s">
+        <v>82</v>
+      </c>
+      <c r="H60" s="65"/>
+      <c r="I60" s="66" t="s">
+        <v>24</v>
+      </c>
+      <c r="J60" s="67" t="s">
+        <v>102</v>
+      </c>
+      <c r="K60" s="68"/>
+      <c r="L60" s="6"/>
+      <c r="M60" s="6"/>
+      <c r="N60" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="50">
-    <mergeCell ref="D48:F48"/>
+  <mergeCells count="62">
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="B54:B60"/>
+    <mergeCell ref="B49:B53"/>
+    <mergeCell ref="D59:F59"/>
+    <mergeCell ref="B15:B26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B27:B39"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="B42:B48"/>
     <mergeCell ref="D47:F47"/>
-    <mergeCell ref="D49:F49"/>
-    <mergeCell ref="B48:B50"/>
-    <mergeCell ref="B41:B47"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D41:F41"/>
     <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D17:F17"/>
+    <mergeCell ref="D38:F38"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="D23:F23"/>
+    <mergeCell ref="D24:F24"/>
+    <mergeCell ref="D25:F25"/>
     <mergeCell ref="D33:F33"/>
     <mergeCell ref="D34:F34"/>
     <mergeCell ref="D35:F35"/>
     <mergeCell ref="D36:F36"/>
     <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D13:F14"/>
-    <mergeCell ref="G13:G14"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="B16:B27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="B28:B40"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="D49:F49"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D60:F60"/>
     <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D41:F41"/>
     <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D51:F51"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4674,7 +5328,7 @@
           <x14:formula1>
             <xm:f>master!#REF!</xm:f>
           </x14:formula1>
-          <xm:sqref>H15:H50</xm:sqref>
+          <xm:sqref>H14:H60</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4684,7 +5338,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:C43"/>
+  <dimension ref="B1:C52"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="4.6640625" customWidth="1"/>
@@ -4698,229 +5352,286 @@
       </c>
     </row>
     <row r="2" spans="2:3">
-      <c r="B2" s="63" t="s">
+      <c r="B2" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="C2" s="63" t="s">
+      <c r="C2" s="62" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="3" spans="2:3">
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="63"/>
     </row>
     <row r="4" spans="2:3">
       <c r="B4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="2:3">
       <c r="B5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:3">
       <c r="C6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="2:3">
       <c r="C7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="2:3">
       <c r="C8" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="2:3">
       <c r="C9" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="2:3">
       <c r="C10" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="11" spans="2:3">
       <c r="C11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="12" spans="2:3">
       <c r="C12" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="13" spans="2:3">
       <c r="C13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="2:3">
       <c r="C14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="2:3">
       <c r="C15" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="16" spans="2:3">
       <c r="B16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C16" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="17" spans="2:3">
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
+      <c r="B17" s="63"/>
+      <c r="C17" s="63"/>
     </row>
     <row r="18" spans="2:3">
       <c r="B18" t="s">
-        <v>120</v>
-      </c>
-      <c r="C18" s="70" t="s">
-        <v>130</v>
+        <v>103</v>
+      </c>
+      <c r="C18" s="69" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="C19" s="70" t="s">
+      <c r="C19" s="69" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="2:3">
+      <c r="C20" s="69" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="20" spans="2:3">
-      <c r="C20" s="70" t="s">
+    <row r="21" spans="2:3">
+      <c r="C21" s="69" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="21" spans="2:3">
-      <c r="C21" s="70" t="s">
+    <row r="22" spans="2:3">
+      <c r="C22" s="69" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" spans="2:3">
-      <c r="C22" s="70" t="s">
+    <row r="23" spans="2:3">
+      <c r="C23" s="69" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" spans="2:3">
-      <c r="C23" s="70" t="s">
+    <row r="24" spans="2:3">
+      <c r="C24" s="69" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="24" spans="2:3">
-      <c r="C24" s="70" t="s">
+    <row r="25" spans="2:3">
+      <c r="C25" s="70" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="25" spans="2:3">
-      <c r="C25" s="71" t="s">
+    <row r="26" spans="2:3">
+      <c r="C26" s="69" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="2:3">
-      <c r="C26" s="70" t="s">
+    <row r="27" spans="2:3">
+      <c r="C27" s="69" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="27" spans="2:3">
-      <c r="C27" s="70" t="s">
+    <row r="28" spans="2:3">
+      <c r="C28" s="69" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="28" spans="2:3">
-      <c r="C28" s="70" t="s">
+    <row r="29" spans="2:3">
+      <c r="C29" s="69" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="29" spans="2:3">
-      <c r="C29" s="70" t="s">
+    <row r="30" spans="2:3">
+      <c r="C30" s="69" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="30" spans="2:3">
-      <c r="C30" s="70" t="s">
-        <v>75</v>
-      </c>
-    </row>
     <row r="31" spans="2:3">
-      <c r="B31" s="64"/>
-      <c r="C31" s="64"/>
+      <c r="B31" s="63"/>
+      <c r="C31" s="63"/>
     </row>
     <row r="32" spans="2:3">
       <c r="B32" t="s">
-        <v>139</v>
-      </c>
-      <c r="C32" s="70" t="s">
-        <v>76</v>
+        <v>144</v>
+      </c>
+      <c r="C32" s="69" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="33" spans="2:3">
-      <c r="C33" s="70" t="s">
-        <v>87</v>
+      <c r="B33" t="s">
+        <v>155</v>
+      </c>
+      <c r="C33" s="69" t="s">
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="2:3">
-      <c r="C34" s="70" t="s">
-        <v>82</v>
+      <c r="B34" t="s">
+        <v>137</v>
+      </c>
+      <c r="C34" s="69" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="35" spans="2:3">
-      <c r="C35" s="70" t="s">
-        <v>91</v>
+      <c r="C35" s="69" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="2:3">
-      <c r="C36" t="s">
-        <v>83</v>
+      <c r="C36" s="69" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="37" spans="2:3">
       <c r="C37" t="s">
-        <v>84</v>
+        <v>128</v>
       </c>
     </row>
     <row r="38" spans="2:3">
       <c r="C38" t="s">
-        <v>85</v>
+        <v>151</v>
       </c>
     </row>
     <row r="39" spans="2:3">
-      <c r="B39" s="64"/>
-      <c r="C39" s="64"/>
+      <c r="C39" t="s">
+        <v>152</v>
+      </c>
     </row>
     <row r="40" spans="2:3">
-      <c r="B40" t="s">
+      <c r="C40" s="69" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3">
+      <c r="B41" t="s">
+        <v>123</v>
+      </c>
+      <c r="C41" s="69" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3">
+      <c r="C42" s="69" t="s">
         <v>140</v>
       </c>
-      <c r="C40" s="70" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3">
-      <c r="C41" s="70" t="s">
+    </row>
+    <row r="43" spans="2:3">
+      <c r="C43" s="69" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3">
+      <c r="C44" s="69" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3">
+      <c r="C45" s="69" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3">
+      <c r="B46" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" s="69" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="47" spans="2:3">
+      <c r="C47" s="69" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="48" spans="2:3">
+      <c r="C48" s="69" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" spans="3:3">
+      <c r="C49" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="50" spans="3:3">
+      <c r="C50" s="69" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="51" spans="3:3">
+      <c r="C51" s="69" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="42" spans="2:3">
-      <c r="C42" s="70" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3">
-      <c r="C43" s="70"/>
+    <row r="52" spans="3:3">
+      <c r="C52" s="69" t="s">
+        <v>150</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>

--- a/IG/7日版/AI Native-提案演習_IG.xlsx
+++ b/IG/7日版/AI Native-提案演習_IG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\myrepo\ai_navive\IG\7日版\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C12445E-6676-4B14-BA5E-FABBA54CAF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AEF868D3-98F8-4C59-BE87-DF2B87002593}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="860" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,6 +24,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">特記イベント!$A$1:$L$15</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
@@ -88,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="168">
   <si>
     <t>1 日目</t>
     <rPh sb="2" eb="3">
@@ -1435,10 +1436,6 @@
     <rPh sb="5" eb="8">
       <t>ゼンタイゾウ</t>
     </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
-    <t>提案演習の全体像について</t>
     <phoneticPr fontId="3"/>
   </si>
   <si>
@@ -1591,25 +1588,6 @@
     <phoneticPr fontId="3"/>
   </si>
   <si>
-    <t>提案資料を指定の場所に納品することを説明する。</t>
-    <rPh sb="0" eb="2">
-      <t>テイアン</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>シテイ</t>
-    </rPh>
-    <rPh sb="8" eb="10">
-      <t>バショ</t>
-    </rPh>
-    <rPh sb="11" eb="13">
-      <t>ノウヒン</t>
-    </rPh>
-    <rPh sb="18" eb="20">
-      <t>セツメイ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
-  </si>
-  <si>
     <t xml:space="preserve">提案の実施の流れについて説明する。
 ■手順
 1. フィードバック内容の整理
@@ -1701,13 +1679,7 @@
       <t>イシキ</t>
     </rPh>
     <rPh sb="8" eb="10">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="58" eb="60">
-      <t>シュウセイ</t>
-    </rPh>
-    <rPh sb="65" eb="66">
-      <t>ツタ</t>
+      <t>シュウセイシュウセイツタ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -1749,6 +1721,84 @@
     </rPh>
     <rPh sb="22" eb="24">
       <t>ガイヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>提案資料を指定の場所に提出することを説明する。</t>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テイシュツ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セツメイ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t xml:space="preserve">・AI-03
+</t>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">提案資料を指定の場所に提出することを説明する。
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Meiryo UI"/>
+        <family val="3"/>
+        <charset val="128"/>
+      </rPr>
+      <t>※修正前の提案資料は不要。</t>
+    </r>
+    <rPh sb="0" eb="2">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>シテイ</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>バショ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>テイシュツ</t>
+    </rPh>
+    <rPh sb="18" eb="20">
+      <t>セツメイ</t>
+    </rPh>
+    <rPh sb="25" eb="27">
+      <t>シュウセイ</t>
+    </rPh>
+    <rPh sb="27" eb="28">
+      <t>マエ</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>テイアン</t>
+    </rPh>
+    <rPh sb="31" eb="33">
+      <t>シリョウ</t>
+    </rPh>
+    <rPh sb="34" eb="36">
+      <t>フヨウ</t>
+    </rPh>
+    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>研修の全体像について</t>
+    <rPh sb="0" eb="2">
+      <t>ケンシュウ</t>
     </rPh>
     <phoneticPr fontId="3"/>
   </si>
@@ -2448,6 +2498,36 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="20" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2508,6 +2588,15 @@
     <xf numFmtId="0" fontId="5" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2525,45 +2614,6 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" textRotation="255" wrapText="1"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="20" fontId="5" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -2941,15 +2991,15 @@
     </row>
     <row r="2" spans="1:7" ht="27">
       <c r="A2" s="13"/>
-      <c r="B2" s="83" t="str">
+      <c r="B2" s="93" t="str">
         <f>"コースプラン/インストラクションガイド 「"&amp;master!$B$1&amp;"_IG」"</f>
         <v>コースプラン/インストラクションガイド 「AI Native-提案演習_IG」</v>
       </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-      <c r="G2" s="83"/>
+      <c r="C2" s="93"/>
+      <c r="D2" s="93"/>
+      <c r="E2" s="93"/>
+      <c r="F2" s="93"/>
+      <c r="G2" s="93"/>
     </row>
     <row r="3" spans="1:7" ht="27.6" thickBot="1">
       <c r="A3" s="13"/>
@@ -2962,10 +3012,10 @@
     </row>
     <row r="4" spans="1:7" ht="27.6" thickBot="1">
       <c r="A4" s="13"/>
-      <c r="B4" s="84" t="s">
+      <c r="B4" s="94" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="85"/>
+      <c r="C4" s="95"/>
       <c r="D4" s="13"/>
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
@@ -2973,8 +3023,8 @@
     </row>
     <row r="5" spans="1:7" ht="27.6" thickBot="1">
       <c r="A5" s="13"/>
-      <c r="B5" s="86"/>
-      <c r="C5" s="87"/>
+      <c r="B5" s="96"/>
+      <c r="C5" s="97"/>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
@@ -2985,10 +3035,10 @@
       <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:7" ht="16.2">
-      <c r="B7" s="88" t="s">
+      <c r="B7" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="C7" s="88"/>
+      <c r="C7" s="98"/>
       <c r="D7" s="1"/>
       <c r="F7" s="1"/>
     </row>
@@ -3097,10 +3147,10 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="36"/>
-      <c r="B15" s="119" t="s">
+      <c r="B15" s="90" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="115"/>
+      <c r="C15" s="86"/>
       <c r="D15" s="55"/>
       <c r="E15" s="79"/>
       <c r="F15" s="55"/>
@@ -3113,11 +3163,11 @@
       <c r="B16" s="53">
         <v>0.45833333333333331</v>
       </c>
-      <c r="C16" s="121" t="str">
+      <c r="C16" s="92" t="str">
         <f>master!B32</f>
         <v>提案演習の全体像</v>
       </c>
-      <c r="D16" s="114"/>
+      <c r="D16" s="85"/>
       <c r="E16" s="79"/>
       <c r="F16" s="55"/>
       <c r="G16" s="79"/>
@@ -3125,11 +3175,11 @@
     <row r="17" spans="1:8">
       <c r="A17" s="49"/>
       <c r="B17" s="55"/>
-      <c r="C17" s="117" t="str">
+      <c r="C17" s="88" t="str">
         <f>master!B33</f>
         <v>提案資料</v>
       </c>
-      <c r="D17" s="114"/>
+      <c r="D17" s="85"/>
       <c r="E17" s="79"/>
       <c r="F17" s="55"/>
       <c r="G17" s="79"/>
@@ -3137,20 +3187,20 @@
     <row r="18" spans="1:8">
       <c r="A18" s="49"/>
       <c r="B18" s="55"/>
-      <c r="C18" s="117" t="str">
+      <c r="C18" s="88" t="str">
         <f>master!B34</f>
         <v>提案資料の作成</v>
       </c>
-      <c r="D18" s="114"/>
+      <c r="D18" s="85"/>
       <c r="E18" s="79"/>
       <c r="F18" s="55"/>
       <c r="G18" s="79"/>
     </row>
     <row r="19" spans="1:8">
-      <c r="A19" s="116"/>
+      <c r="A19" s="87"/>
       <c r="B19" s="55"/>
-      <c r="C19" s="117"/>
-      <c r="D19" s="114"/>
+      <c r="C19" s="88"/>
+      <c r="D19" s="85"/>
       <c r="E19" s="79"/>
       <c r="F19" s="55"/>
       <c r="G19" s="79"/>
@@ -3160,8 +3210,8 @@
         <v>0.5</v>
       </c>
       <c r="B20" s="55"/>
-      <c r="C20" s="117"/>
-      <c r="D20" s="114"/>
+      <c r="C20" s="88"/>
+      <c r="D20" s="85"/>
       <c r="E20" s="79"/>
       <c r="F20" s="55"/>
       <c r="G20" s="79"/>
@@ -3169,8 +3219,8 @@
     <row r="21" spans="1:8">
       <c r="A21" s="49"/>
       <c r="B21" s="38"/>
-      <c r="C21" s="118"/>
-      <c r="D21" s="120"/>
+      <c r="C21" s="89"/>
+      <c r="D21" s="91"/>
       <c r="E21" s="77"/>
       <c r="F21" s="74"/>
       <c r="G21" s="77"/>
@@ -3515,10 +3565,10 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:12" ht="16.2">
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="92"/>
+      <c r="C4" s="102"/>
       <c r="D4" s="8"/>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -3529,16 +3579,16 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:12" ht="36" customHeight="1">
-      <c r="B5" s="93"/>
-      <c r="C5" s="93"/>
-      <c r="D5" s="93"/>
-      <c r="E5" s="93"/>
-      <c r="F5" s="93"/>
-      <c r="G5" s="93"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="93"/>
-      <c r="J5" s="93"/>
-      <c r="K5" s="93"/>
+      <c r="B5" s="103"/>
+      <c r="C5" s="103"/>
+      <c r="D5" s="103"/>
+      <c r="E5" s="103"/>
+      <c r="F5" s="103"/>
+      <c r="G5" s="103"/>
+      <c r="H5" s="103"/>
+      <c r="I5" s="103"/>
+      <c r="J5" s="103"/>
+      <c r="K5" s="103"/>
     </row>
     <row r="6" spans="1:12">
       <c r="B6" s="10"/>
@@ -3553,10 +3603,10 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="94" t="s">
+      <c r="D7" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="94"/>
+      <c r="E7" s="104"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
@@ -3588,46 +3638,46 @@
     </row>
     <row r="10" spans="1:12">
       <c r="A10" s="10"/>
-      <c r="B10" s="91"/>
-      <c r="C10" s="91" t="s">
+      <c r="B10" s="101"/>
+      <c r="C10" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="D10" s="91" t="s">
+      <c r="D10" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="91"/>
-      <c r="F10" s="91"/>
-      <c r="G10" s="91" t="s">
+      <c r="E10" s="101"/>
+      <c r="F10" s="101"/>
+      <c r="G10" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="H10" s="95" t="s">
+      <c r="H10" s="105" t="s">
         <v>23</v>
       </c>
-      <c r="I10" s="90" t="s">
+      <c r="I10" s="100" t="s">
         <v>31</v>
       </c>
-      <c r="J10" s="90"/>
-      <c r="K10" s="90" t="s">
+      <c r="J10" s="100"/>
+      <c r="K10" s="100" t="s">
         <v>30</v>
       </c>
       <c r="L10" s="10"/>
     </row>
     <row r="11" spans="1:12">
       <c r="A11" s="10"/>
-      <c r="B11" s="91"/>
-      <c r="C11" s="91"/>
-      <c r="D11" s="91"/>
-      <c r="E11" s="91"/>
-      <c r="F11" s="91"/>
-      <c r="G11" s="91"/>
-      <c r="H11" s="96"/>
+      <c r="B11" s="101"/>
+      <c r="C11" s="101"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="101"/>
+      <c r="F11" s="101"/>
+      <c r="G11" s="101"/>
+      <c r="H11" s="106"/>
       <c r="I11" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J11" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K11" s="91"/>
+      <c r="K11" s="101"/>
       <c r="L11" s="10"/>
     </row>
     <row r="12" spans="1:12" ht="63">
@@ -3636,11 +3686,11 @@
       <c r="C12" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="D12" s="89" t="s">
+      <c r="D12" s="99" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="89"/>
-      <c r="F12" s="89"/>
+      <c r="E12" s="99"/>
+      <c r="F12" s="99"/>
       <c r="G12" s="80" t="s">
         <v>41</v>
       </c>
@@ -3660,11 +3710,11 @@
       <c r="C13" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="D13" s="89" t="s">
+      <c r="D13" s="99" t="s">
         <v>118</v>
       </c>
-      <c r="E13" s="89"/>
-      <c r="F13" s="89"/>
+      <c r="E13" s="99"/>
+      <c r="F13" s="99"/>
       <c r="G13" s="80" t="s">
         <v>119</v>
       </c>
@@ -3684,11 +3734,11 @@
       <c r="C14" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="D14" s="89" t="s">
+      <c r="D14" s="99" t="s">
         <v>121</v>
       </c>
-      <c r="E14" s="89"/>
-      <c r="F14" s="89"/>
+      <c r="E14" s="99"/>
+      <c r="F14" s="99"/>
       <c r="G14" s="80" t="s">
         <v>119</v>
       </c>
@@ -3789,12 +3839,12 @@
       <c r="M3" s="9"/>
     </row>
     <row r="4" spans="1:14" ht="16.2">
-      <c r="B4" s="92" t="s">
+      <c r="B4" s="102" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="92"/>
-      <c r="D4" s="92"/>
-      <c r="E4" s="92"/>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="7"/>
@@ -3805,16 +3855,16 @@
       <c r="M4" s="9"/>
     </row>
     <row r="5" spans="1:14" ht="36" customHeight="1">
-      <c r="B5" s="108"/>
-      <c r="C5" s="108"/>
-      <c r="D5" s="108"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="108"/>
-      <c r="G5" s="108"/>
-      <c r="H5" s="108"/>
-      <c r="I5" s="108"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="108"/>
+      <c r="B5" s="121"/>
+      <c r="C5" s="121"/>
+      <c r="D5" s="121"/>
+      <c r="E5" s="121"/>
+      <c r="F5" s="121"/>
+      <c r="G5" s="121"/>
+      <c r="H5" s="121"/>
+      <c r="I5" s="121"/>
+      <c r="J5" s="121"/>
+      <c r="K5" s="121"/>
       <c r="L5" s="26"/>
       <c r="M5" s="27"/>
     </row>
@@ -3834,10 +3884,10 @@
       <c r="C7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="94" t="s">
+      <c r="D7" s="104" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="94"/>
+      <c r="E7" s="104"/>
       <c r="F7" s="30" t="s">
         <v>10</v>
       </c>
@@ -3900,7 +3950,7 @@
         <v>42</v>
       </c>
       <c r="C10" s="33" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D10" s="42" t="s">
         <v>19</v>
@@ -3919,28 +3969,28 @@
     </row>
     <row r="12" spans="1:14" ht="24" customHeight="1">
       <c r="A12" s="10"/>
-      <c r="B12" s="91" t="s">
+      <c r="B12" s="101" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="91" t="s">
+      <c r="C12" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="91" t="s">
+      <c r="D12" s="101" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="91"/>
-      <c r="F12" s="91"/>
-      <c r="G12" s="91" t="s">
+      <c r="E12" s="101"/>
+      <c r="F12" s="101"/>
+      <c r="G12" s="101" t="s">
         <v>9</v>
       </c>
-      <c r="H12" s="90" t="s">
+      <c r="H12" s="100" t="s">
         <v>23</v>
       </c>
-      <c r="I12" s="106" t="s">
+      <c r="I12" s="119" t="s">
         <v>31</v>
       </c>
-      <c r="J12" s="107"/>
-      <c r="K12" s="90" t="s">
+      <c r="J12" s="120"/>
+      <c r="K12" s="100" t="s">
         <v>32</v>
       </c>
       <c r="L12" s="6"/>
@@ -3949,20 +3999,20 @@
     </row>
     <row r="13" spans="1:14">
       <c r="A13" s="10"/>
-      <c r="B13" s="91"/>
-      <c r="C13" s="91"/>
-      <c r="D13" s="91"/>
-      <c r="E13" s="91"/>
-      <c r="F13" s="91"/>
-      <c r="G13" s="91"/>
-      <c r="H13" s="90"/>
+      <c r="B13" s="101"/>
+      <c r="C13" s="101"/>
+      <c r="D13" s="101"/>
+      <c r="E13" s="101"/>
+      <c r="F13" s="101"/>
+      <c r="G13" s="101"/>
+      <c r="H13" s="100"/>
       <c r="I13" s="25" t="s">
         <v>25</v>
       </c>
       <c r="J13" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="K13" s="91"/>
+      <c r="K13" s="101"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
       <c r="N13" s="6"/>
@@ -3977,11 +4027,11 @@
         <f>master!C4</f>
         <v>はじめに　｜　“Be a social designer”とは</v>
       </c>
-      <c r="D14" s="103" t="s">
+      <c r="D14" s="116" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="104"/>
-      <c r="F14" s="105"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="118"/>
       <c r="G14" s="47" t="s">
         <v>83</v>
       </c>
@@ -3999,7 +4049,7 @@
     </row>
     <row r="15" spans="1:14" ht="63">
       <c r="A15" s="10"/>
-      <c r="B15" s="109" t="str">
+      <c r="B15" s="113" t="str">
         <f>master!B5</f>
         <v>企画提案のステップ</v>
       </c>
@@ -4007,11 +4057,11 @@
         <f>master!C5</f>
         <v>企画提案のステップ</v>
       </c>
-      <c r="D15" s="103" t="s">
+      <c r="D15" s="116" t="s">
         <v>85</v>
       </c>
-      <c r="E15" s="104"/>
-      <c r="F15" s="105"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="118"/>
       <c r="G15" s="47" t="s">
         <v>83</v>
       </c>
@@ -4029,16 +4079,16 @@
     </row>
     <row r="16" spans="1:14" ht="163.80000000000001">
       <c r="A16" s="11"/>
-      <c r="B16" s="110"/>
+      <c r="B16" s="114"/>
       <c r="C16" s="47" t="str">
         <f>master!C6</f>
         <v>STEP①-1　日常の不便を考える</v>
       </c>
-      <c r="D16" s="103" t="s">
+      <c r="D16" s="116" t="s">
         <v>115</v>
       </c>
-      <c r="E16" s="104"/>
-      <c r="F16" s="105"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="118"/>
       <c r="G16" s="47" t="s">
         <v>114</v>
       </c>
@@ -4056,16 +4106,16 @@
     </row>
     <row r="17" spans="1:14" ht="37.799999999999997">
       <c r="A17" s="11"/>
-      <c r="B17" s="110"/>
+      <c r="B17" s="114"/>
       <c r="C17" s="47" t="str">
         <f>master!C7</f>
         <v>STEP①-2　課題の深掘り</v>
       </c>
-      <c r="D17" s="103" t="s">
+      <c r="D17" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="E17" s="104"/>
-      <c r="F17" s="105"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="118"/>
       <c r="G17" s="47" t="s">
         <v>36</v>
       </c>
@@ -4083,16 +4133,16 @@
     </row>
     <row r="18" spans="1:14" ht="151.19999999999999">
       <c r="A18" s="11"/>
-      <c r="B18" s="110"/>
+      <c r="B18" s="114"/>
       <c r="C18" s="47" t="str">
         <f>master!C8</f>
         <v>STEP①-3　ITアイデアへ落とし込む</v>
       </c>
-      <c r="D18" s="103" t="s">
+      <c r="D18" s="116" t="s">
         <v>87</v>
       </c>
-      <c r="E18" s="104"/>
-      <c r="F18" s="105"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="118"/>
       <c r="G18" s="47" t="s">
         <v>43</v>
       </c>
@@ -4110,16 +4160,16 @@
     </row>
     <row r="19" spans="1:14" ht="252">
       <c r="A19" s="11"/>
-      <c r="B19" s="110"/>
+      <c r="B19" s="114"/>
       <c r="C19" s="47" t="str">
         <f>master!C9</f>
         <v>STEP②-1 創出したアイデアに関する調査・確認</v>
       </c>
-      <c r="D19" s="103" t="s">
+      <c r="D19" s="116" t="s">
         <v>88</v>
       </c>
-      <c r="E19" s="104"/>
-      <c r="F19" s="105"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="118"/>
       <c r="G19" s="47" t="s">
         <v>45</v>
       </c>
@@ -4137,16 +4187,16 @@
     </row>
     <row r="20" spans="1:14" ht="126">
       <c r="A20" s="11"/>
-      <c r="B20" s="110"/>
+      <c r="B20" s="114"/>
       <c r="C20" s="47" t="str">
         <f>master!C10</f>
         <v>STEP②-2 環境分析</v>
       </c>
-      <c r="D20" s="103" t="s">
+      <c r="D20" s="116" t="s">
         <v>89</v>
       </c>
-      <c r="E20" s="104"/>
-      <c r="F20" s="105"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="118"/>
       <c r="G20" s="47" t="s">
         <v>44</v>
       </c>
@@ -4164,16 +4214,16 @@
     </row>
     <row r="21" spans="1:14" ht="63">
       <c r="A21" s="11"/>
-      <c r="B21" s="110"/>
+      <c r="B21" s="114"/>
       <c r="C21" s="47" t="str">
         <f>master!C11</f>
         <v>（参考）PEST分析</v>
       </c>
-      <c r="D21" s="103" t="s">
+      <c r="D21" s="116" t="s">
         <v>90</v>
       </c>
-      <c r="E21" s="104"/>
-      <c r="F21" s="105"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="118"/>
       <c r="G21" s="47" t="s">
         <v>83</v>
       </c>
@@ -4191,16 +4241,16 @@
     </row>
     <row r="22" spans="1:14" ht="75.599999999999994">
       <c r="A22" s="11"/>
-      <c r="B22" s="110"/>
+      <c r="B22" s="114"/>
       <c r="C22" s="47" t="str">
         <f>master!C12</f>
         <v>（参考） 3C分析</v>
       </c>
-      <c r="D22" s="103" t="s">
+      <c r="D22" s="116" t="s">
         <v>91</v>
       </c>
-      <c r="E22" s="104"/>
-      <c r="F22" s="105"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="118"/>
       <c r="G22" s="47" t="s">
         <v>37</v>
       </c>
@@ -4218,16 +4268,16 @@
     </row>
     <row r="23" spans="1:14" ht="75.599999999999994">
       <c r="A23" s="11"/>
-      <c r="B23" s="110"/>
+      <c r="B23" s="114"/>
       <c r="C23" s="47" t="str">
         <f>master!C13</f>
         <v>（参考） SWOT分析</v>
       </c>
-      <c r="D23" s="103" t="s">
+      <c r="D23" s="116" t="s">
         <v>92</v>
       </c>
-      <c r="E23" s="104"/>
-      <c r="F23" s="105"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="118"/>
       <c r="G23" s="47" t="s">
         <v>37</v>
       </c>
@@ -4245,16 +4295,16 @@
     </row>
     <row r="24" spans="1:14" ht="113.4">
       <c r="A24" s="11"/>
-      <c r="B24" s="110"/>
+      <c r="B24" s="114"/>
       <c r="C24" s="47" t="str">
         <f>master!C14</f>
         <v>STEP③-1 提案書作成</v>
       </c>
-      <c r="D24" s="103" t="s">
+      <c r="D24" s="116" t="s">
         <v>93</v>
       </c>
-      <c r="E24" s="104"/>
-      <c r="F24" s="105"/>
+      <c r="E24" s="117"/>
+      <c r="F24" s="118"/>
       <c r="G24" s="47" t="s">
         <v>38</v>
       </c>
@@ -4272,16 +4322,16 @@
     </row>
     <row r="25" spans="1:14" ht="88.2">
       <c r="A25" s="11"/>
-      <c r="B25" s="110"/>
+      <c r="B25" s="114"/>
       <c r="C25" s="47" t="str">
         <f>master!C15</f>
         <v>STEP③-2 プロトタイプ作成</v>
       </c>
-      <c r="D25" s="103" t="s">
+      <c r="D25" s="116" t="s">
         <v>94</v>
       </c>
-      <c r="E25" s="104"/>
-      <c r="F25" s="105"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="118"/>
       <c r="G25" s="47" t="s">
         <v>39</v>
       </c>
@@ -4299,16 +4349,16 @@
     </row>
     <row r="26" spans="1:14" ht="113.4">
       <c r="A26" s="11"/>
-      <c r="B26" s="111"/>
+      <c r="B26" s="115"/>
       <c r="C26" s="47" t="str">
         <f>master!C16</f>
         <v>まとめ</v>
       </c>
-      <c r="D26" s="103" t="s">
+      <c r="D26" s="116" t="s">
         <v>95</v>
       </c>
-      <c r="E26" s="104"/>
-      <c r="F26" s="105"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="118"/>
       <c r="G26" s="47" t="s">
         <v>38</v>
       </c>
@@ -4326,7 +4376,7 @@
     </row>
     <row r="27" spans="1:14" ht="37.799999999999997">
       <c r="A27" s="11"/>
-      <c r="B27" s="109" t="str">
+      <c r="B27" s="113" t="str">
         <f>master!B18</f>
         <v>提案書のサンプルについて</v>
       </c>
@@ -4334,11 +4384,11 @@
         <f>master!C18</f>
         <v>はじめに</v>
       </c>
-      <c r="D27" s="103" t="s">
+      <c r="D27" s="116" t="s">
         <v>113</v>
       </c>
-      <c r="E27" s="104"/>
-      <c r="F27" s="105"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="118"/>
       <c r="G27" s="47" t="s">
         <v>98</v>
       </c>
@@ -4356,16 +4406,16 @@
     </row>
     <row r="28" spans="1:14" ht="25.2">
       <c r="A28" s="11"/>
-      <c r="B28" s="110"/>
+      <c r="B28" s="114"/>
       <c r="C28" s="47" t="str">
         <f>master!C19</f>
         <v>１．サマリ</v>
       </c>
-      <c r="D28" s="103" t="s">
+      <c r="D28" s="116" t="s">
         <v>96</v>
       </c>
-      <c r="E28" s="104"/>
-      <c r="F28" s="105"/>
+      <c r="E28" s="117"/>
+      <c r="F28" s="118"/>
       <c r="G28" s="47" t="s">
         <v>78</v>
       </c>
@@ -4383,16 +4433,16 @@
     </row>
     <row r="29" spans="1:14" ht="25.2">
       <c r="A29" s="11"/>
-      <c r="B29" s="110"/>
+      <c r="B29" s="114"/>
       <c r="C29" s="47" t="str">
         <f>master!C20</f>
         <v>２．背景</v>
       </c>
-      <c r="D29" s="103" t="s">
+      <c r="D29" s="116" t="s">
         <v>110</v>
       </c>
-      <c r="E29" s="104"/>
-      <c r="F29" s="105"/>
+      <c r="E29" s="117"/>
+      <c r="F29" s="118"/>
       <c r="G29" s="47" t="s">
         <v>78</v>
       </c>
@@ -4410,16 +4460,16 @@
     </row>
     <row r="30" spans="1:14" ht="25.2">
       <c r="A30" s="11"/>
-      <c r="B30" s="110"/>
+      <c r="B30" s="114"/>
       <c r="C30" s="47" t="str">
         <f>master!C21</f>
         <v>３．現状課題</v>
       </c>
-      <c r="D30" s="103" t="s">
+      <c r="D30" s="116" t="s">
         <v>111</v>
       </c>
-      <c r="E30" s="104"/>
-      <c r="F30" s="105"/>
+      <c r="E30" s="117"/>
+      <c r="F30" s="118"/>
       <c r="G30" s="47" t="s">
         <v>78</v>
       </c>
@@ -4437,16 +4487,16 @@
     </row>
     <row r="31" spans="1:14" ht="63">
       <c r="A31" s="11"/>
-      <c r="B31" s="110"/>
+      <c r="B31" s="114"/>
       <c r="C31" s="47" t="str">
         <f>master!C22</f>
         <v>４．業界動向・市場分析</v>
       </c>
-      <c r="D31" s="103" t="s">
+      <c r="D31" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="E31" s="104"/>
-      <c r="F31" s="105"/>
+      <c r="E31" s="117"/>
+      <c r="F31" s="118"/>
       <c r="G31" s="47" t="s">
         <v>99</v>
       </c>
@@ -4464,16 +4514,16 @@
     </row>
     <row r="32" spans="1:14" ht="37.799999999999997">
       <c r="A32" s="11"/>
-      <c r="B32" s="110"/>
+      <c r="B32" s="114"/>
       <c r="C32" s="47" t="str">
         <f>master!C23</f>
         <v>５．市場機会</v>
       </c>
-      <c r="D32" s="103" t="s">
+      <c r="D32" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="E32" s="104"/>
-      <c r="F32" s="105"/>
+      <c r="E32" s="117"/>
+      <c r="F32" s="118"/>
       <c r="G32" s="47" t="s">
         <v>98</v>
       </c>
@@ -4491,16 +4541,16 @@
     </row>
     <row r="33" spans="1:14" ht="37.799999999999997">
       <c r="A33" s="11"/>
-      <c r="B33" s="110"/>
+      <c r="B33" s="114"/>
       <c r="C33" s="47" t="str">
         <f>master!C24</f>
         <v>６．サービス概要</v>
       </c>
-      <c r="D33" s="103" t="s">
+      <c r="D33" s="116" t="s">
         <v>105</v>
       </c>
-      <c r="E33" s="104"/>
-      <c r="F33" s="105"/>
+      <c r="E33" s="117"/>
+      <c r="F33" s="118"/>
       <c r="G33" s="47" t="s">
         <v>98</v>
       </c>
@@ -4518,16 +4568,16 @@
     </row>
     <row r="34" spans="1:14" ht="63">
       <c r="A34" s="11"/>
-      <c r="B34" s="110"/>
+      <c r="B34" s="114"/>
       <c r="C34" s="47" t="str">
         <f>master!C25</f>
         <v>７．利用者体験イメージ</v>
       </c>
-      <c r="D34" s="103" t="s">
+      <c r="D34" s="116" t="s">
         <v>106</v>
       </c>
-      <c r="E34" s="104"/>
-      <c r="F34" s="105"/>
+      <c r="E34" s="117"/>
+      <c r="F34" s="118"/>
       <c r="G34" s="47" t="s">
         <v>99</v>
       </c>
@@ -4545,16 +4595,16 @@
     </row>
     <row r="35" spans="1:14" ht="25.2">
       <c r="A35" s="11"/>
-      <c r="B35" s="110"/>
+      <c r="B35" s="114"/>
       <c r="C35" s="47" t="str">
         <f>master!C26</f>
         <v>８．事業構成</v>
       </c>
-      <c r="D35" s="103" t="s">
+      <c r="D35" s="116" t="s">
         <v>97</v>
       </c>
-      <c r="E35" s="104"/>
-      <c r="F35" s="105"/>
+      <c r="E35" s="117"/>
+      <c r="F35" s="118"/>
       <c r="G35" s="47" t="s">
         <v>78</v>
       </c>
@@ -4572,16 +4622,16 @@
     </row>
     <row r="36" spans="1:14" ht="37.799999999999997">
       <c r="A36" s="11"/>
-      <c r="B36" s="110"/>
+      <c r="B36" s="114"/>
       <c r="C36" s="47" t="str">
         <f>master!C27</f>
         <v>９．提供価値</v>
       </c>
-      <c r="D36" s="103" t="s">
+      <c r="D36" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="E36" s="104"/>
-      <c r="F36" s="105"/>
+      <c r="E36" s="117"/>
+      <c r="F36" s="118"/>
       <c r="G36" s="47" t="s">
         <v>98</v>
       </c>
@@ -4599,16 +4649,16 @@
     </row>
     <row r="37" spans="1:14" ht="63">
       <c r="A37" s="11"/>
-      <c r="B37" s="110"/>
+      <c r="B37" s="114"/>
       <c r="C37" s="47" t="str">
         <f>master!C28</f>
         <v>１０．収益モデル</v>
       </c>
-      <c r="D37" s="103" t="s">
+      <c r="D37" s="116" t="s">
         <v>100</v>
       </c>
-      <c r="E37" s="104"/>
-      <c r="F37" s="105"/>
+      <c r="E37" s="117"/>
+      <c r="F37" s="118"/>
       <c r="G37" s="47" t="s">
         <v>99</v>
       </c>
@@ -4626,16 +4676,16 @@
     </row>
     <row r="38" spans="1:14" ht="63">
       <c r="A38" s="11"/>
-      <c r="B38" s="110"/>
+      <c r="B38" s="114"/>
       <c r="C38" s="47" t="str">
         <f>master!C29</f>
         <v>１１．リスク・課題</v>
       </c>
-      <c r="D38" s="103" t="s">
+      <c r="D38" s="116" t="s">
         <v>108</v>
       </c>
-      <c r="E38" s="104"/>
-      <c r="F38" s="105"/>
+      <c r="E38" s="117"/>
+      <c r="F38" s="118"/>
       <c r="G38" s="47" t="s">
         <v>99</v>
       </c>
@@ -4653,16 +4703,16 @@
     </row>
     <row r="39" spans="1:14" ht="37.799999999999997">
       <c r="A39" s="11"/>
-      <c r="B39" s="111"/>
+      <c r="B39" s="115"/>
       <c r="C39" s="47" t="str">
         <f>master!C30</f>
         <v>１２．今後の展望</v>
       </c>
-      <c r="D39" s="103" t="s">
+      <c r="D39" s="116" t="s">
         <v>109</v>
       </c>
-      <c r="E39" s="104"/>
-      <c r="F39" s="105"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="118"/>
       <c r="G39" s="47" t="s">
         <v>98</v>
       </c>
@@ -4680,19 +4730,19 @@
     </row>
     <row r="40" spans="1:14" ht="88.2">
       <c r="A40" s="11"/>
-      <c r="B40" s="112" t="str">
+      <c r="B40" s="83" t="str">
         <f>master!B32</f>
         <v>提案演習の全体像</v>
       </c>
       <c r="C40" s="64" t="str">
         <f>master!C32</f>
-        <v>提案演習の全体像について</v>
-      </c>
-      <c r="D40" s="97" t="s">
+        <v>研修の全体像について</v>
+      </c>
+      <c r="D40" s="107" t="s">
         <v>139</v>
       </c>
-      <c r="E40" s="98"/>
-      <c r="F40" s="99"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="109"/>
       <c r="G40" s="64" t="s">
         <v>131</v>
       </c>
@@ -4710,7 +4760,7 @@
     </row>
     <row r="41" spans="1:14" ht="201.6">
       <c r="A41" s="11"/>
-      <c r="B41" s="113" t="str">
+      <c r="B41" s="84" t="str">
         <f>master!B33</f>
         <v>提案資料</v>
       </c>
@@ -4718,11 +4768,11 @@
         <f>master!C33</f>
         <v>提案資料について</v>
       </c>
-      <c r="D41" s="97" t="s">
-        <v>157</v>
-      </c>
-      <c r="E41" s="98"/>
-      <c r="F41" s="99"/>
+      <c r="D41" s="107" t="s">
+        <v>156</v>
+      </c>
+      <c r="E41" s="108"/>
+      <c r="F41" s="109"/>
       <c r="G41" s="64" t="s">
         <v>80</v>
       </c>
@@ -4740,7 +4790,7 @@
     </row>
     <row r="42" spans="1:14" ht="163.80000000000001">
       <c r="A42" s="11"/>
-      <c r="B42" s="100" t="str">
+      <c r="B42" s="110" t="str">
         <f>master!B34</f>
         <v>提案資料の作成</v>
       </c>
@@ -4748,11 +4798,11 @@
         <f>master!C34</f>
         <v>提案テーマの検討</v>
       </c>
-      <c r="D42" s="97" t="s">
-        <v>146</v>
-      </c>
-      <c r="E42" s="98"/>
-      <c r="F42" s="99"/>
+      <c r="D42" s="107" t="s">
+        <v>145</v>
+      </c>
+      <c r="E42" s="108"/>
+      <c r="F42" s="109"/>
       <c r="G42" s="64" t="s">
         <v>132</v>
       </c>
@@ -4770,16 +4820,16 @@
     </row>
     <row r="43" spans="1:14" ht="138.6">
       <c r="A43" s="11"/>
-      <c r="B43" s="101"/>
+      <c r="B43" s="111"/>
       <c r="C43" s="64" t="str">
         <f>master!C35</f>
         <v>提案テーマの意見交換</v>
       </c>
-      <c r="D43" s="97" t="s">
-        <v>147</v>
-      </c>
-      <c r="E43" s="98"/>
-      <c r="F43" s="99"/>
+      <c r="D43" s="107" t="s">
+        <v>146</v>
+      </c>
+      <c r="E43" s="108"/>
+      <c r="F43" s="109"/>
       <c r="G43" s="64" t="s">
         <v>81</v>
       </c>
@@ -4797,16 +4847,16 @@
     </row>
     <row r="44" spans="1:14" ht="75.599999999999994">
       <c r="A44" s="11"/>
-      <c r="B44" s="101"/>
+      <c r="B44" s="111"/>
       <c r="C44" s="64" t="str">
         <f>master!C36</f>
         <v>提案テーマの調査</v>
       </c>
-      <c r="D44" s="97" t="s">
+      <c r="D44" s="107" t="s">
         <v>134</v>
       </c>
-      <c r="E44" s="98"/>
-      <c r="F44" s="99"/>
+      <c r="E44" s="108"/>
+      <c r="F44" s="109"/>
       <c r="G44" s="64" t="s">
         <v>130</v>
       </c>
@@ -4824,16 +4874,16 @@
     </row>
     <row r="45" spans="1:14" ht="88.2">
       <c r="A45" s="11"/>
-      <c r="B45" s="101"/>
+      <c r="B45" s="111"/>
       <c r="C45" s="64" t="str">
         <f>master!C37</f>
         <v>提案内容の具体化</v>
       </c>
-      <c r="D45" s="97" t="s">
+      <c r="D45" s="107" t="s">
         <v>133</v>
       </c>
-      <c r="E45" s="98"/>
-      <c r="F45" s="99"/>
+      <c r="E45" s="108"/>
+      <c r="F45" s="109"/>
       <c r="G45" s="64" t="s">
         <v>131</v>
       </c>
@@ -4851,18 +4901,18 @@
     </row>
     <row r="46" spans="1:14" ht="151.19999999999999">
       <c r="A46" s="11"/>
-      <c r="B46" s="101"/>
+      <c r="B46" s="111"/>
       <c r="C46" s="64" t="str">
         <f>master!C38</f>
         <v>提案資料の作成</v>
       </c>
-      <c r="D46" s="97" t="s">
+      <c r="D46" s="107" t="s">
         <v>135</v>
       </c>
-      <c r="E46" s="98"/>
-      <c r="F46" s="99"/>
+      <c r="E46" s="108"/>
+      <c r="F46" s="109"/>
       <c r="G46" s="64" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H46" s="65"/>
       <c r="I46" s="66" t="s">
@@ -4878,16 +4928,16 @@
     </row>
     <row r="47" spans="1:14" ht="25.2">
       <c r="A47" s="11"/>
-      <c r="B47" s="101"/>
+      <c r="B47" s="111"/>
       <c r="C47" s="64" t="str">
         <f>master!C39</f>
         <v>提案資料の提出</v>
       </c>
-      <c r="D47" s="97" t="s">
-        <v>158</v>
-      </c>
-      <c r="E47" s="98"/>
-      <c r="F47" s="99"/>
+      <c r="D47" s="107" t="s">
+        <v>164</v>
+      </c>
+      <c r="E47" s="108"/>
+      <c r="F47" s="109"/>
       <c r="G47" s="64" t="s">
         <v>82</v>
       </c>
@@ -4905,14 +4955,14 @@
     </row>
     <row r="48" spans="1:14" ht="25.2">
       <c r="A48" s="11"/>
-      <c r="B48" s="101"/>
+      <c r="B48" s="111"/>
       <c r="C48" s="64" t="str">
         <f>master!C40</f>
         <v>演習の実施</v>
       </c>
-      <c r="D48" s="97"/>
-      <c r="E48" s="98"/>
-      <c r="F48" s="99"/>
+      <c r="D48" s="107"/>
+      <c r="E48" s="108"/>
+      <c r="F48" s="109"/>
       <c r="G48" s="64" t="s">
         <v>82</v>
       </c>
@@ -4930,7 +4980,7 @@
     </row>
     <row r="49" spans="1:14" ht="88.2">
       <c r="A49" s="11"/>
-      <c r="B49" s="100" t="str">
+      <c r="B49" s="110" t="str">
         <f>master!B41</f>
         <v>提案の実施</v>
       </c>
@@ -4938,11 +4988,11 @@
         <f>master!C41</f>
         <v>提案の実施の説明</v>
       </c>
-      <c r="D49" s="97" t="s">
+      <c r="D49" s="107" t="s">
         <v>136</v>
       </c>
-      <c r="E49" s="98"/>
-      <c r="F49" s="99"/>
+      <c r="E49" s="108"/>
+      <c r="F49" s="109"/>
       <c r="G49" s="64" t="s">
         <v>131</v>
       </c>
@@ -4960,16 +5010,16 @@
     </row>
     <row r="50" spans="1:14" ht="25.2">
       <c r="A50" s="11"/>
-      <c r="B50" s="101"/>
+      <c r="B50" s="111"/>
       <c r="C50" s="64" t="str">
         <f>master!C42</f>
         <v>発表順の決定</v>
       </c>
-      <c r="D50" s="97" t="s">
-        <v>149</v>
-      </c>
-      <c r="E50" s="98"/>
-      <c r="F50" s="99"/>
+      <c r="D50" s="107" t="s">
+        <v>148</v>
+      </c>
+      <c r="E50" s="108"/>
+      <c r="F50" s="109"/>
       <c r="G50" s="64" t="s">
         <v>82</v>
       </c>
@@ -4987,16 +5037,16 @@
     </row>
     <row r="51" spans="1:14" ht="25.2">
       <c r="A51" s="11"/>
-      <c r="B51" s="101"/>
+      <c r="B51" s="111"/>
       <c r="C51" s="64" t="str">
         <f>master!C43</f>
         <v>提案の実施</v>
       </c>
-      <c r="D51" s="97" t="s">
-        <v>160</v>
-      </c>
-      <c r="E51" s="98"/>
-      <c r="F51" s="99"/>
+      <c r="D51" s="107" t="s">
+        <v>158</v>
+      </c>
+      <c r="E51" s="108"/>
+      <c r="F51" s="109"/>
       <c r="G51" s="64" t="s">
         <v>82</v>
       </c>
@@ -5014,16 +5064,16 @@
     </row>
     <row r="52" spans="1:14" ht="25.2">
       <c r="A52" s="11"/>
-      <c r="B52" s="101"/>
+      <c r="B52" s="111"/>
       <c r="C52" s="64" t="str">
         <f>master!C44</f>
         <v>提案のフィードバック</v>
       </c>
-      <c r="D52" s="97" t="s">
-        <v>161</v>
-      </c>
-      <c r="E52" s="98"/>
-      <c r="F52" s="99"/>
+      <c r="D52" s="107" t="s">
+        <v>159</v>
+      </c>
+      <c r="E52" s="108"/>
+      <c r="F52" s="109"/>
       <c r="G52" s="64" t="s">
         <v>82</v>
       </c>
@@ -5041,14 +5091,14 @@
     </row>
     <row r="53" spans="1:14" ht="25.2">
       <c r="A53" s="11"/>
-      <c r="B53" s="102"/>
+      <c r="B53" s="112"/>
       <c r="C53" s="64" t="str">
         <f>master!C45</f>
         <v>演習の実施</v>
       </c>
-      <c r="D53" s="97"/>
-      <c r="E53" s="98"/>
-      <c r="F53" s="99"/>
+      <c r="D53" s="107"/>
+      <c r="E53" s="108"/>
+      <c r="F53" s="109"/>
       <c r="G53" s="64" t="s">
         <v>82</v>
       </c>
@@ -5066,7 +5116,7 @@
     </row>
     <row r="54" spans="1:14" ht="113.4">
       <c r="A54" s="11"/>
-      <c r="B54" s="100" t="str">
+      <c r="B54" s="110" t="str">
         <f>master!B46</f>
         <v>提案の改善</v>
       </c>
@@ -5074,11 +5124,11 @@
         <f>master!C46</f>
         <v>演習内容の説明</v>
       </c>
-      <c r="D54" s="97" t="s">
-        <v>159</v>
-      </c>
-      <c r="E54" s="98"/>
-      <c r="F54" s="99"/>
+      <c r="D54" s="107" t="s">
+        <v>157</v>
+      </c>
+      <c r="E54" s="108"/>
+      <c r="F54" s="109"/>
       <c r="G54" s="64" t="s">
         <v>79</v>
       </c>
@@ -5096,16 +5146,16 @@
     </row>
     <row r="55" spans="1:14" ht="25.2">
       <c r="A55" s="11"/>
-      <c r="B55" s="101"/>
+      <c r="B55" s="111"/>
       <c r="C55" s="64" t="str">
         <f>master!C47</f>
         <v>フィードバック内容の整理</v>
       </c>
-      <c r="D55" s="97" t="s">
-        <v>162</v>
-      </c>
-      <c r="E55" s="98"/>
-      <c r="F55" s="99"/>
+      <c r="D55" s="107" t="s">
+        <v>160</v>
+      </c>
+      <c r="E55" s="108"/>
+      <c r="F55" s="109"/>
       <c r="G55" s="64" t="s">
         <v>82</v>
       </c>
@@ -5123,16 +5173,16 @@
     </row>
     <row r="56" spans="1:14" ht="25.2">
       <c r="A56" s="11"/>
-      <c r="B56" s="101"/>
+      <c r="B56" s="111"/>
       <c r="C56" s="64" t="str">
         <f>master!C48</f>
         <v>提案資料の修正</v>
       </c>
-      <c r="D56" s="97" t="s">
-        <v>163</v>
-      </c>
-      <c r="E56" s="98"/>
-      <c r="F56" s="99"/>
+      <c r="D56" s="107" t="s">
+        <v>161</v>
+      </c>
+      <c r="E56" s="108"/>
+      <c r="F56" s="109"/>
       <c r="G56" s="64" t="s">
         <v>82</v>
       </c>
@@ -5150,16 +5200,16 @@
     </row>
     <row r="57" spans="1:14" ht="25.2">
       <c r="A57" s="11"/>
-      <c r="B57" s="101"/>
+      <c r="B57" s="111"/>
       <c r="C57" s="64" t="str">
         <f>master!C49</f>
         <v>提案資料の確認</v>
       </c>
-      <c r="D57" s="97" t="s">
-        <v>164</v>
-      </c>
-      <c r="E57" s="98"/>
-      <c r="F57" s="99"/>
+      <c r="D57" s="107" t="s">
+        <v>162</v>
+      </c>
+      <c r="E57" s="108"/>
+      <c r="F57" s="109"/>
       <c r="G57" s="64" t="s">
         <v>82</v>
       </c>
@@ -5175,20 +5225,20 @@
       <c r="M57" s="6"/>
       <c r="N57" s="6"/>
     </row>
-    <row r="58" spans="1:14" ht="25.2">
+    <row r="58" spans="1:14" ht="37.799999999999997">
       <c r="A58" s="11"/>
-      <c r="B58" s="101"/>
+      <c r="B58" s="111"/>
       <c r="C58" s="64" t="str">
         <f>master!C50</f>
         <v>提案資料の提出</v>
       </c>
-      <c r="D58" s="97" t="s">
-        <v>158</v>
-      </c>
-      <c r="E58" s="98"/>
-      <c r="F58" s="99"/>
+      <c r="D58" s="107" t="s">
+        <v>166</v>
+      </c>
+      <c r="E58" s="108"/>
+      <c r="F58" s="109"/>
       <c r="G58" s="64" t="s">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="H58" s="65"/>
       <c r="I58" s="66" t="s">
@@ -5204,14 +5254,14 @@
     </row>
     <row r="59" spans="1:14" ht="25.2">
       <c r="A59" s="11"/>
-      <c r="B59" s="101"/>
+      <c r="B59" s="111"/>
       <c r="C59" s="64" t="str">
         <f>master!C51</f>
         <v>最終発表の準備</v>
       </c>
-      <c r="D59" s="97"/>
-      <c r="E59" s="98"/>
-      <c r="F59" s="99"/>
+      <c r="D59" s="107"/>
+      <c r="E59" s="108"/>
+      <c r="F59" s="109"/>
       <c r="G59" s="64" t="s">
         <v>82</v>
       </c>
@@ -5229,14 +5279,14 @@
     </row>
     <row r="60" spans="1:14" ht="25.2">
       <c r="A60" s="11"/>
-      <c r="B60" s="102"/>
+      <c r="B60" s="112"/>
       <c r="C60" s="64" t="str">
         <f>master!C52</f>
         <v>演習の実施</v>
       </c>
-      <c r="D60" s="97"/>
-      <c r="E60" s="98"/>
-      <c r="F60" s="99"/>
+      <c r="D60" s="107"/>
+      <c r="E60" s="108"/>
+      <c r="F60" s="109"/>
       <c r="G60" s="64" t="s">
         <v>82</v>
       </c>
@@ -5254,39 +5304,21 @@
     </row>
   </sheetData>
   <mergeCells count="62">
-    <mergeCell ref="D50:F50"/>
-    <mergeCell ref="D56:F56"/>
-    <mergeCell ref="D55:F55"/>
-    <mergeCell ref="D58:F58"/>
-    <mergeCell ref="B54:B60"/>
-    <mergeCell ref="B49:B53"/>
-    <mergeCell ref="D59:F59"/>
-    <mergeCell ref="B15:B26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="B27:B39"/>
-    <mergeCell ref="D43:F43"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D40:F40"/>
-    <mergeCell ref="D42:F42"/>
-    <mergeCell ref="B42:B48"/>
-    <mergeCell ref="D47:F47"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="H12:H13"/>
-    <mergeCell ref="B4:E4"/>
-    <mergeCell ref="B5:K5"/>
-    <mergeCell ref="D12:F13"/>
-    <mergeCell ref="G12:G13"/>
-    <mergeCell ref="B12:B13"/>
-    <mergeCell ref="C12:C13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D41:F41"/>
-    <mergeCell ref="D15:F15"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D16:F16"/>
-    <mergeCell ref="D18:F18"/>
-    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D46:F46"/>
+    <mergeCell ref="D48:F48"/>
+    <mergeCell ref="D60:F60"/>
+    <mergeCell ref="D44:F44"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="D54:F54"/>
+    <mergeCell ref="D52:F52"/>
+    <mergeCell ref="D53:F53"/>
+    <mergeCell ref="D51:F51"/>
+    <mergeCell ref="D14:F14"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="D31:F31"/>
+    <mergeCell ref="D32:F32"/>
     <mergeCell ref="D17:F17"/>
     <mergeCell ref="D38:F38"/>
     <mergeCell ref="D26:F26"/>
@@ -5300,22 +5332,40 @@
     <mergeCell ref="D35:F35"/>
     <mergeCell ref="D36:F36"/>
     <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D14:F14"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="H12:H13"/>
+    <mergeCell ref="B4:E4"/>
+    <mergeCell ref="B5:K5"/>
+    <mergeCell ref="D12:F13"/>
+    <mergeCell ref="G12:G13"/>
+    <mergeCell ref="B12:B13"/>
+    <mergeCell ref="C12:C13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="B15:B26"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="B27:B39"/>
+    <mergeCell ref="D43:F43"/>
+    <mergeCell ref="D28:F28"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="D42:F42"/>
+    <mergeCell ref="B42:B48"/>
+    <mergeCell ref="D47:F47"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="D41:F41"/>
+    <mergeCell ref="D15:F15"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D16:F16"/>
+    <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D50:F50"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="D55:F55"/>
+    <mergeCell ref="D58:F58"/>
+    <mergeCell ref="B54:B60"/>
+    <mergeCell ref="B49:B53"/>
+    <mergeCell ref="D59:F59"/>
     <mergeCell ref="D49:F49"/>
-    <mergeCell ref="D46:F46"/>
-    <mergeCell ref="D48:F48"/>
-    <mergeCell ref="D60:F60"/>
-    <mergeCell ref="D44:F44"/>
-    <mergeCell ref="D45:F45"/>
-    <mergeCell ref="D57:F57"/>
-    <mergeCell ref="D54:F54"/>
-    <mergeCell ref="D52:F52"/>
-    <mergeCell ref="D53:F53"/>
-    <mergeCell ref="D51:F51"/>
   </mergeCells>
   <phoneticPr fontId="3"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5518,15 +5568,15 @@
         <v>144</v>
       </c>
       <c r="C32" s="69" t="s">
-        <v>145</v>
+        <v>167</v>
       </c>
     </row>
     <row r="33" spans="2:3">
       <c r="B33" t="s">
+        <v>154</v>
+      </c>
+      <c r="C33" s="69" t="s">
         <v>155</v>
-      </c>
-      <c r="C33" s="69" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="34" spans="2:3">
@@ -5554,17 +5604,17 @@
     </row>
     <row r="38" spans="2:3">
       <c r="C38" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="39" spans="2:3">
       <c r="C39" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="40" spans="2:3">
       <c r="C40" s="69" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="41" spans="2:3">
@@ -5592,7 +5642,7 @@
     </row>
     <row r="45" spans="2:3">
       <c r="C45" s="69" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="46" spans="2:3">
@@ -5610,17 +5660,17 @@
     </row>
     <row r="48" spans="2:3">
       <c r="C48" s="69" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="49" spans="3:3">
       <c r="C49" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="50" spans="3:3">
       <c r="C50" s="69" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="51" spans="3:3">
@@ -5630,7 +5680,7 @@
     </row>
     <row r="52" spans="3:3">
       <c r="C52" s="69" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
   </sheetData>
